--- a/results/results.xlsx
+++ b/results/results.xlsx
@@ -1,204 +1,288 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="30720" windowHeight="15540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="30720" windowHeight="15540" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="train2" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="append" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="epoch" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="train2" sheetId="1" r:id="rId1"/>
+    <sheet name="append" sheetId="2" r:id="rId2"/>
+    <sheet name="epoch" sheetId="3" r:id="rId3"/>
+    <sheet name="test_domain" sheetId="4" r:id="rId4"/>
+    <sheet name="origin_domain_num" sheetId="5" r:id="rId5"/>
+    <sheet name="O" sheetId="6" r:id="rId6"/>
+    <sheet name="T" sheetId="7" r:id="rId7"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="20">
+  <si>
+    <t>HyperParameters</t>
+  </si>
+  <si>
+    <t>Origin_domain_nums</t>
+  </si>
+  <si>
+    <t>VAL_ACC</t>
+  </si>
+  <si>
+    <t>VAL_F1</t>
+  </si>
+  <si>
+    <t>TEST_ACC</t>
+  </si>
+  <si>
+    <t>TEST_F1</t>
+  </si>
+  <si>
+    <t>epoch</t>
+  </si>
+  <si>
+    <t>loss_value</t>
+  </si>
+  <si>
+    <t>kernel_size</t>
+  </si>
+  <si>
+    <t>NaN</t>
+  </si>
+  <si>
+    <t>out_channels</t>
+  </si>
+  <si>
+    <t>stride</t>
+  </si>
+  <si>
+    <t>acc</t>
+  </si>
+  <si>
+    <t>f1</t>
+  </si>
+  <si>
+    <t>test_domain</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>192</t>
+  </si>
+  <si>
+    <t>224</t>
+  </si>
+  <si>
+    <t>299</t>
+  </si>
+  <si>
+    <t>331</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="34">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -396,7 +480,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -563,218 +647,179 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="9" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="10" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="11" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -828,7 +873,14 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.4"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -838,74 +890,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1192,915 +1181,1996 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:O13"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
-    <col width="12.1666666666667" customWidth="1" min="3" max="4"/>
-    <col width="10.0555555555556" customWidth="1" min="8" max="8"/>
+    <col min="3" max="4" width="12.1666666666667" customWidth="1"/>
+    <col min="8" max="8" width="10.0555555555556" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>HyperParameters</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Origin_domain_nums</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>VAL_ACC</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>VAL_F1</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>TEST_ACC</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>TEST_F1</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>epoch</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>loss_value</t>
-        </is>
-      </c>
-      <c r="K1" s="9" t="n"/>
-      <c r="L1" s="9" t="n"/>
-      <c r="M1" s="9" t="n"/>
-      <c r="N1" s="9" t="n"/>
-      <c r="O1" s="1" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>kernel_size</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
+    <row r="1" spans="1:15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="1"/>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="5">
+        <v>1</v>
+      </c>
+      <c r="C2">
         <v>99.286142</v>
       </c>
-      <c r="D2" t="n">
-        <v>99.11224199999999</v>
-      </c>
-      <c r="E2" s="2" t="n">
+      <c r="D2">
+        <v>99.112242</v>
+      </c>
+      <c r="E2" s="4">
         <v>98.672</v>
       </c>
-      <c r="F2" s="2" t="n">
-        <v>97.91500000000001</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="F2" s="4">
+        <v>97.915</v>
+      </c>
+      <c r="G2">
         <v>18</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>-4.553487</v>
       </c>
-      <c r="K2" s="8" t="n"/>
-      <c r="L2" s="8" t="n"/>
-      <c r="M2" s="8" t="n"/>
-      <c r="N2" s="8" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="3" t="n">
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="2"/>
+      <c r="B3" s="5">
         <v>2</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>99.795565</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>99.668491</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>99.806</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>99.654</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>17</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>-4.95593</v>
       </c>
-      <c r="K3" s="8" t="n"/>
-      <c r="L3" s="8" t="n"/>
-      <c r="M3" s="8" t="n"/>
-      <c r="N3" s="8" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="n"/>
-      <c r="B4" s="3" t="n">
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="2"/>
+      <c r="B4" s="5">
         <v>3</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>99.958742</v>
       </c>
-      <c r="D4" t="n">
-        <v>99.94950300000001</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="D4">
+        <v>99.949503</v>
+      </c>
+      <c r="E4">
         <v>99.979</v>
       </c>
-      <c r="F4" t="n">
-        <v>99.97499999999999</v>
-      </c>
-      <c r="G4" t="n">
-        <v>9</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
-      <c r="K4" s="8" t="n"/>
-      <c r="L4" s="8" t="n"/>
-      <c r="M4" s="8" t="n"/>
-      <c r="N4" s="8" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="n"/>
-      <c r="B5" s="1" t="n">
+      <c r="F4">
+        <v>99.975</v>
+      </c>
+      <c r="G4">
+        <v>9</v>
+      </c>
+      <c r="H4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="3"/>
+      <c r="B5" s="1">
         <v>4</v>
       </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="K5" s="8" t="n"/>
-      <c r="L5" s="8" t="n"/>
-      <c r="M5" s="8" t="n"/>
-      <c r="N5" s="8" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>out_channels</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="n">
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1">
         <v>1</v>
       </c>
-      <c r="C6" t="n">
-        <v>99.86518599999999</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="C6">
+        <v>99.865186</v>
+      </c>
+      <c r="D6">
         <v>99.790657</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="4">
         <v>94.774</v>
       </c>
-      <c r="F6" s="2" t="n">
-        <v>91.98699999999999</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="F6" s="4">
+        <v>91.987</v>
+      </c>
+      <c r="G6">
         <v>18</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>-1.901774</v>
       </c>
-      <c r="K6" s="8" t="n"/>
-      <c r="L6" s="8" t="n"/>
-      <c r="M6" s="8" t="n"/>
-      <c r="N6" s="8" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="n"/>
-      <c r="B7" s="3" t="n">
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="2"/>
+      <c r="B7" s="5">
         <v>2</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>99.899438</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>99.861825</v>
       </c>
-      <c r="E7" t="n">
-        <v>99.94199999999999</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="E7">
+        <v>99.942</v>
+      </c>
+      <c r="F7">
         <v>99.895</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>18</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
-      <c r="K7" s="8" t="n"/>
-      <c r="L7" s="8" t="n"/>
-      <c r="M7" s="8" t="n"/>
-      <c r="N7" s="8" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n"/>
-      <c r="B8" s="3" t="n">
+      <c r="H7" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="2"/>
+      <c r="B8" s="5">
         <v>3</v>
       </c>
-      <c r="C8" t="n">
-        <v>99.91233099999999</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="C8">
+        <v>99.912331</v>
+      </c>
+      <c r="D8">
         <v>99.863231</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>99.923</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>99.854</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>15</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="n"/>
-      <c r="L8" s="8" t="n"/>
-      <c r="M8" s="8" t="n"/>
-      <c r="N8" s="8" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="n"/>
-      <c r="B9" s="1" t="n">
+      <c r="H8" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="3"/>
+      <c r="B9" s="1">
         <v>4</v>
       </c>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
-      <c r="H9" s="8" t="n"/>
-      <c r="I9" s="10" t="n"/>
-      <c r="K9" s="8" t="n"/>
-      <c r="L9" s="8" t="n"/>
-      <c r="M9" s="8" t="n"/>
-      <c r="N9" s="8" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>stride</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n">
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="10"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="7">
         <v>1</v>
       </c>
-      <c r="C10" t="n">
-        <v>72.38270044326779</v>
-      </c>
-      <c r="D10" t="n">
+      <c r="C10">
+        <v>72.3827004432678</v>
+      </c>
+      <c r="D10">
         <v>58.018171787262</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="4">
         <v>19.65</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" s="4">
         <v>19.597</v>
       </c>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="10" t="n"/>
-      <c r="K10" s="8" t="n"/>
-      <c r="L10" s="8" t="n"/>
-      <c r="M10" s="8" t="n"/>
-      <c r="N10" s="8" t="n"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="7" t="n">
+      <c r="H10" s="8"/>
+      <c r="I10" s="10"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+    </row>
+    <row r="11" spans="2:14">
+      <c r="B11" s="7">
         <v>2</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>63.8185977935791</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>50.573068857193</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" s="4">
         <v>12.272</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F11" s="4">
         <v>12.17</v>
       </c>
-      <c r="H11" s="8" t="n"/>
-      <c r="I11" s="10" t="n"/>
-      <c r="K11" s="8" t="n"/>
-      <c r="L11" s="8" t="n"/>
-      <c r="M11" s="8" t="n"/>
-      <c r="N11" s="8" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="7" t="n">
+      <c r="H11" s="8"/>
+      <c r="I11" s="10"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+    </row>
+    <row r="12" spans="2:14">
+      <c r="B12" s="7">
         <v>3</v>
       </c>
-      <c r="C12" t="n">
-        <v>75.82381367683411</v>
-      </c>
-      <c r="D12" t="n">
+      <c r="C12">
+        <v>75.8238136768341</v>
+      </c>
+      <c r="D12">
         <v>59.1672897338867</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" s="4">
         <v>21.244</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="F12" s="4">
         <v>20.374</v>
       </c>
-      <c r="H12" s="8" t="n"/>
-      <c r="I12" s="10" t="n"/>
-      <c r="K12" s="8" t="n"/>
-      <c r="L12" s="8" t="n"/>
-      <c r="M12" s="8" t="n"/>
-      <c r="N12" s="8" t="n"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="7" t="n">
+      <c r="H12" s="8"/>
+      <c r="I12" s="10"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+    </row>
+    <row r="13" spans="2:2">
+      <c r="B13" s="7">
         <v>4</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
     <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A6:A9"/>
   </mergeCells>
   <conditionalFormatting sqref="K2:N13">
-    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>95</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F13"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="5"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>HyperParameters</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Origin_domain_nums</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>VAL_ACC</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>VAL_F1</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>TEST_ACC</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>TEST_F1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>kernel_size</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="n">
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2">
         <v>99.9593049287796</v>
       </c>
-      <c r="D2" t="n">
-        <v>99.93973970413209</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="D2">
+        <v>99.9397397041321</v>
+      </c>
+      <c r="E2">
         <v>98.398</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>98.792</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="1" t="n">
+    <row r="3" spans="1:6">
+      <c r="A3" s="2"/>
+      <c r="B3" s="1">
         <v>2</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>99.7955650091171</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>99.6684908866882</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="4">
         <v>64.816</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="4">
         <v>29.186</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="n"/>
-      <c r="B4" s="1" t="n">
+    <row r="4" spans="1:6">
+      <c r="A4" s="2"/>
+      <c r="B4" s="1">
         <v>3</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>99.9587416648865</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>99.9495029449463</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="4">
         <v>63.254</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="4">
         <v>26.131</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="n"/>
-      <c r="B5" s="1" t="n">
+    <row r="5" spans="1:6">
+      <c r="A5" s="3"/>
+      <c r="B5" s="1">
         <v>4</v>
       </c>
-      <c r="C5" t="n">
-        <v>99.99095499515531</v>
-      </c>
-      <c r="D5" t="n">
-        <v>99.99334812164309</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="C5">
+        <v>99.9909549951553</v>
+      </c>
+      <c r="D5">
+        <v>99.9933481216431</v>
+      </c>
+      <c r="E5">
         <v>98.173</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>98.617</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>out_channels</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="n">
+    <row r="6" spans="1:6">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1">
         <v>1</v>
       </c>
-      <c r="C6" t="n">
-        <v>99.84175264835361</v>
-      </c>
-      <c r="D6" t="n">
-        <v>99.71640110015871</v>
-      </c>
-      <c r="E6" s="2" t="n">
+      <c r="C6">
+        <v>99.8417526483536</v>
+      </c>
+      <c r="D6">
+        <v>99.7164011001587</v>
+      </c>
+      <c r="E6" s="4">
         <v>65.471</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="4">
         <v>45.811</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="n"/>
-      <c r="B7" s="1" t="n">
+    <row r="7" spans="1:6">
+      <c r="A7" s="2"/>
+      <c r="B7" s="1">
         <v>2</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>99.8994380235672</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>99.8618245124817</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="4">
         <v>57.042</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="4">
         <v>46.206</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="n"/>
-      <c r="B8" s="1" t="n">
+    <row r="8" spans="1:6">
+      <c r="A8" s="2"/>
+      <c r="B8" s="1">
         <v>3</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>99.9123305082321</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>99.8632311820984</v>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>85.09999999999999</v>
-      </c>
-      <c r="F8" s="2" t="n">
+      <c r="E8" s="4">
+        <v>85.1</v>
+      </c>
+      <c r="F8" s="4">
         <v>69.209</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="5" t="n"/>
-      <c r="B9" s="1" t="n">
+    <row r="9" spans="1:6">
+      <c r="A9" s="3"/>
+      <c r="B9" s="1">
         <v>4</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>99.8711407184601</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>99.7591853141785</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="4">
         <v>58.145</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="4">
         <v>42.666</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>stride</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="n">
+    <row r="10" spans="1:6">
+      <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1">
         <v>1</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>99.941223859787</v>
       </c>
-      <c r="D10" t="n">
-        <v>99.84889626502989</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="D10">
+        <v>99.8488962650299</v>
+      </c>
+      <c r="E10">
         <v>97.818</v>
       </c>
-      <c r="F10" t="n">
-        <v>94.09999999999999</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="1" t="n">
+      <c r="F10">
+        <v>94.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="2"/>
+      <c r="B11" s="1">
         <v>2</v>
       </c>
-      <c r="C11" t="n">
-        <v>99.93895888328549</v>
-      </c>
-      <c r="D11" t="n">
+      <c r="C11">
+        <v>99.9389588832855</v>
+      </c>
+      <c r="D11">
         <v>99.8430132865906</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>97.578</v>
       </c>
-      <c r="F11" t="n">
-        <v>93.45399999999999</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="1" t="n">
+      <c r="F11">
+        <v>93.454</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="2"/>
+      <c r="B12" s="1">
         <v>3</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>99.9547839164734</v>
       </c>
-      <c r="D12" t="n">
-        <v>99.88374710083011</v>
-      </c>
-      <c r="E12" t="n">
+      <c r="D12">
+        <v>99.8837471008301</v>
+      </c>
+      <c r="E12">
         <v>97.327</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>92.614</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="n"/>
-      <c r="B13" s="1" t="n">
+    <row r="13" spans="1:6">
+      <c r="A13" s="3"/>
+      <c r="B13" s="1">
         <v>4</v>
       </c>
-      <c r="C13" t="n">
-        <v>99.93669986724851</v>
-      </c>
-      <c r="D13" t="n">
+      <c r="C13">
+        <v>99.9366998672485</v>
+      </c>
+      <c r="D13">
         <v>99.8372435569763</v>
       </c>
-      <c r="E13" t="n">
-        <v>97.33199999999999</v>
-      </c>
-      <c r="F13" t="n">
+      <c r="E13">
+        <v>97.332</v>
+      </c>
+      <c r="F13">
         <v>92.608</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
     <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A6:A9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="5"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>HyperParameters</t>
-        </is>
-      </c>
-      <c r="B1" s="11" t="inlineStr">
-        <is>
-          <t>Origin_domain_nums</t>
-        </is>
-      </c>
-      <c r="C1" s="11" t="inlineStr">
-        <is>
-          <t>epoch</t>
-        </is>
-      </c>
-      <c r="D1" s="11" t="inlineStr">
-        <is>
-          <t>acc</t>
-        </is>
-      </c>
-      <c r="E1" s="11" t="inlineStr">
-        <is>
-          <t>f1</t>
-        </is>
-      </c>
-      <c r="F1" s="11" t="inlineStr">
-        <is>
-          <t>loss_value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>kernel_size</t>
-        </is>
-      </c>
-      <c r="B2" s="11" t="n">
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="n">
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>8</v>
+      </c>
+      <c r="D2">
         <v>99.9593049287796</v>
       </c>
-      <c r="E2" t="n">
-        <v>99.93973970413208</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-4.995636097957633</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="n"/>
-      <c r="B3" s="11" t="n">
+      <c r="E2">
+        <v>99.9397397041321</v>
+      </c>
+      <c r="F2">
+        <v>-4.99563609795763</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="2"/>
+      <c r="B3" s="1">
         <v>2</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>17</v>
       </c>
-      <c r="D3" t="n">
-        <v>99.79556500911713</v>
-      </c>
-      <c r="E3" t="n">
-        <v>99.66849088668823</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-4.955929873519099</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="n"/>
-      <c r="B4" s="11" t="n">
+      <c r="D3">
+        <v>99.7955650091171</v>
+      </c>
+      <c r="E3">
+        <v>99.6684908866882</v>
+      </c>
+      <c r="F3">
+        <v>-4.9559298735191</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2"/>
+      <c r="B4" s="1">
         <v>3</v>
       </c>
-      <c r="C4" t="n">
-        <v>9</v>
-      </c>
-      <c r="D4" t="n">
-        <v>99.95874166488647</v>
-      </c>
-      <c r="E4" t="n">
-        <v>99.94950294494629</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="n"/>
-      <c r="B5" s="11" t="n">
+      <c r="C4">
+        <v>9</v>
+      </c>
+      <c r="D4">
+        <v>99.9587416648865</v>
+      </c>
+      <c r="E4">
+        <v>99.9495029449463</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="3"/>
+      <c r="B5" s="1">
         <v>4</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>15</v>
       </c>
-      <c r="D5" t="n">
-        <v>99.99095499515533</v>
-      </c>
-      <c r="E5" t="n">
-        <v>99.99334812164307</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-4.998751735411627</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>out_channels</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="n">
+      <c r="D5">
+        <v>99.9909549951553</v>
+      </c>
+      <c r="E5">
+        <v>99.9933481216431</v>
+      </c>
+      <c r="F5">
+        <v>-4.99875173541163</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1">
         <v>1</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>21</v>
       </c>
-      <c r="D6" t="n">
-        <v>99.84175264835358</v>
-      </c>
-      <c r="E6" t="n">
-        <v>99.71640110015869</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-1.982393078032257</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="n"/>
-      <c r="B7" s="11" t="n">
+      <c r="D6">
+        <v>99.8417526483536</v>
+      </c>
+      <c r="E6">
+        <v>99.7164011001587</v>
+      </c>
+      <c r="F6">
+        <v>-1.98239307803226</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2"/>
+      <c r="B7" s="1">
         <v>2</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>18</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>99.8994380235672</v>
       </c>
-      <c r="E7" t="n">
-        <v>99.86182451248169</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="n"/>
-      <c r="B8" s="11" t="n">
+      <c r="E7">
+        <v>99.8618245124817</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2"/>
+      <c r="B8" s="1">
         <v>3</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>15</v>
       </c>
-      <c r="D8" t="n">
-        <v>99.91233050823212</v>
-      </c>
-      <c r="E8" t="n">
-        <v>99.86323118209839</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="n"/>
-      <c r="B9" s="11" t="n">
+      <c r="D8">
+        <v>99.9123305082321</v>
+      </c>
+      <c r="E8">
+        <v>99.8632311820984</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3"/>
+      <c r="B9" s="1">
         <v>4</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>18</v>
       </c>
-      <c r="D9" t="n">
-        <v>99.87114071846008</v>
-      </c>
-      <c r="E9" t="n">
-        <v>99.75918531417847</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-1.983924461927028</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>stride</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="n">
+      <c r="D9">
+        <v>99.8711407184601</v>
+      </c>
+      <c r="E9">
+        <v>99.7591853141785</v>
+      </c>
+      <c r="F9">
+        <v>-1.98392446192703</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1">
         <v>1</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>20</v>
       </c>
-      <c r="D10" t="n">
-        <v>99.94122385978699</v>
-      </c>
-      <c r="E10" t="n">
-        <v>99.84889626502991</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-9.988624556216202</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="n"/>
-      <c r="B11" s="11" t="n">
+      <c r="D10">
+        <v>99.941223859787</v>
+      </c>
+      <c r="E10">
+        <v>99.8488962650299</v>
+      </c>
+      <c r="F10">
+        <v>-9.9886245562162</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="2"/>
+      <c r="B11" s="1">
         <v>2</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>18</v>
       </c>
-      <c r="D11" t="n">
-        <v>99.93895888328552</v>
-      </c>
-      <c r="E11" t="n">
-        <v>99.84301328659058</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-9.988607092399818</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="11" t="n">
+      <c r="D11">
+        <v>99.9389588832855</v>
+      </c>
+      <c r="E11">
+        <v>99.8430132865906</v>
+      </c>
+      <c r="F11">
+        <v>-9.98860709239982</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="2"/>
+      <c r="B12" s="1">
         <v>3</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>17</v>
       </c>
-      <c r="D12" t="n">
-        <v>99.95478391647339</v>
-      </c>
-      <c r="E12" t="n">
-        <v>99.88374710083008</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-9.991065744719753</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="n"/>
-      <c r="B13" s="11" t="n">
+      <c r="D12">
+        <v>99.9547839164734</v>
+      </c>
+      <c r="E12">
+        <v>99.8837471008301</v>
+      </c>
+      <c r="F12">
+        <v>-9.99106574471975</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3"/>
+      <c r="B13" s="1">
         <v>4</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>13</v>
       </c>
-      <c r="D13" t="n">
-        <v>99.93669986724854</v>
-      </c>
-      <c r="E13" t="n">
-        <v>99.83724355697632</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-9.987175696157996</v>
+      <c r="D13">
+        <v>99.9366998672485</v>
+      </c>
+      <c r="E13">
+        <v>99.8372435569763</v>
+      </c>
+      <c r="F13">
+        <v>-9.987175696158</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
     <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A6:A9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="7"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2">
+        <v>99.9107033014297</v>
+      </c>
+      <c r="D2">
+        <v>99.9189853668213</v>
+      </c>
+      <c r="E2">
+        <v>99.471</v>
+      </c>
+      <c r="F2">
+        <v>99.588</v>
+      </c>
+      <c r="G2">
+        <v>9</v>
+      </c>
+      <c r="H2">
+        <v>0.00363413141153578</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="2"/>
+      <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3">
+        <v>99.8767912387848</v>
+      </c>
+      <c r="D3">
+        <v>99.8790264129639</v>
+      </c>
+      <c r="E3">
+        <v>99.851</v>
+      </c>
+      <c r="F3">
+        <v>99.872</v>
+      </c>
+      <c r="G3">
+        <v>9</v>
+      </c>
+      <c r="H3">
+        <v>0.00494908168230109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="2"/>
+      <c r="B4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4">
+        <v>99.7208029031754</v>
+      </c>
+      <c r="D4">
+        <v>99.786901473999</v>
+      </c>
+      <c r="E4">
+        <v>99.399</v>
+      </c>
+      <c r="F4">
+        <v>99.523</v>
+      </c>
+      <c r="G4">
+        <v>9</v>
+      </c>
+      <c r="H4">
+        <v>0.00769147184459491</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2"/>
+      <c r="B5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5">
+        <v>99.9429166316986</v>
+      </c>
+      <c r="D5">
+        <v>99.9349296092987</v>
+      </c>
+      <c r="E5">
+        <v>96.682</v>
+      </c>
+      <c r="F5">
+        <v>96.607</v>
+      </c>
+      <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="H5">
+        <v>0.00285471958909265</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="3"/>
+      <c r="B6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6">
+        <v>99.9310523271561</v>
+      </c>
+      <c r="D6">
+        <v>99.9264895915985</v>
+      </c>
+      <c r="E6">
+        <v>98.768</v>
+      </c>
+      <c r="F6">
+        <v>94.659</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>0.00311968611649567</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>98.1462210416794</v>
+      </c>
+      <c r="D7">
+        <v>97.713303565979</v>
+      </c>
+      <c r="E7">
+        <v>94.781</v>
+      </c>
+      <c r="F7">
+        <v>91.553</v>
+      </c>
+      <c r="G7">
+        <v>9</v>
+      </c>
+      <c r="H7">
+        <v>0.0568360097414059</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="2"/>
+      <c r="B8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8">
+        <v>98.9267349243164</v>
+      </c>
+      <c r="D8">
+        <v>98.3689963817596</v>
+      </c>
+      <c r="E8">
+        <v>94.25</v>
+      </c>
+      <c r="F8">
+        <v>91.994</v>
+      </c>
+      <c r="G8">
+        <v>9</v>
+      </c>
+      <c r="H8">
+        <v>0.038512183530411</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="2"/>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9">
+        <v>99.3822634220123</v>
+      </c>
+      <c r="D9">
+        <v>98.8369405269623</v>
+      </c>
+      <c r="E9">
+        <v>95.282</v>
+      </c>
+      <c r="F9">
+        <v>91.026</v>
+      </c>
+      <c r="G9">
+        <v>9</v>
+      </c>
+      <c r="H9">
+        <v>0.0220975706950423</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="2"/>
+      <c r="B10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10">
+        <v>99.5495527982712</v>
+      </c>
+      <c r="D10">
+        <v>99.246883392334</v>
+      </c>
+      <c r="E10">
+        <v>57.661</v>
+      </c>
+      <c r="F10">
+        <v>51.999</v>
+      </c>
+      <c r="G10">
+        <v>9</v>
+      </c>
+      <c r="H10">
+        <v>0.0178216193321673</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="3"/>
+      <c r="B11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11">
+        <v>99.2986142635345</v>
+      </c>
+      <c r="D11">
+        <v>98.9125370979309</v>
+      </c>
+      <c r="E11">
+        <v>87.756</v>
+      </c>
+      <c r="F11">
+        <v>78.982</v>
+      </c>
+      <c r="G11">
+        <v>9</v>
+      </c>
+      <c r="H11">
+        <v>0.0261183291162207</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12">
+        <v>99.6439397335052</v>
+      </c>
+      <c r="D12">
+        <v>99.0898489952087</v>
+      </c>
+      <c r="E12">
+        <v>95.362</v>
+      </c>
+      <c r="F12">
+        <v>88.972</v>
+      </c>
+      <c r="G12">
+        <v>9</v>
+      </c>
+      <c r="H12">
+        <v>0.0121360721817612</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="2"/>
+      <c r="B13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13">
+        <v>99.1720199584961</v>
+      </c>
+      <c r="D13">
+        <v>97.8589236736298</v>
+      </c>
+      <c r="E13">
+        <v>97.951</v>
+      </c>
+      <c r="F13">
+        <v>94.541</v>
+      </c>
+      <c r="G13">
+        <v>9</v>
+      </c>
+      <c r="H13">
+        <v>0.0215692312974728</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="2"/>
+      <c r="B14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14">
+        <v>99.625289440155</v>
+      </c>
+      <c r="D14">
+        <v>99.0249037742615</v>
+      </c>
+      <c r="E14">
+        <v>97.464</v>
+      </c>
+      <c r="F14">
+        <v>92.925</v>
+      </c>
+      <c r="G14">
+        <v>9</v>
+      </c>
+      <c r="H14">
+        <v>0.0112352310280964</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="2"/>
+      <c r="B15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15">
+        <v>99.7417151927948</v>
+      </c>
+      <c r="D15">
+        <v>99.3302583694458</v>
+      </c>
+      <c r="E15">
+        <v>71.189</v>
+      </c>
+      <c r="F15">
+        <v>59.327</v>
+      </c>
+      <c r="G15">
+        <v>9</v>
+      </c>
+      <c r="H15">
+        <v>0.00910041349081323</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="3"/>
+      <c r="B16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16">
+        <v>99.6823728084564</v>
+      </c>
+      <c r="D16">
+        <v>99.176812171936</v>
+      </c>
+      <c r="E16">
+        <v>97.825</v>
+      </c>
+      <c r="F16">
+        <v>94.213</v>
+      </c>
+      <c r="G16">
+        <v>9</v>
+      </c>
+      <c r="H16">
+        <v>0.0106352348676191</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="A12:A16"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E2:F16">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+      <formula>95</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="7"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>99.9502658843994</v>
+      </c>
+      <c r="D2">
+        <v>99.9029278755188</v>
+      </c>
+      <c r="E2">
+        <v>95.589</v>
+      </c>
+      <c r="F2">
+        <v>86.906</v>
+      </c>
+      <c r="G2">
+        <v>9</v>
+      </c>
+      <c r="H2">
+        <v>0.00192192141330031</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="2"/>
+      <c r="B3" s="1">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>99.9536544084549</v>
+      </c>
+      <c r="D3">
+        <v>99.904465675354</v>
+      </c>
+      <c r="E3">
+        <v>96.885</v>
+      </c>
+      <c r="F3">
+        <v>90.514</v>
+      </c>
+      <c r="G3">
+        <v>9</v>
+      </c>
+      <c r="H3">
+        <v>0.00221605385103814</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="2"/>
+      <c r="B4" s="1">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>99.9706149101257</v>
+      </c>
+      <c r="D4">
+        <v>99.9578475952148</v>
+      </c>
+      <c r="E4">
+        <v>96.953</v>
+      </c>
+      <c r="F4">
+        <v>96.49</v>
+      </c>
+      <c r="G4">
+        <v>9</v>
+      </c>
+      <c r="H4">
+        <v>0.00165052113798548</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="3"/>
+      <c r="B5" s="1">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>99.9310523271561</v>
+      </c>
+      <c r="D5">
+        <v>99.9264895915985</v>
+      </c>
+      <c r="E5">
+        <v>98.768</v>
+      </c>
+      <c r="F5">
+        <v>94.659</v>
+      </c>
+      <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="H5">
+        <v>0.00311968611649567</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>99.6541142463684</v>
+      </c>
+      <c r="D6">
+        <v>99.4312644004822</v>
+      </c>
+      <c r="E6">
+        <v>58.65</v>
+      </c>
+      <c r="F6">
+        <v>40.343</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>0.0146023094515462</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="2"/>
+      <c r="B7" s="1">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>99.4416028261185</v>
+      </c>
+      <c r="D7">
+        <v>98.7696290016174</v>
+      </c>
+      <c r="E7">
+        <v>66.892</v>
+      </c>
+      <c r="F7">
+        <v>48.693</v>
+      </c>
+      <c r="G7">
+        <v>9</v>
+      </c>
+      <c r="H7">
+        <v>0.017882351706937</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="2"/>
+      <c r="B8" s="1">
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <v>99.5056629180908</v>
+      </c>
+      <c r="D8">
+        <v>98.8088846206665</v>
+      </c>
+      <c r="E8">
+        <v>75.784</v>
+      </c>
+      <c r="F8">
+        <v>62.785</v>
+      </c>
+      <c r="G8">
+        <v>9</v>
+      </c>
+      <c r="H8">
+        <v>0.018432494642468</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="3"/>
+      <c r="B9" s="1">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>99.2986142635345</v>
+      </c>
+      <c r="D9">
+        <v>98.9125370979309</v>
+      </c>
+      <c r="E9">
+        <v>87.756</v>
+      </c>
+      <c r="F9">
+        <v>78.982</v>
+      </c>
+      <c r="G9">
+        <v>9</v>
+      </c>
+      <c r="H9">
+        <v>0.0261183291162207</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>99.762624502182</v>
+      </c>
+      <c r="D10">
+        <v>99.39204454422</v>
+      </c>
+      <c r="E10">
+        <v>92.176</v>
+      </c>
+      <c r="F10">
+        <v>81.565</v>
+      </c>
+      <c r="G10">
+        <v>9</v>
+      </c>
+      <c r="H10">
+        <v>0.00772715039716797</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="2"/>
+      <c r="B11" s="1">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>99.8507916927338</v>
+      </c>
+      <c r="D11">
+        <v>99.6149659156799</v>
+      </c>
+      <c r="E11">
+        <v>95.824</v>
+      </c>
+      <c r="F11">
+        <v>89.244</v>
+      </c>
+      <c r="G11">
+        <v>9</v>
+      </c>
+      <c r="H11">
+        <v>0.00600876197682538</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="2"/>
+      <c r="B12" s="1">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>99.8688817024231</v>
+      </c>
+      <c r="D12">
+        <v>99.6618032455444</v>
+      </c>
+      <c r="E12">
+        <v>96.33</v>
+      </c>
+      <c r="F12">
+        <v>90.439</v>
+      </c>
+      <c r="G12">
+        <v>9</v>
+      </c>
+      <c r="H12">
+        <v>0.00556477332719972</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="3"/>
+      <c r="B13" s="1">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>99.6823728084564</v>
+      </c>
+      <c r="D13">
+        <v>99.176812171936</v>
+      </c>
+      <c r="E13">
+        <v>97.825</v>
+      </c>
+      <c r="F13">
+        <v>94.213</v>
+      </c>
+      <c r="G13">
+        <v>9</v>
+      </c>
+      <c r="H13">
+        <v>0.0106352348676191</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E2:F13">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+      <formula>95</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="3"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>9</v>
+      </c>
+      <c r="D2">
+        <v>0.00192192141330031</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2"/>
+      <c r="B3" s="1">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>9</v>
+      </c>
+      <c r="D3">
+        <v>0.00221605385103814</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2"/>
+      <c r="B4" s="1">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>9</v>
+      </c>
+      <c r="D4">
+        <v>0.00165052113798548</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="3"/>
+      <c r="B5" s="1">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>0.00311968611649567</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>9</v>
+      </c>
+      <c r="D6">
+        <v>0.0146023094515462</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2"/>
+      <c r="B7" s="1">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>0.017882351706937</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="2"/>
+      <c r="B8" s="1">
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <v>9</v>
+      </c>
+      <c r="D8">
+        <v>0.018432494642468</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="3"/>
+      <c r="B9" s="1">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>9</v>
+      </c>
+      <c r="D9">
+        <v>0.0261183291162207</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>9</v>
+      </c>
+      <c r="D10">
+        <v>0.00772715039716797</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2"/>
+      <c r="B11" s="1">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>9</v>
+      </c>
+      <c r="D11">
+        <v>0.00600876197682538</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2"/>
+      <c r="B12" s="1">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>9</v>
+      </c>
+      <c r="D12">
+        <v>0.00556477332719972</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="3"/>
+      <c r="B13" s="1">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>9</v>
+      </c>
+      <c r="D13">
+        <v>0.0106352348676191</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="3"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2">
+        <v>9</v>
+      </c>
+      <c r="D2">
+        <v>0.00363413141153578</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3">
+        <v>9</v>
+      </c>
+      <c r="D3">
+        <v>0.00494908168230109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4">
+        <v>9</v>
+      </c>
+      <c r="D4">
+        <v>0.00769147184459491</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>0.00285471958909265</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6">
+        <v>9</v>
+      </c>
+      <c r="D6">
+        <v>0.00311968611649567</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>0.0568360097414059</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8">
+        <v>9</v>
+      </c>
+      <c r="D8">
+        <v>0.038512183530411</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9">
+        <v>9</v>
+      </c>
+      <c r="D9">
+        <v>0.0220975706950423</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10">
+        <v>9</v>
+      </c>
+      <c r="D10">
+        <v>0.0178216193321673</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11">
+        <v>9</v>
+      </c>
+      <c r="D11">
+        <v>0.0261183291162207</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12">
+        <v>9</v>
+      </c>
+      <c r="D12">
+        <v>0.0121360721817612</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13">
+        <v>9</v>
+      </c>
+      <c r="D13">
+        <v>0.0215692312974728</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14">
+        <v>9</v>
+      </c>
+      <c r="D14">
+        <v>0.0112352310280964</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15">
+        <v>9</v>
+      </c>
+      <c r="D15">
+        <v>0.00910041349081323</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16">
+        <v>9</v>
+      </c>
+      <c r="D16">
+        <v>0.0106352348676191</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="A12:A16"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/results/results.xlsx
+++ b/results/results.xlsx
@@ -4,11 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="15540" activeTab="1"/>
+    <workbookView windowWidth="30720" windowHeight="15540" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="train2" sheetId="1" r:id="rId1"/>
     <sheet name="append" sheetId="2" r:id="rId2"/>
+    <sheet name="test_domain" sheetId="3" r:id="rId3"/>
+    <sheet name="origin_domain_num" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="17">
   <si>
     <t>HyperParameters</t>
   </si>
@@ -57,13 +59,28 @@
     <t>kernel_size</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>out_channels</t>
   </si>
   <si>
     <t>stride</t>
+  </si>
+  <si>
+    <t>test_domain</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>192</t>
+  </si>
+  <si>
+    <t>224</t>
+  </si>
+  <si>
+    <t>299</t>
+  </si>
+  <si>
+    <t>331</t>
   </si>
 </sst>
 </file>
@@ -816,7 +833,14 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.4"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1235,9 +1259,6 @@
       <c r="G4">
         <v>9</v>
       </c>
-      <c r="H4" t="s">
-        <v>9</v>
-      </c>
       <c r="K4" s="8"/>
       <c r="L4" s="8"/>
       <c r="M4" s="8"/>
@@ -1273,7 +1294,7 @@
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
@@ -1321,9 +1342,6 @@
       <c r="G7">
         <v>18</v>
       </c>
-      <c r="H7" t="s">
-        <v>9</v>
-      </c>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
@@ -1348,9 +1366,6 @@
       </c>
       <c r="G8">
         <v>15</v>
-      </c>
-      <c r="H8" t="s">
-        <v>9</v>
       </c>
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
@@ -1388,7 +1403,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
@@ -1650,7 +1665,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
@@ -1674,7 +1689,7 @@
         <v>-1.98239307803226</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:7">
       <c r="A7" s="2"/>
       <c r="B7" s="1">
         <v>2</v>
@@ -1694,11 +1709,8 @@
       <c r="G7">
         <v>18</v>
       </c>
-      <c r="H7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="2"/>
       <c r="B8" s="1">
         <v>3</v>
@@ -1717,9 +1729,6 @@
       </c>
       <c r="G8">
         <v>15</v>
-      </c>
-      <c r="H8" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1748,7 +1757,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
@@ -1856,4 +1865,760 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="7"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2">
+        <v>99.9920904636383</v>
+      </c>
+      <c r="D2">
+        <v>99.9864816665649</v>
+      </c>
+      <c r="E2">
+        <v>99.977</v>
+      </c>
+      <c r="F2">
+        <v>99.97</v>
+      </c>
+      <c r="G2">
+        <v>9</v>
+      </c>
+      <c r="H2">
+        <v>-4.99774523981223</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="2"/>
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3">
+        <v>99.9858677387238</v>
+      </c>
+      <c r="D3">
+        <v>99.9896049499512</v>
+      </c>
+      <c r="E3">
+        <v>99.989</v>
+      </c>
+      <c r="F3">
+        <v>99.989</v>
+      </c>
+      <c r="G3">
+        <v>9</v>
+      </c>
+      <c r="H3">
+        <v>-4.99714172395001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="2"/>
+      <c r="B4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4">
+        <v>99.988129734993</v>
+      </c>
+      <c r="D4">
+        <v>99.9912738800049</v>
+      </c>
+      <c r="E4">
+        <v>99.886</v>
+      </c>
+      <c r="F4">
+        <v>99.907</v>
+      </c>
+      <c r="G4">
+        <v>9</v>
+      </c>
+      <c r="H4">
+        <v>-4.99696022241941</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2"/>
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>99.9875664710999</v>
+      </c>
+      <c r="D5">
+        <v>99.983161687851</v>
+      </c>
+      <c r="E5">
+        <v>99.077</v>
+      </c>
+      <c r="F5">
+        <v>99.267</v>
+      </c>
+      <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="H5">
+        <v>-4.99809275376823</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="3"/>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6">
+        <v>99.9819159507751</v>
+      </c>
+      <c r="D6">
+        <v>99.9867081642151</v>
+      </c>
+      <c r="E6">
+        <v>99.904</v>
+      </c>
+      <c r="F6">
+        <v>99.924</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>-4.99561883191311</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>99.8926162719727</v>
+      </c>
+      <c r="D7">
+        <v>99.821412563324</v>
+      </c>
+      <c r="E7">
+        <v>97.568</v>
+      </c>
+      <c r="F7">
+        <v>96.723</v>
+      </c>
+      <c r="G7">
+        <v>9</v>
+      </c>
+      <c r="H7">
+        <v>-1.97668515187799</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="2"/>
+      <c r="B8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>99.8909175395966</v>
+      </c>
+      <c r="D8">
+        <v>99.7759938240051</v>
+      </c>
+      <c r="E8">
+        <v>99.237</v>
+      </c>
+      <c r="F8">
+        <v>98.489</v>
+      </c>
+      <c r="G8">
+        <v>9</v>
+      </c>
+      <c r="H8">
+        <v>-1.97836087901611</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="2"/>
+      <c r="B9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>99.912965297699</v>
+      </c>
+      <c r="D9">
+        <v>99.8649716377258</v>
+      </c>
+      <c r="E9">
+        <v>98.724</v>
+      </c>
+      <c r="F9">
+        <v>98.492</v>
+      </c>
+      <c r="G9">
+        <v>9</v>
+      </c>
+      <c r="H9">
+        <v>-1.9819516396919</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="2"/>
+      <c r="B10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>99.9186158180237</v>
+      </c>
+      <c r="D10">
+        <v>99.8486459255219</v>
+      </c>
+      <c r="E10">
+        <v>87.486</v>
+      </c>
+      <c r="F10">
+        <v>86.79</v>
+      </c>
+      <c r="G10">
+        <v>9</v>
+      </c>
+      <c r="H10">
+        <v>-1.98223552976237</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="3"/>
+      <c r="B11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>99.8943150043488</v>
+      </c>
+      <c r="D11">
+        <v>99.8338580131531</v>
+      </c>
+      <c r="E11">
+        <v>99.615</v>
+      </c>
+      <c r="F11">
+        <v>99.505</v>
+      </c>
+      <c r="G11">
+        <v>9</v>
+      </c>
+      <c r="H11">
+        <v>-1.97654703623647</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12">
+        <v>99.9559164047241</v>
+      </c>
+      <c r="D12">
+        <v>99.8866438865662</v>
+      </c>
+      <c r="E12">
+        <v>99.378</v>
+      </c>
+      <c r="F12">
+        <v>98.428</v>
+      </c>
+      <c r="G12">
+        <v>9</v>
+      </c>
+      <c r="H12">
+        <v>-9.9890995266984</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="2"/>
+      <c r="B13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13">
+        <v>99.9197423458099</v>
+      </c>
+      <c r="D13">
+        <v>99.7939705848694</v>
+      </c>
+      <c r="E13">
+        <v>99.832</v>
+      </c>
+      <c r="F13">
+        <v>99.577</v>
+      </c>
+      <c r="G13">
+        <v>9</v>
+      </c>
+      <c r="H13">
+        <v>-9.98527306813911</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="2"/>
+      <c r="B14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14">
+        <v>99.9107003211975</v>
+      </c>
+      <c r="D14">
+        <v>99.7699856758118</v>
+      </c>
+      <c r="E14">
+        <v>99.287</v>
+      </c>
+      <c r="F14">
+        <v>98.143</v>
+      </c>
+      <c r="G14">
+        <v>9</v>
+      </c>
+      <c r="H14">
+        <v>-9.982670648841</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="2"/>
+      <c r="B15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15">
+        <v>99.9197423458099</v>
+      </c>
+      <c r="D15">
+        <v>99.7935831546783</v>
+      </c>
+      <c r="E15">
+        <v>93.002</v>
+      </c>
+      <c r="F15">
+        <v>85.313</v>
+      </c>
+      <c r="G15">
+        <v>9</v>
+      </c>
+      <c r="H15">
+        <v>-9.98458944087604</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="3"/>
+      <c r="B16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16">
+        <v>99.945741891861</v>
+      </c>
+      <c r="D16">
+        <v>99.8603463172913</v>
+      </c>
+      <c r="E16">
+        <v>99.931</v>
+      </c>
+      <c r="F16">
+        <v>99.824</v>
+      </c>
+      <c r="G16">
+        <v>9</v>
+      </c>
+      <c r="H16">
+        <v>-9.9883948820532</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="A12:A16"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E2:F16">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+      <formula>95</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="7"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>99.9864399433136</v>
+      </c>
+      <c r="D2">
+        <v>99.9900281429291</v>
+      </c>
+      <c r="E2">
+        <v>95.181</v>
+      </c>
+      <c r="F2">
+        <v>96.518</v>
+      </c>
+      <c r="G2">
+        <v>14</v>
+      </c>
+      <c r="H2">
+        <v>-4.99772138127013</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="2"/>
+      <c r="B3" s="1">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>99.9875664710999</v>
+      </c>
+      <c r="D3">
+        <v>99.9908626079559</v>
+      </c>
+      <c r="E3">
+        <v>98.503</v>
+      </c>
+      <c r="F3">
+        <v>98.896</v>
+      </c>
+      <c r="G3">
+        <v>14</v>
+      </c>
+      <c r="H3">
+        <v>-4.99774081376247</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="2"/>
+      <c r="B4" s="1">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>99.9902039766312</v>
+      </c>
+      <c r="D4">
+        <v>99.9927997589111</v>
+      </c>
+      <c r="E4">
+        <v>98.631</v>
+      </c>
+      <c r="F4">
+        <v>98.994</v>
+      </c>
+      <c r="G4">
+        <v>14</v>
+      </c>
+      <c r="H4">
+        <v>-4.99805709504116</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="3"/>
+      <c r="B5" s="1">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>99.9819159507751</v>
+      </c>
+      <c r="D5">
+        <v>99.9867081642151</v>
+      </c>
+      <c r="E5">
+        <v>99.904</v>
+      </c>
+      <c r="F5">
+        <v>99.924</v>
+      </c>
+      <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="H5">
+        <v>-4.99561883191311</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>99.905052781105</v>
+      </c>
+      <c r="D6">
+        <v>99.8232543468475</v>
+      </c>
+      <c r="E6">
+        <v>88.501</v>
+      </c>
+      <c r="F6">
+        <v>83.253</v>
+      </c>
+      <c r="G6">
+        <v>14</v>
+      </c>
+      <c r="H6">
+        <v>-1.99191459134824</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="2"/>
+      <c r="B7" s="1">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>99.9299168586731</v>
+      </c>
+      <c r="D7">
+        <v>99.8602092266083</v>
+      </c>
+      <c r="E7">
+        <v>91.923</v>
+      </c>
+      <c r="F7">
+        <v>86.091</v>
+      </c>
+      <c r="G7">
+        <v>14</v>
+      </c>
+      <c r="H7">
+        <v>-1.99381102716303</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="2"/>
+      <c r="B8" s="1">
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <v>99.9253928661346</v>
+      </c>
+      <c r="D8">
+        <v>99.8613595962524</v>
+      </c>
+      <c r="E8">
+        <v>95.9</v>
+      </c>
+      <c r="F8">
+        <v>92.122</v>
+      </c>
+      <c r="G8">
+        <v>14</v>
+      </c>
+      <c r="H8">
+        <v>-1.99353704146732</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="3"/>
+      <c r="B9" s="1">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>99.8943150043488</v>
+      </c>
+      <c r="D9">
+        <v>99.8338580131531</v>
+      </c>
+      <c r="E9">
+        <v>99.615</v>
+      </c>
+      <c r="F9">
+        <v>99.505</v>
+      </c>
+      <c r="G9">
+        <v>9</v>
+      </c>
+      <c r="H9">
+        <v>-1.97654703623647</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>99.9186158180237</v>
+      </c>
+      <c r="D10">
+        <v>99.7906684875488</v>
+      </c>
+      <c r="E10">
+        <v>97.564</v>
+      </c>
+      <c r="F10">
+        <v>93.345</v>
+      </c>
+      <c r="G10">
+        <v>14</v>
+      </c>
+      <c r="H10">
+        <v>-9.98524733085853</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="2"/>
+      <c r="B11" s="1">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>99.9344408512115</v>
+      </c>
+      <c r="D11">
+        <v>99.8314917087555</v>
+      </c>
+      <c r="E11">
+        <v>98.433</v>
+      </c>
+      <c r="F11">
+        <v>95.8</v>
+      </c>
+      <c r="G11">
+        <v>14</v>
+      </c>
+      <c r="H11">
+        <v>-9.98823816790057</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="2"/>
+      <c r="B12" s="1">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>99.9540328979492</v>
+      </c>
+      <c r="D12">
+        <v>99.881899356842</v>
+      </c>
+      <c r="E12">
+        <v>98.547</v>
+      </c>
+      <c r="F12">
+        <v>96.119</v>
+      </c>
+      <c r="G12">
+        <v>14</v>
+      </c>
+      <c r="H12">
+        <v>-9.99127202507615</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="3"/>
+      <c r="B13" s="1">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>99.945741891861</v>
+      </c>
+      <c r="D13">
+        <v>99.8603463172913</v>
+      </c>
+      <c r="E13">
+        <v>99.931</v>
+      </c>
+      <c r="F13">
+        <v>99.824</v>
+      </c>
+      <c r="G13">
+        <v>9</v>
+      </c>
+      <c r="H13">
+        <v>-9.9883948820532</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E2:F13">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+      <formula>95</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/results/results.xlsx
+++ b/results/results.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="30720" windowHeight="15540" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="30720" windowHeight="15540" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="train2" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="append" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="test_domain" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="origin_domain_num" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="test_domain_old" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="origin_domain_num_old" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="origin_domain_num_regression" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="test_domain_regression" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -18,10 +18,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.000_ "/>
-  </numFmts>
-  <fonts count="25">
+  <numFmts count="0"/>
+  <fonts count="22">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -33,27 +31,6 @@
       <name val="宋体"/>
       <charset val="134"/>
       <b val="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
@@ -598,157 +575,144 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -805,22 +769,6 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -1181,12 +1129,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15.6"/>
-  <cols>
-    <col width="12.1666666666667" customWidth="1" min="3" max="4"/>
-    <col width="10.0555555555556" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -1196,7 +1140,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Origin_domain_nums</t>
+          <t>test_domain</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -1221,19 +1165,14 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>epoch</t>
+          <t>TEST_R</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>loss_value</t>
-        </is>
-      </c>
-      <c r="K1" s="7" t="n"/>
-      <c r="L1" s="7" t="n"/>
-      <c r="M1" s="7" t="n"/>
-      <c r="N1" s="7" t="n"/>
-      <c r="O1" s="1" t="n"/>
+          <t>TEST_P</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -1241,350 +1180,408 @@
           <t>kernel_size</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
-        <v>1</v>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>99.9593049287796</v>
+        <v>99.99209046363831</v>
       </c>
       <c r="D2" t="n">
-        <v>99.93973970413209</v>
+        <v>99.9864816665649</v>
       </c>
       <c r="E2" t="n">
-        <v>98.398</v>
+        <v>99.977</v>
       </c>
       <c r="F2" t="n">
-        <v>98.792</v>
+        <v>99.97</v>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>99.973</v>
       </c>
       <c r="H2" t="n">
-        <v>-4.99563609795763</v>
-      </c>
-      <c r="K2" s="8" t="n"/>
-      <c r="L2" s="8" t="n"/>
-      <c r="M2" s="8" t="n"/>
-      <c r="N2" s="8" t="n"/>
+        <v>99.968</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
-      <c r="B3" s="1" t="n">
-        <v>2</v>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>99.7955650091171</v>
+        <v>99.9858677387238</v>
       </c>
       <c r="D3" t="n">
-        <v>99.6684908866882</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>64.816</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>29.186</v>
+        <v>99.9896049499512</v>
+      </c>
+      <c r="E3" t="n">
+        <v>99.989</v>
+      </c>
+      <c r="F3" t="n">
+        <v>99.989</v>
       </c>
       <c r="G3" t="n">
-        <v>17</v>
+        <v>99.992</v>
       </c>
       <c r="H3" t="n">
-        <v>-4.9559298735191</v>
-      </c>
-      <c r="K3" s="8" t="n"/>
-      <c r="L3" s="8" t="n"/>
-      <c r="M3" s="8" t="n"/>
-      <c r="N3" s="8" t="n"/>
+        <v>99.985</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
-      <c r="B4" s="1" t="n">
-        <v>3</v>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>99.9587416648865</v>
+        <v>99.988129734993</v>
       </c>
       <c r="D4" t="n">
-        <v>99.9495029449463</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>63.254</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>26.131</v>
+        <v>99.9912738800049</v>
+      </c>
+      <c r="E4" t="n">
+        <v>99.886</v>
+      </c>
+      <c r="F4" t="n">
+        <v>99.907</v>
       </c>
       <c r="G4" t="n">
-        <v>9</v>
-      </c>
-      <c r="K4" s="8" t="n"/>
-      <c r="L4" s="8" t="n"/>
-      <c r="M4" s="8" t="n"/>
-      <c r="N4" s="8" t="n"/>
+        <v>99.925</v>
+      </c>
+      <c r="H4" t="n">
+        <v>99.89</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n"/>
-      <c r="B5" s="1" t="n">
-        <v>4</v>
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>99.99095499515531</v>
+        <v>99.9875664710999</v>
       </c>
       <c r="D5" t="n">
-        <v>99.99334812164309</v>
+        <v>99.98316168785099</v>
       </c>
       <c r="E5" t="n">
-        <v>98.173</v>
+        <v>99.077</v>
       </c>
       <c r="F5" t="n">
-        <v>98.617</v>
+        <v>99.267</v>
       </c>
       <c r="G5" t="n">
-        <v>15</v>
+        <v>99.21599999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.99875173541163</v>
-      </c>
-      <c r="K5" s="8" t="n"/>
-      <c r="L5" s="8" t="n"/>
-      <c r="M5" s="8" t="n"/>
-      <c r="N5" s="8" t="n"/>
+        <v>99.321</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="3" t="n"/>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>99.9819159507751</v>
+      </c>
+      <c r="D6" t="n">
+        <v>99.9867081642151</v>
+      </c>
+      <c r="E6" t="n">
+        <v>99.904</v>
+      </c>
+      <c r="F6" t="n">
+        <v>99.92400000000001</v>
+      </c>
+      <c r="G6" t="n">
+        <v>99.94199999999999</v>
+      </c>
+      <c r="H6" t="n">
+        <v>99.90600000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>out_channels</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>99.84175264835361</v>
-      </c>
-      <c r="D6" t="n">
-        <v>99.71640110015871</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>65.471</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>45.811</v>
-      </c>
-      <c r="G6" t="n">
-        <v>21</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-1.98239307803226</v>
-      </c>
-      <c r="K6" s="8" t="n"/>
-      <c r="L6" s="8" t="n"/>
-      <c r="M6" s="8" t="n"/>
-      <c r="N6" s="8" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="1" t="n">
-        <v>2</v>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
       </c>
       <c r="C7" t="n">
-        <v>99.8994380235672</v>
+        <v>99.8926162719727</v>
       </c>
       <c r="D7" t="n">
-        <v>99.8618245124817</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>57.042</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>46.206</v>
+        <v>99.821412563324</v>
+      </c>
+      <c r="E7" t="n">
+        <v>97.568</v>
+      </c>
+      <c r="F7" t="n">
+        <v>96.723</v>
       </c>
       <c r="G7" t="n">
-        <v>18</v>
-      </c>
-      <c r="K7" s="8" t="n"/>
-      <c r="L7" s="8" t="n"/>
-      <c r="M7" s="8" t="n"/>
-      <c r="N7" s="8" t="n"/>
+        <v>98.40900000000001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>95.276</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
-      <c r="B8" s="1" t="n">
-        <v>3</v>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
       </c>
       <c r="C8" t="n">
-        <v>99.9123305082321</v>
+        <v>99.8909175395966</v>
       </c>
       <c r="D8" t="n">
-        <v>99.8632311820984</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>85.09999999999999</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>69.209</v>
+        <v>99.7759938240051</v>
+      </c>
+      <c r="E8" t="n">
+        <v>99.23699999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>98.489</v>
       </c>
       <c r="G8" t="n">
-        <v>15</v>
-      </c>
-      <c r="K8" s="8" t="n"/>
-      <c r="L8" s="8" t="n"/>
-      <c r="M8" s="8" t="n"/>
-      <c r="N8" s="8" t="n"/>
+        <v>99.477</v>
+      </c>
+      <c r="H8" t="n">
+        <v>97.59999999999999</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n"/>
-      <c r="B9" s="1" t="n">
-        <v>4</v>
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
       </c>
       <c r="C9" t="n">
-        <v>99.8711407184601</v>
+        <v>99.912965297699</v>
       </c>
       <c r="D9" t="n">
-        <v>99.7591853141785</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>58.145</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>42.666</v>
+        <v>99.8649716377258</v>
+      </c>
+      <c r="E9" t="n">
+        <v>98.724</v>
+      </c>
+      <c r="F9" t="n">
+        <v>98.492</v>
       </c>
       <c r="G9" t="n">
-        <v>18</v>
+        <v>97.761</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.98392446192703</v>
-      </c>
-      <c r="I9" s="9" t="n"/>
-      <c r="K9" s="8" t="n"/>
-      <c r="L9" s="8" t="n"/>
-      <c r="M9" s="8" t="n"/>
-      <c r="N9" s="8" t="n"/>
+        <v>99.26600000000001</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>99.9186158180237</v>
+      </c>
+      <c r="D10" t="n">
+        <v>99.84864592552189</v>
+      </c>
+      <c r="E10" t="n">
+        <v>87.486</v>
+      </c>
+      <c r="F10" t="n">
+        <v>86.79000000000001</v>
+      </c>
+      <c r="G10" t="n">
+        <v>86.873</v>
+      </c>
+      <c r="H10" t="n">
+        <v>87.85599999999999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>99.8943150043488</v>
+      </c>
+      <c r="D11" t="n">
+        <v>99.8338580131531</v>
+      </c>
+      <c r="E11" t="n">
+        <v>99.61499999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>99.505</v>
+      </c>
+      <c r="G11" t="n">
+        <v>99.491</v>
+      </c>
+      <c r="H11" t="n">
+        <v>99.523</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>stride</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="n">
-        <v>99.941223859787</v>
-      </c>
-      <c r="D10" t="n">
-        <v>99.84889626502989</v>
-      </c>
-      <c r="E10" t="n">
-        <v>97.818</v>
-      </c>
-      <c r="F10" t="n">
-        <v>94.09999999999999</v>
-      </c>
-      <c r="G10" t="n">
-        <v>20</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-9.9886245562162</v>
-      </c>
-      <c r="I10" s="9" t="n"/>
-      <c r="K10" s="8" t="n"/>
-      <c r="L10" s="8" t="n"/>
-      <c r="M10" s="8" t="n"/>
-      <c r="N10" s="8" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n"/>
-      <c r="B11" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" t="n">
-        <v>99.93895888328549</v>
-      </c>
-      <c r="D11" t="n">
-        <v>99.8430132865906</v>
-      </c>
-      <c r="E11" t="n">
-        <v>97.578</v>
-      </c>
-      <c r="F11" t="n">
-        <v>93.45399999999999</v>
-      </c>
-      <c r="G11" t="n">
-        <v>18</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-9.988607092399819</v>
-      </c>
-      <c r="I11" s="9" t="n"/>
-      <c r="K11" s="8" t="n"/>
-      <c r="L11" s="8" t="n"/>
-      <c r="M11" s="8" t="n"/>
-      <c r="N11" s="8" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n"/>
-      <c r="B12" s="1" t="n">
-        <v>3</v>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
       </c>
       <c r="C12" t="n">
-        <v>99.9547839164734</v>
+        <v>99.95591640472411</v>
       </c>
       <c r="D12" t="n">
-        <v>99.88374710083011</v>
+        <v>99.8866438865662</v>
       </c>
       <c r="E12" t="n">
-        <v>97.327</v>
+        <v>99.378</v>
       </c>
       <c r="F12" t="n">
-        <v>92.614</v>
+        <v>98.428</v>
       </c>
       <c r="G12" t="n">
-        <v>17</v>
+        <v>98.595</v>
       </c>
       <c r="H12" t="n">
-        <v>-9.99106574471975</v>
-      </c>
-      <c r="I12" s="9" t="n"/>
-      <c r="K12" s="8" t="n"/>
-      <c r="L12" s="8" t="n"/>
-      <c r="M12" s="8" t="n"/>
-      <c r="N12" s="8" t="n"/>
+        <v>98.26300000000001</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n"/>
-      <c r="B13" s="1" t="n">
-        <v>4</v>
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
       </c>
       <c r="C13" t="n">
-        <v>99.93669986724851</v>
+        <v>99.91974234580989</v>
       </c>
       <c r="D13" t="n">
-        <v>99.8372435569763</v>
+        <v>99.7939705848694</v>
       </c>
       <c r="E13" t="n">
-        <v>97.33199999999999</v>
+        <v>99.83199999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>92.608</v>
+        <v>99.577</v>
       </c>
       <c r="G13" t="n">
-        <v>13</v>
+        <v>99.83199999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-9.987175696157999</v>
+        <v>99.325</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>99.9107003211975</v>
+      </c>
+      <c r="D14" t="n">
+        <v>99.7699856758118</v>
+      </c>
+      <c r="E14" t="n">
+        <v>99.28700000000001</v>
+      </c>
+      <c r="F14" t="n">
+        <v>98.143</v>
+      </c>
+      <c r="G14" t="n">
+        <v>96.91</v>
+      </c>
+      <c r="H14" t="n">
+        <v>99.465</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>99.91974234580989</v>
+      </c>
+      <c r="D15" t="n">
+        <v>99.7935831546783</v>
+      </c>
+      <c r="E15" t="n">
+        <v>93.002</v>
+      </c>
+      <c r="F15" t="n">
+        <v>85.313</v>
+      </c>
+      <c r="G15" t="n">
+        <v>93.05800000000001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>80.71299999999999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n"/>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>99.945741891861</v>
+      </c>
+      <c r="D16" t="n">
+        <v>99.8603463172913</v>
+      </c>
+      <c r="E16" t="n">
+        <v>99.931</v>
+      </c>
+      <c r="F16" t="n">
+        <v>99.824</v>
+      </c>
+      <c r="G16" t="n">
+        <v>99.745</v>
+      </c>
+      <c r="H16" t="n">
+        <v>99.90300000000001</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="A2:A6"/>
   </mergeCells>
-  <conditionalFormatting sqref="K2:N13">
-    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
-      <formula>95</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1595,7 +1592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15.6"/>
   <sheetData>
     <row r="1">
@@ -1631,12 +1628,12 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>epoch</t>
+          <t>TEST_R</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>loss_value</t>
+          <t>TEST_P</t>
         </is>
       </c>
     </row>
@@ -1650,22 +1647,22 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>99.9593049287796</v>
+        <v>99.9864399433136</v>
       </c>
       <c r="D2" t="n">
-        <v>99.93973970413209</v>
+        <v>99.99002814292911</v>
       </c>
       <c r="E2" t="n">
-        <v>98.398</v>
+        <v>95.181</v>
       </c>
       <c r="F2" t="n">
-        <v>98.792</v>
+        <v>96.518</v>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>96.956</v>
       </c>
       <c r="H2" t="n">
-        <v>-4.99563609795763</v>
+        <v>96.166</v>
       </c>
     </row>
     <row r="3">
@@ -1674,25 +1671,22 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>99.7955650091171</v>
+        <v>99.9875664710999</v>
       </c>
       <c r="D3" t="n">
-        <v>99.6684908866882</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>96.73</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>97.599</v>
+        <v>99.9908626079559</v>
+      </c>
+      <c r="E3" t="n">
+        <v>98.503</v>
+      </c>
+      <c r="F3" t="n">
+        <v>98.896</v>
       </c>
       <c r="G3" t="n">
-        <v>17</v>
+        <v>98.688</v>
       </c>
       <c r="H3" t="n">
-        <v>-4.9559298735191</v>
-      </c>
-      <c r="I3" t="n">
-        <v>10</v>
+        <v>99.125</v>
       </c>
     </row>
     <row r="4">
@@ -1701,22 +1695,22 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>99.9587416648865</v>
+        <v>99.99020397663119</v>
       </c>
       <c r="D4" t="n">
-        <v>99.9495029449463</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>96.70399999999999</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>97.587</v>
+        <v>99.9927997589111</v>
+      </c>
+      <c r="E4" t="n">
+        <v>98.631</v>
+      </c>
+      <c r="F4" t="n">
+        <v>98.994</v>
       </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>98.80500000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>-4.996</v>
+        <v>99.199</v>
       </c>
     </row>
     <row r="5">
@@ -1725,22 +1719,22 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>99.99095499515531</v>
+        <v>99.9819159507751</v>
       </c>
       <c r="D5" t="n">
-        <v>99.99334812164309</v>
+        <v>99.9867081642151</v>
       </c>
       <c r="E5" t="n">
-        <v>98.173</v>
+        <v>99.904</v>
       </c>
       <c r="F5" t="n">
-        <v>98.617</v>
+        <v>99.92400000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>15</v>
+        <v>99.94199999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.99875173541163</v>
+        <v>99.90600000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1753,22 +1747,22 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>99.84175264835361</v>
+        <v>99.905052781105</v>
       </c>
       <c r="D6" t="n">
-        <v>99.71640110015871</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>83.979</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>74.04900000000001</v>
+        <v>99.82325434684751</v>
+      </c>
+      <c r="E6" t="n">
+        <v>88.501</v>
+      </c>
+      <c r="F6" t="n">
+        <v>83.253</v>
       </c>
       <c r="G6" t="n">
-        <v>21</v>
+        <v>81.164</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.98239307803226</v>
+        <v>88.371</v>
       </c>
     </row>
     <row r="7">
@@ -1777,19 +1771,22 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>99.8994380235672</v>
+        <v>99.9299168586731</v>
       </c>
       <c r="D7" t="n">
-        <v>99.8618245124817</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>87.614</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>83.947</v>
+        <v>99.8602092266083</v>
+      </c>
+      <c r="E7" t="n">
+        <v>91.923</v>
+      </c>
+      <c r="F7" t="n">
+        <v>86.09099999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>18</v>
+        <v>85.104</v>
+      </c>
+      <c r="H7" t="n">
+        <v>89.297</v>
       </c>
     </row>
     <row r="8">
@@ -1798,19 +1795,22 @@
         <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>99.9123305082321</v>
+        <v>99.9253928661346</v>
       </c>
       <c r="D8" t="n">
-        <v>99.8632311820984</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>83.51000000000001</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>72.327</v>
+        <v>99.8613595962524</v>
+      </c>
+      <c r="E8" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>92.122</v>
       </c>
       <c r="G8" t="n">
-        <v>15</v>
+        <v>91.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>94.33799999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1819,22 +1819,22 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>99.8711407184601</v>
+        <v>99.8943150043488</v>
       </c>
       <c r="D9" t="n">
-        <v>99.7591853141785</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>85.15300000000001</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>79.717</v>
+        <v>99.8338580131531</v>
+      </c>
+      <c r="E9" t="n">
+        <v>99.61499999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>99.505</v>
       </c>
       <c r="G9" t="n">
-        <v>18</v>
+        <v>99.491</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.98392446192703</v>
+        <v>99.523</v>
       </c>
     </row>
     <row r="10">
@@ -1847,22 +1847,22 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>99.941223859787</v>
+        <v>99.9186158180237</v>
       </c>
       <c r="D10" t="n">
-        <v>99.84889626502989</v>
+        <v>99.7906684875488</v>
       </c>
       <c r="E10" t="n">
-        <v>97.818</v>
+        <v>97.56399999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>94.09999999999999</v>
+        <v>93.345</v>
       </c>
       <c r="G10" t="n">
-        <v>20</v>
+        <v>90.292</v>
       </c>
       <c r="H10" t="n">
-        <v>-9.9886245562162</v>
+        <v>97.09</v>
       </c>
     </row>
     <row r="11">
@@ -1871,25 +1871,22 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>99.93895888328549</v>
+        <v>99.93444085121151</v>
       </c>
       <c r="D11" t="n">
-        <v>99.8430132865906</v>
+        <v>99.83149170875549</v>
       </c>
       <c r="E11" t="n">
-        <v>97.578</v>
+        <v>98.43300000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>93.45399999999999</v>
+        <v>95.8</v>
       </c>
       <c r="G11" t="n">
-        <v>18</v>
+        <v>93.373</v>
       </c>
       <c r="H11" t="n">
-        <v>-9.988607092399819</v>
-      </c>
-      <c r="I11" t="n">
-        <v>10</v>
+        <v>98.619</v>
       </c>
     </row>
     <row r="12">
@@ -1898,22 +1895,22 @@
         <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>99.9547839164734</v>
+        <v>99.9540328979492</v>
       </c>
       <c r="D12" t="n">
-        <v>99.88374710083011</v>
+        <v>99.881899356842</v>
       </c>
       <c r="E12" t="n">
-        <v>97.327</v>
+        <v>98.547</v>
       </c>
       <c r="F12" t="n">
-        <v>92.614</v>
+        <v>96.119</v>
       </c>
       <c r="G12" t="n">
-        <v>17</v>
+        <v>93.815</v>
       </c>
       <c r="H12" t="n">
-        <v>-9.99106574471975</v>
+        <v>98.771</v>
       </c>
     </row>
     <row r="13">
@@ -1922,22 +1919,22 @@
         <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>99.93669986724851</v>
+        <v>99.945741891861</v>
       </c>
       <c r="D13" t="n">
-        <v>99.8372435569763</v>
+        <v>99.8603463172913</v>
       </c>
       <c r="E13" t="n">
-        <v>97.33199999999999</v>
+        <v>99.931</v>
       </c>
       <c r="F13" t="n">
-        <v>92.608</v>
+        <v>99.824</v>
       </c>
       <c r="G13" t="n">
-        <v>13</v>
+        <v>99.745</v>
       </c>
       <c r="H13" t="n">
-        <v>-9.987175696157999</v>
+        <v>99.90300000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1956,458 +1953,356 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>HyperParameters</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
-        <is>
-          <t>test_domain</t>
-        </is>
-      </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Origin_domain_nums</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>VAL_ACC</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>VAL_F1</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>TEST_ACC</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>TEST_F1</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>TEST_R</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>TEST_P</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>kernel_size</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+      <c r="B2" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>99.99209046363831</v>
+        <v>99.9864399433136</v>
       </c>
       <c r="D2" t="n">
-        <v>99.98648166656494</v>
+        <v>99.99002814292908</v>
       </c>
       <c r="E2" t="n">
-        <v>99.977</v>
+        <v>95.941</v>
       </c>
       <c r="F2" t="n">
-        <v>99.97</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>99.973</v>
+        <v>88.523</v>
       </c>
       <c r="H2" t="n">
-        <v>99.968</v>
+        <v>80.298</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="n"/>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
+      <c r="A3" s="5" t="n"/>
+      <c r="B3" s="4" t="n">
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>99.98586773872375</v>
+        <v>99.98756647109985</v>
       </c>
       <c r="D3" t="n">
-        <v>99.98960494995117</v>
+        <v>99.99086260795593</v>
       </c>
       <c r="E3" t="n">
-        <v>99.989</v>
+        <v>99.337</v>
       </c>
       <c r="F3" t="n">
-        <v>99.989</v>
+        <v>89.477</v>
       </c>
       <c r="G3" t="n">
-        <v>99.992</v>
+        <v>89.898</v>
       </c>
       <c r="H3" t="n">
-        <v>99.985</v>
+        <v>89.10899999999999</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="n"/>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="4" t="n">
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>99.98812973499298</v>
+        <v>99.99020397663116</v>
       </c>
       <c r="D4" t="n">
-        <v>99.99127388000488</v>
+        <v>99.99279975891113</v>
       </c>
       <c r="E4" t="n">
-        <v>99.886</v>
+        <v>99.354</v>
       </c>
       <c r="F4" t="n">
-        <v>99.907</v>
+        <v>89.333</v>
       </c>
       <c r="G4" t="n">
-        <v>99.925</v>
+        <v>89.914</v>
       </c>
       <c r="H4" t="n">
-        <v>99.89</v>
+        <v>88.828</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="n"/>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
+      <c r="A5" s="6" t="n"/>
+      <c r="B5" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>99.98756647109985</v>
+        <v>99.98191595077515</v>
       </c>
       <c r="D5" t="n">
-        <v>99.98316168785095</v>
+        <v>99.98670816421509</v>
       </c>
       <c r="E5" t="n">
-        <v>99.077</v>
+        <v>99.88800000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>99.267</v>
+        <v>90.083</v>
       </c>
       <c r="G5" t="n">
-        <v>99.21599999999999</v>
+        <v>90.508</v>
       </c>
       <c r="H5" t="n">
-        <v>99.321</v>
+        <v>89.703</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="n"/>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>out_channels</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>99.98191595077515</v>
+        <v>99.90505278110504</v>
       </c>
       <c r="D6" t="n">
-        <v>99.98670816421509</v>
+        <v>99.82325434684753</v>
       </c>
       <c r="E6" t="n">
-        <v>99.904</v>
+        <v>88.83199999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>99.92400000000001</v>
+        <v>59.747</v>
       </c>
       <c r="G6" t="n">
-        <v>99.94199999999999</v>
+        <v>59.656</v>
       </c>
       <c r="H6" t="n">
-        <v>99.90600000000001</v>
+        <v>69.584</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>out_channels</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="4" t="n">
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>99.89261627197266</v>
+        <v>99.9299168586731</v>
       </c>
       <c r="D7" t="n">
-        <v>99.82141256332397</v>
+        <v>99.86020922660828</v>
       </c>
       <c r="E7" t="n">
-        <v>97.568</v>
+        <v>90.794</v>
       </c>
       <c r="F7" t="n">
-        <v>96.723</v>
+        <v>62.129</v>
       </c>
       <c r="G7" t="n">
-        <v>98.40900000000001</v>
+        <v>62.113</v>
       </c>
       <c r="H7" t="n">
-        <v>95.276</v>
+        <v>70.282</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n"/>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="4" t="n">
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>99.89091753959656</v>
+        <v>99.92539286613464</v>
       </c>
       <c r="D8" t="n">
-        <v>99.77599382400513</v>
+        <v>99.86135959625244</v>
       </c>
       <c r="E8" t="n">
-        <v>99.23699999999999</v>
+        <v>92.498</v>
       </c>
       <c r="F8" t="n">
-        <v>98.489</v>
+        <v>66.66500000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>99.477</v>
+        <v>65.357</v>
       </c>
       <c r="H8" t="n">
-        <v>97.59999999999999</v>
+        <v>76.568</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="n"/>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>99.91296529769897</v>
+        <v>99.89431500434875</v>
       </c>
       <c r="D9" t="n">
-        <v>99.86497163772583</v>
+        <v>99.83385801315308</v>
       </c>
       <c r="E9" t="n">
-        <v>98.724</v>
+        <v>96.136</v>
       </c>
       <c r="F9" t="n">
-        <v>98.492</v>
+        <v>78.087</v>
       </c>
       <c r="G9" t="n">
-        <v>97.761</v>
+        <v>76.456</v>
       </c>
       <c r="H9" t="n">
-        <v>99.26600000000001</v>
+        <v>80.867</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n"/>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>stride</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="C10" t="n">
         <v>99.91861581802368</v>
       </c>
       <c r="D10" t="n">
-        <v>99.84864592552185</v>
+        <v>99.79066848754883</v>
       </c>
       <c r="E10" t="n">
-        <v>87.486</v>
+        <v>97.822</v>
       </c>
       <c r="F10" t="n">
-        <v>86.79000000000001</v>
+        <v>94.715</v>
       </c>
       <c r="G10" t="n">
-        <v>86.873</v>
+        <v>92.733</v>
       </c>
       <c r="H10" t="n">
-        <v>87.85599999999999</v>
+        <v>97.042</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n"/>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="4" t="n">
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>99.89431500434875</v>
+        <v>99.93444085121155</v>
       </c>
       <c r="D11" t="n">
-        <v>99.83385801315308</v>
+        <v>99.83149170875549</v>
       </c>
       <c r="E11" t="n">
-        <v>99.61499999999999</v>
+        <v>98.956</v>
       </c>
       <c r="F11" t="n">
-        <v>99.505</v>
+        <v>97.06399999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>99.491</v>
+        <v>95.66500000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>99.523</v>
+        <v>98.63</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>stride</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="4" t="n">
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>99.95591640472412</v>
+        <v>99.95403289794922</v>
       </c>
       <c r="D12" t="n">
-        <v>99.88664388656616</v>
+        <v>99.88189935684204</v>
       </c>
       <c r="E12" t="n">
-        <v>99.378</v>
+        <v>98.96899999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>98.428</v>
+        <v>97.08799999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>98.595</v>
+        <v>95.69499999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>98.26300000000001</v>
+        <v>98.649</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n"/>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>99.91974234580994</v>
+        <v>99.94574189186096</v>
       </c>
       <c r="D13" t="n">
-        <v>99.79397058486938</v>
+        <v>99.86034631729126</v>
       </c>
       <c r="E13" t="n">
-        <v>99.83199999999999</v>
+        <v>99.923</v>
       </c>
       <c r="F13" t="n">
-        <v>99.577</v>
+        <v>99.262</v>
       </c>
       <c r="G13" t="n">
-        <v>99.83199999999999</v>
+        <v>99.176</v>
       </c>
       <c r="H13" t="n">
-        <v>99.325</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="n"/>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>99.91070032119751</v>
-      </c>
-      <c r="D14" t="n">
-        <v>99.76998567581177</v>
-      </c>
-      <c r="E14" t="n">
-        <v>99.28700000000001</v>
-      </c>
-      <c r="F14" t="n">
-        <v>98.143</v>
-      </c>
-      <c r="G14" t="n">
-        <v>96.91</v>
-      </c>
-      <c r="H14" t="n">
-        <v>99.465</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="n"/>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>99.91974234580994</v>
-      </c>
-      <c r="D15" t="n">
-        <v>99.79358315467834</v>
-      </c>
-      <c r="E15" t="n">
-        <v>93.002</v>
-      </c>
-      <c r="F15" t="n">
-        <v>85.313</v>
-      </c>
-      <c r="G15" t="n">
-        <v>93.05800000000001</v>
-      </c>
-      <c r="H15" t="n">
-        <v>80.71299999999999</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="n"/>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>99.94574189186096</v>
-      </c>
-      <c r="D16" t="n">
-        <v>99.86034631729126</v>
-      </c>
-      <c r="E16" t="n">
-        <v>99.931</v>
-      </c>
-      <c r="F16" t="n">
-        <v>99.824</v>
-      </c>
-      <c r="G16" t="n">
-        <v>99.745</v>
-      </c>
-      <c r="H16" t="n">
-        <v>99.90300000000001</v>
+        <v>99.34999999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A7:A11"/>
-    <mergeCell ref="A12:A16"/>
-    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A6:A9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2419,356 +2314,458 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>HyperParameters</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
-        <is>
-          <t>Origin_domain_nums</t>
-        </is>
-      </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>test_domain</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>VAL_ACC</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>VAL_F1</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>TEST_ACC</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>TEST_F1</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>TEST_R</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>TEST_P</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>kernel_size</t>
         </is>
       </c>
-      <c r="B2" s="11" t="n">
-        <v>1</v>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>99.9864399433136</v>
+        <v>99.99209046363831</v>
       </c>
       <c r="D2" t="n">
-        <v>99.99002814292908</v>
+        <v>99.98648166656494</v>
       </c>
       <c r="E2" t="n">
-        <v>95.181</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>96.518</v>
+        <v>90.51300000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>96.956</v>
+        <v>90.52200000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>96.166</v>
+        <v>90.505</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="n"/>
-      <c r="B3" s="11" t="n">
-        <v>2</v>
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
       </c>
       <c r="C3" t="n">
+        <v>99.98586773872375</v>
+      </c>
+      <c r="D3" t="n">
+        <v>99.98960494995117</v>
+      </c>
+      <c r="E3" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>90.511</v>
+      </c>
+      <c r="G3" t="n">
+        <v>90.55200000000001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>90.471</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>99.98812973499298</v>
+      </c>
+      <c r="D4" t="n">
+        <v>99.99127388000488</v>
+      </c>
+      <c r="E4" t="n">
+        <v>99.852</v>
+      </c>
+      <c r="F4" t="n">
+        <v>89.976</v>
+      </c>
+      <c r="G4" t="n">
+        <v>90.486</v>
+      </c>
+      <c r="H4" t="n">
+        <v>89.50700000000001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>99.98756647109985</v>
       </c>
-      <c r="D3" t="n">
-        <v>99.99086260795593</v>
-      </c>
-      <c r="E3" t="n">
-        <v>98.503</v>
-      </c>
-      <c r="F3" t="n">
-        <v>98.896</v>
-      </c>
-      <c r="G3" t="n">
-        <v>98.688</v>
-      </c>
-      <c r="H3" t="n">
-        <v>99.125</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="n"/>
-      <c r="B4" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="n">
-        <v>99.99020397663116</v>
-      </c>
-      <c r="D4" t="n">
-        <v>99.99279975891113</v>
-      </c>
-      <c r="E4" t="n">
-        <v>98.631</v>
-      </c>
-      <c r="F4" t="n">
-        <v>98.994</v>
-      </c>
-      <c r="G4" t="n">
-        <v>98.80500000000001</v>
-      </c>
-      <c r="H4" t="n">
-        <v>99.199</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="n"/>
-      <c r="B5" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
+        <v>99.98316168785095</v>
+      </c>
+      <c r="E5" t="n">
+        <v>99.169</v>
+      </c>
+      <c r="F5" t="n">
+        <v>87.849</v>
+      </c>
+      <c r="G5" t="n">
+        <v>88.959</v>
+      </c>
+      <c r="H5" t="n">
+        <v>87.27800000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>99.98191595077515</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D6" t="n">
         <v>99.98670816421509</v>
       </c>
-      <c r="E5" t="n">
-        <v>99.904</v>
-      </c>
-      <c r="F5" t="n">
-        <v>99.92400000000001</v>
-      </c>
-      <c r="G5" t="n">
-        <v>99.94199999999999</v>
-      </c>
-      <c r="H5" t="n">
-        <v>99.90600000000001</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="E6" t="n">
+        <v>99.88800000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>90.083</v>
+      </c>
+      <c r="G6" t="n">
+        <v>90.508</v>
+      </c>
+      <c r="H6" t="n">
+        <v>89.703</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>out_channels</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>99.90505278110504</v>
-      </c>
-      <c r="D6" t="n">
-        <v>99.82325434684753</v>
-      </c>
-      <c r="E6" t="n">
-        <v>88.501</v>
-      </c>
-      <c r="F6" t="n">
-        <v>83.253</v>
-      </c>
-      <c r="G6" t="n">
-        <v>81.164</v>
-      </c>
-      <c r="H6" t="n">
-        <v>88.371</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="n"/>
-      <c r="B7" s="11" t="n">
-        <v>2</v>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
       </c>
       <c r="C7" t="n">
-        <v>99.9299168586731</v>
+        <v>99.89261627197266</v>
       </c>
       <c r="D7" t="n">
-        <v>99.86020922660828</v>
+        <v>99.82141256332397</v>
       </c>
       <c r="E7" t="n">
-        <v>91.923</v>
+        <v>91.71299999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>86.09099999999999</v>
+        <v>74.636</v>
       </c>
       <c r="G7" t="n">
-        <v>85.104</v>
+        <v>73.61199999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>89.297</v>
+        <v>77.649</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="n"/>
-      <c r="B8" s="11" t="n">
-        <v>3</v>
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
       </c>
       <c r="C8" t="n">
-        <v>99.92539286613464</v>
+        <v>99.89091753959656</v>
       </c>
       <c r="D8" t="n">
-        <v>99.86135959625244</v>
+        <v>99.77599382400513</v>
       </c>
       <c r="E8" t="n">
-        <v>95.90000000000001</v>
+        <v>98.124</v>
       </c>
       <c r="F8" t="n">
-        <v>92.122</v>
+        <v>80.325</v>
       </c>
       <c r="G8" t="n">
-        <v>91.005</v>
+        <v>79.146</v>
       </c>
       <c r="H8" t="n">
-        <v>94.33799999999999</v>
+        <v>82.17700000000001</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="n"/>
-      <c r="B9" s="11" t="n">
-        <v>4</v>
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
       </c>
       <c r="C9" t="n">
-        <v>99.89431500434875</v>
+        <v>99.91296529769897</v>
       </c>
       <c r="D9" t="n">
-        <v>99.83385801315308</v>
+        <v>99.86497163772583</v>
       </c>
       <c r="E9" t="n">
-        <v>99.61499999999999</v>
+        <v>94.827</v>
       </c>
       <c r="F9" t="n">
-        <v>99.505</v>
+        <v>75.172</v>
       </c>
       <c r="G9" t="n">
-        <v>99.491</v>
+        <v>73.351</v>
       </c>
       <c r="H9" t="n">
-        <v>99.523</v>
+        <v>79.794</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>stride</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="n">
-        <v>1</v>
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
       </c>
       <c r="C10" t="n">
         <v>99.91861581802368</v>
       </c>
       <c r="D10" t="n">
-        <v>99.79066848754883</v>
+        <v>99.84864592552185</v>
       </c>
       <c r="E10" t="n">
-        <v>97.56399999999999</v>
+        <v>79.79300000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>93.345</v>
+        <v>56.416</v>
       </c>
       <c r="G10" t="n">
-        <v>90.292</v>
+        <v>54.994</v>
       </c>
       <c r="H10" t="n">
-        <v>97.09</v>
+        <v>68.705</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="n"/>
-      <c r="B11" s="11" t="n">
-        <v>2</v>
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
       </c>
       <c r="C11" t="n">
-        <v>99.93444085121155</v>
+        <v>99.89431500434875</v>
       </c>
       <c r="D11" t="n">
-        <v>99.83149170875549</v>
+        <v>99.83385801315308</v>
       </c>
       <c r="E11" t="n">
-        <v>98.43300000000001</v>
+        <v>96.136</v>
       </c>
       <c r="F11" t="n">
-        <v>95.8</v>
+        <v>78.087</v>
       </c>
       <c r="G11" t="n">
-        <v>93.373</v>
+        <v>76.456</v>
       </c>
       <c r="H11" t="n">
-        <v>98.619</v>
+        <v>80.867</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="n"/>
-      <c r="B12" s="11" t="n">
-        <v>3</v>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>stride</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
       </c>
       <c r="C12" t="n">
-        <v>99.95403289794922</v>
+        <v>99.95591640472412</v>
       </c>
       <c r="D12" t="n">
-        <v>99.88189935684204</v>
+        <v>99.88664388656616</v>
       </c>
       <c r="E12" t="n">
-        <v>98.547</v>
+        <v>99.328</v>
       </c>
       <c r="F12" t="n">
-        <v>96.119</v>
+        <v>98.089</v>
       </c>
       <c r="G12" t="n">
-        <v>93.815</v>
+        <v>97.633</v>
       </c>
       <c r="H12" t="n">
-        <v>98.771</v>
+        <v>98.571</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="n"/>
-      <c r="B13" s="11" t="n">
-        <v>4</v>
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
       </c>
       <c r="C13" t="n">
+        <v>99.91974234580994</v>
+      </c>
+      <c r="D13" t="n">
+        <v>99.79397058486938</v>
+      </c>
+      <c r="E13" t="n">
+        <v>99.90300000000001</v>
+      </c>
+      <c r="F13" t="n">
+        <v>99.214</v>
+      </c>
+      <c r="G13" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>99.129</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>99.91070032119751</v>
+      </c>
+      <c r="D14" t="n">
+        <v>99.76998567581177</v>
+      </c>
+      <c r="E14" t="n">
+        <v>99.373</v>
+      </c>
+      <c r="F14" t="n">
+        <v>98.045</v>
+      </c>
+      <c r="G14" t="n">
+        <v>97.167</v>
+      </c>
+      <c r="H14" t="n">
+        <v>98.983</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>99.91974234580994</v>
+      </c>
+      <c r="D15" t="n">
+        <v>99.79358315467834</v>
+      </c>
+      <c r="E15" t="n">
+        <v>94.73099999999999</v>
+      </c>
+      <c r="F15" t="n">
+        <v>89.735</v>
+      </c>
+      <c r="G15" t="n">
+        <v>93.512</v>
+      </c>
+      <c r="H15" t="n">
+        <v>87.086</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
         <v>99.94574189186096</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D16" t="n">
         <v>99.86034631729126</v>
       </c>
-      <c r="E13" t="n">
-        <v>99.931</v>
-      </c>
-      <c r="F13" t="n">
-        <v>99.824</v>
-      </c>
-      <c r="G13" t="n">
-        <v>99.745</v>
-      </c>
-      <c r="H13" t="n">
-        <v>99.90300000000001</v>
+      <c r="E16" t="n">
+        <v>99.923</v>
+      </c>
+      <c r="F16" t="n">
+        <v>99.262</v>
+      </c>
+      <c r="G16" t="n">
+        <v>99.176</v>
+      </c>
+      <c r="H16" t="n">
+        <v>99.34999999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="A2:A6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/results.xlsx
+++ b/results/results.xlsx
@@ -10,6 +10,8 @@
     <sheet name="origin_domain_num_old" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="origin_domain_num_regression" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="test_domain_regression" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="origin_domain_num" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="test_domain" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -2390,6 +2392,830 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" s="5" t="n"/>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>99.98586773872375</v>
+      </c>
+      <c r="D3" t="n">
+        <v>99.98960494995117</v>
+      </c>
+      <c r="E3" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>90.511</v>
+      </c>
+      <c r="G3" t="n">
+        <v>90.55200000000001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>90.471</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>99.98812973499298</v>
+      </c>
+      <c r="D4" t="n">
+        <v>99.99127388000488</v>
+      </c>
+      <c r="E4" t="n">
+        <v>99.852</v>
+      </c>
+      <c r="F4" t="n">
+        <v>89.976</v>
+      </c>
+      <c r="G4" t="n">
+        <v>90.486</v>
+      </c>
+      <c r="H4" t="n">
+        <v>89.50700000000001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>99.98756647109985</v>
+      </c>
+      <c r="D5" t="n">
+        <v>99.98316168785095</v>
+      </c>
+      <c r="E5" t="n">
+        <v>99.169</v>
+      </c>
+      <c r="F5" t="n">
+        <v>87.849</v>
+      </c>
+      <c r="G5" t="n">
+        <v>88.959</v>
+      </c>
+      <c r="H5" t="n">
+        <v>87.27800000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>99.98191595077515</v>
+      </c>
+      <c r="D6" t="n">
+        <v>99.98670816421509</v>
+      </c>
+      <c r="E6" t="n">
+        <v>99.88800000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>90.083</v>
+      </c>
+      <c r="G6" t="n">
+        <v>90.508</v>
+      </c>
+      <c r="H6" t="n">
+        <v>89.703</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>out_channels</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>99.89261627197266</v>
+      </c>
+      <c r="D7" t="n">
+        <v>99.82141256332397</v>
+      </c>
+      <c r="E7" t="n">
+        <v>91.71299999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>74.636</v>
+      </c>
+      <c r="G7" t="n">
+        <v>73.61199999999999</v>
+      </c>
+      <c r="H7" t="n">
+        <v>77.649</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>99.89091753959656</v>
+      </c>
+      <c r="D8" t="n">
+        <v>99.77599382400513</v>
+      </c>
+      <c r="E8" t="n">
+        <v>98.124</v>
+      </c>
+      <c r="F8" t="n">
+        <v>80.325</v>
+      </c>
+      <c r="G8" t="n">
+        <v>79.146</v>
+      </c>
+      <c r="H8" t="n">
+        <v>82.17700000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>99.91296529769897</v>
+      </c>
+      <c r="D9" t="n">
+        <v>99.86497163772583</v>
+      </c>
+      <c r="E9" t="n">
+        <v>94.827</v>
+      </c>
+      <c r="F9" t="n">
+        <v>75.172</v>
+      </c>
+      <c r="G9" t="n">
+        <v>73.351</v>
+      </c>
+      <c r="H9" t="n">
+        <v>79.794</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>99.91861581802368</v>
+      </c>
+      <c r="D10" t="n">
+        <v>99.84864592552185</v>
+      </c>
+      <c r="E10" t="n">
+        <v>79.79300000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>56.416</v>
+      </c>
+      <c r="G10" t="n">
+        <v>54.994</v>
+      </c>
+      <c r="H10" t="n">
+        <v>68.705</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>99.89431500434875</v>
+      </c>
+      <c r="D11" t="n">
+        <v>99.83385801315308</v>
+      </c>
+      <c r="E11" t="n">
+        <v>96.136</v>
+      </c>
+      <c r="F11" t="n">
+        <v>78.087</v>
+      </c>
+      <c r="G11" t="n">
+        <v>76.456</v>
+      </c>
+      <c r="H11" t="n">
+        <v>80.867</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>stride</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>99.95591640472412</v>
+      </c>
+      <c r="D12" t="n">
+        <v>99.88664388656616</v>
+      </c>
+      <c r="E12" t="n">
+        <v>99.328</v>
+      </c>
+      <c r="F12" t="n">
+        <v>98.089</v>
+      </c>
+      <c r="G12" t="n">
+        <v>97.633</v>
+      </c>
+      <c r="H12" t="n">
+        <v>98.571</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>99.91974234580994</v>
+      </c>
+      <c r="D13" t="n">
+        <v>99.79397058486938</v>
+      </c>
+      <c r="E13" t="n">
+        <v>99.90300000000001</v>
+      </c>
+      <c r="F13" t="n">
+        <v>99.214</v>
+      </c>
+      <c r="G13" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>99.129</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>99.91070032119751</v>
+      </c>
+      <c r="D14" t="n">
+        <v>99.76998567581177</v>
+      </c>
+      <c r="E14" t="n">
+        <v>99.373</v>
+      </c>
+      <c r="F14" t="n">
+        <v>98.045</v>
+      </c>
+      <c r="G14" t="n">
+        <v>97.167</v>
+      </c>
+      <c r="H14" t="n">
+        <v>98.983</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>99.91974234580994</v>
+      </c>
+      <c r="D15" t="n">
+        <v>99.79358315467834</v>
+      </c>
+      <c r="E15" t="n">
+        <v>94.73099999999999</v>
+      </c>
+      <c r="F15" t="n">
+        <v>89.735</v>
+      </c>
+      <c r="G15" t="n">
+        <v>93.512</v>
+      </c>
+      <c r="H15" t="n">
+        <v>87.086</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>99.94574189186096</v>
+      </c>
+      <c r="D16" t="n">
+        <v>99.86034631729126</v>
+      </c>
+      <c r="E16" t="n">
+        <v>99.923</v>
+      </c>
+      <c r="F16" t="n">
+        <v>99.262</v>
+      </c>
+      <c r="G16" t="n">
+        <v>99.176</v>
+      </c>
+      <c r="H16" t="n">
+        <v>99.34999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="A2:A6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>HyperParameters</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Origin_domain_nums</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>VAL_ACC</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>VAL_F1</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>TEST_ACC</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>TEST_F1</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>TEST_R</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>TEST_P</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>kernel_size</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>99.9864399433136</v>
+      </c>
+      <c r="D2" t="n">
+        <v>99.99002814292908</v>
+      </c>
+      <c r="E2" t="n">
+        <v>95.941</v>
+      </c>
+      <c r="F2" t="n">
+        <v>82.73999999999999</v>
+      </c>
+      <c r="G2" t="n">
+        <v>88.523</v>
+      </c>
+      <c r="H2" t="n">
+        <v>80.298</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n"/>
+      <c r="B3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>99.98756647109985</v>
+      </c>
+      <c r="D3" t="n">
+        <v>99.99086260795593</v>
+      </c>
+      <c r="E3" t="n">
+        <v>99.337</v>
+      </c>
+      <c r="F3" t="n">
+        <v>89.477</v>
+      </c>
+      <c r="G3" t="n">
+        <v>89.898</v>
+      </c>
+      <c r="H3" t="n">
+        <v>89.10899999999999</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>99.99020397663116</v>
+      </c>
+      <c r="D4" t="n">
+        <v>99.99279975891113</v>
+      </c>
+      <c r="E4" t="n">
+        <v>99.354</v>
+      </c>
+      <c r="F4" t="n">
+        <v>89.333</v>
+      </c>
+      <c r="G4" t="n">
+        <v>89.914</v>
+      </c>
+      <c r="H4" t="n">
+        <v>88.828</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n"/>
+      <c r="B5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>99.98191595077515</v>
+      </c>
+      <c r="D5" t="n">
+        <v>99.98670816421509</v>
+      </c>
+      <c r="E5" t="n">
+        <v>99.88800000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>90.083</v>
+      </c>
+      <c r="G5" t="n">
+        <v>90.508</v>
+      </c>
+      <c r="H5" t="n">
+        <v>89.703</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>out_channels</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>99.90505278110504</v>
+      </c>
+      <c r="D6" t="n">
+        <v>99.82325434684753</v>
+      </c>
+      <c r="E6" t="n">
+        <v>84.821</v>
+      </c>
+      <c r="F6" t="n">
+        <v>68.45099999999999</v>
+      </c>
+      <c r="G6" t="n">
+        <v>68.322</v>
+      </c>
+      <c r="H6" t="n">
+        <v>70.871</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>99.9299168586731</v>
+      </c>
+      <c r="D7" t="n">
+        <v>99.86020922660828</v>
+      </c>
+      <c r="E7" t="n">
+        <v>87.27800000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>69.95099999999999</v>
+      </c>
+      <c r="G7" t="n">
+        <v>71.11199999999999</v>
+      </c>
+      <c r="H7" t="n">
+        <v>70.714</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>99.92539286613464</v>
+      </c>
+      <c r="D8" t="n">
+        <v>99.86135959625244</v>
+      </c>
+      <c r="E8" t="n">
+        <v>93.78700000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>76.54000000000001</v>
+      </c>
+      <c r="G8" t="n">
+        <v>76.73399999999999</v>
+      </c>
+      <c r="H8" t="n">
+        <v>77.337</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>99.89431500434875</v>
+      </c>
+      <c r="D9" t="n">
+        <v>99.83385801315308</v>
+      </c>
+      <c r="E9" t="n">
+        <v>99.59099999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>83.306</v>
+      </c>
+      <c r="G9" t="n">
+        <v>83.47199999999999</v>
+      </c>
+      <c r="H9" t="n">
+        <v>83.205</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>stride</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>99.91861581802368</v>
+      </c>
+      <c r="D10" t="n">
+        <v>99.79066848754883</v>
+      </c>
+      <c r="E10" t="n">
+        <v>97.822</v>
+      </c>
+      <c r="F10" t="n">
+        <v>94.715</v>
+      </c>
+      <c r="G10" t="n">
+        <v>92.733</v>
+      </c>
+      <c r="H10" t="n">
+        <v>97.042</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="n">
+        <v>99.93444085121155</v>
+      </c>
+      <c r="D11" t="n">
+        <v>99.83149170875549</v>
+      </c>
+      <c r="E11" t="n">
+        <v>98.956</v>
+      </c>
+      <c r="F11" t="n">
+        <v>97.06399999999999</v>
+      </c>
+      <c r="G11" t="n">
+        <v>95.66500000000001</v>
+      </c>
+      <c r="H11" t="n">
+        <v>98.63</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>99.95403289794922</v>
+      </c>
+      <c r="D12" t="n">
+        <v>99.88189935684204</v>
+      </c>
+      <c r="E12" t="n">
+        <v>98.96899999999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>97.08799999999999</v>
+      </c>
+      <c r="G12" t="n">
+        <v>95.69499999999999</v>
+      </c>
+      <c r="H12" t="n">
+        <v>98.649</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" t="n">
+        <v>99.94574189186096</v>
+      </c>
+      <c r="D13" t="n">
+        <v>99.86034631729126</v>
+      </c>
+      <c r="E13" t="n">
+        <v>99.923</v>
+      </c>
+      <c r="F13" t="n">
+        <v>99.262</v>
+      </c>
+      <c r="G13" t="n">
+        <v>99.176</v>
+      </c>
+      <c r="H13" t="n">
+        <v>99.34999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="A6:A9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>HyperParameters</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>test_domain</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>VAL_ACC</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>VAL_F1</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>TEST_ACC</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>TEST_F1</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>TEST_R</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>TEST_P</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>kernel_size</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>99.99209046363831</v>
+      </c>
+      <c r="D2" t="n">
+        <v>99.98648166656494</v>
+      </c>
+      <c r="E2" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>90.51300000000001</v>
+      </c>
+      <c r="G2" t="n">
+        <v>90.52200000000001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>90.505</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="4" t="n"/>
       <c r="B3" s="4" t="inlineStr">
         <is>
@@ -2511,16 +3337,16 @@
         <v>99.82141256332397</v>
       </c>
       <c r="E7" t="n">
-        <v>91.71299999999999</v>
+        <v>94.655</v>
       </c>
       <c r="F7" t="n">
-        <v>74.636</v>
+        <v>79.488</v>
       </c>
       <c r="G7" t="n">
-        <v>73.61199999999999</v>
+        <v>80.73099999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>77.649</v>
+        <v>79.248</v>
       </c>
     </row>
     <row r="8">
@@ -2537,16 +3363,16 @@
         <v>99.77599382400513</v>
       </c>
       <c r="E8" t="n">
-        <v>98.124</v>
+        <v>98.59099999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>80.325</v>
+        <v>82.476</v>
       </c>
       <c r="G8" t="n">
-        <v>79.146</v>
+        <v>83.07899999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>82.17700000000001</v>
+        <v>81.98999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -2563,16 +3389,16 @@
         <v>99.86497163772583</v>
       </c>
       <c r="E9" t="n">
-        <v>94.827</v>
+        <v>97.355</v>
       </c>
       <c r="F9" t="n">
-        <v>75.172</v>
+        <v>81.91800000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>73.351</v>
+        <v>81.49299999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>79.794</v>
+        <v>82.509</v>
       </c>
     </row>
     <row r="10">
@@ -2589,16 +3415,16 @@
         <v>99.84864592552185</v>
       </c>
       <c r="E10" t="n">
-        <v>79.79300000000001</v>
+        <v>90.012</v>
       </c>
       <c r="F10" t="n">
-        <v>56.416</v>
+        <v>74.024</v>
       </c>
       <c r="G10" t="n">
-        <v>54.994</v>
+        <v>74.02500000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>68.705</v>
+        <v>75.167</v>
       </c>
     </row>
     <row r="11">
@@ -2615,16 +3441,16 @@
         <v>99.83385801315308</v>
       </c>
       <c r="E11" t="n">
-        <v>96.136</v>
+        <v>99.59099999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>78.087</v>
+        <v>83.306</v>
       </c>
       <c r="G11" t="n">
-        <v>76.456</v>
+        <v>83.47199999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>80.867</v>
+        <v>83.205</v>
       </c>
     </row>
     <row r="12">

--- a/results/results.xlsx
+++ b/results/results.xlsx
@@ -4,17 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="15540" tabRatio="568" firstSheet="1" activeTab="5"/>
+    <workbookView windowWidth="30720" windowHeight="15540" tabRatio="568" activeTab="5"/>
   </bookViews>
   <sheets>
-    <sheet name="origin_domain_num_regression" sheetId="1" r:id="rId1"/>
-    <sheet name="test_domain_regression" sheetId="2" r:id="rId2"/>
-    <sheet name="origin_domain_num" sheetId="3" r:id="rId3"/>
-    <sheet name="test_domain" sheetId="4" r:id="rId4"/>
-    <sheet name="conv2d_O_regression" sheetId="5" r:id="rId5"/>
-    <sheet name="conv2d_T_regression" sheetId="6" r:id="rId6"/>
-    <sheet name="max_pool2d_T" sheetId="7" r:id="rId7"/>
-    <sheet name="linear_T_regression" sheetId="8" r:id="rId8"/>
+    <sheet name="conv2d_O_regression" sheetId="5" r:id="rId1"/>
+    <sheet name="conv2d_T_regression" sheetId="6" r:id="rId2"/>
+    <sheet name="max_pool2d_T" sheetId="7" r:id="rId3"/>
+    <sheet name="linear_T_regression" sheetId="8" r:id="rId4"/>
+    <sheet name="conv2d_T_regression_half" sheetId="9" r:id="rId5"/>
+    <sheet name="conv2d_T_regression_quarter" sheetId="10" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="18">
   <si>
     <t>HyperParameters</t>
   </si>
@@ -747,8 +745,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1104,36 +1107,36 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="4">
         <v>1</v>
       </c>
       <c r="C2">
@@ -1143,21 +1146,21 @@
         <v>99.9900281429291</v>
       </c>
       <c r="E2">
-        <v>95.941</v>
+        <v>95.181</v>
       </c>
       <c r="F2">
-        <v>82.74</v>
+        <v>95.212</v>
       </c>
       <c r="G2">
-        <v>88.523</v>
+        <v>95.181</v>
       </c>
       <c r="H2">
-        <v>80.298</v>
+        <v>95.355</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="2"/>
-      <c r="B3" s="1">
+      <c r="A3" s="5"/>
+      <c r="B3" s="4">
         <v>2</v>
       </c>
       <c r="C3">
@@ -1167,21 +1170,21 @@
         <v>99.9908626079559</v>
       </c>
       <c r="E3">
-        <v>99.337</v>
+        <v>98.503</v>
       </c>
       <c r="F3">
-        <v>89.477</v>
+        <v>98.498</v>
       </c>
       <c r="G3">
-        <v>89.898</v>
+        <v>98.503</v>
       </c>
       <c r="H3">
-        <v>89.109</v>
+        <v>98.518</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="2"/>
-      <c r="B4" s="1">
+      <c r="A4" s="5"/>
+      <c r="B4" s="4">
         <v>3</v>
       </c>
       <c r="C4">
@@ -1191,21 +1194,21 @@
         <v>99.9927997589111</v>
       </c>
       <c r="E4">
-        <v>99.354</v>
+        <v>98.631</v>
       </c>
       <c r="F4">
-        <v>89.333</v>
+        <v>98.627</v>
       </c>
       <c r="G4">
-        <v>89.914</v>
+        <v>98.631</v>
       </c>
       <c r="H4">
-        <v>88.828</v>
+        <v>98.643</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="3"/>
-      <c r="B5" s="1">
+      <c r="A5" s="6"/>
+      <c r="B5" s="4">
         <v>4</v>
       </c>
       <c r="C5">
@@ -1215,121 +1218,121 @@
         <v>99.9867081642151</v>
       </c>
       <c r="E5">
-        <v>99.888</v>
+        <v>99.904</v>
       </c>
       <c r="F5">
-        <v>90.083</v>
+        <v>99.904</v>
       </c>
       <c r="G5">
-        <v>90.508</v>
+        <v>99.904</v>
       </c>
       <c r="H5">
-        <v>89.703</v>
+        <v>99.904</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="4">
         <v>1</v>
       </c>
       <c r="C6">
-        <v>99.905052781105</v>
+        <v>98.8420270684827</v>
       </c>
       <c r="D6">
-        <v>99.8232543468475</v>
+        <v>98.2860435123388</v>
       </c>
       <c r="E6">
-        <v>88.832</v>
+        <v>79.427</v>
       </c>
       <c r="F6">
-        <v>59.747</v>
+        <v>75.417</v>
       </c>
       <c r="G6">
-        <v>59.656</v>
+        <v>79.427</v>
       </c>
       <c r="H6">
-        <v>69.584</v>
+        <v>76.396</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="2"/>
-      <c r="B7" s="1">
+      <c r="A7" s="5"/>
+      <c r="B7" s="4">
         <v>2</v>
       </c>
       <c r="C7">
-        <v>99.9299168586731</v>
+        <v>99.0813490800086</v>
       </c>
       <c r="D7">
-        <v>99.8602092266083</v>
+        <v>98.6454575478686</v>
       </c>
       <c r="E7">
-        <v>90.794</v>
+        <v>81.733</v>
       </c>
       <c r="F7">
-        <v>62.129</v>
+        <v>77.542</v>
       </c>
       <c r="G7">
-        <v>62.113</v>
+        <v>81.733</v>
       </c>
       <c r="H7">
-        <v>70.282</v>
+        <v>77.425</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="2"/>
-      <c r="B8" s="1">
+      <c r="A8" s="5"/>
+      <c r="B8" s="4">
         <v>3</v>
       </c>
       <c r="C8">
-        <v>99.9253928661346</v>
+        <v>98.9600542799831</v>
       </c>
       <c r="D8">
-        <v>99.8613595962524</v>
+        <v>98.5175557858459</v>
       </c>
       <c r="E8">
-        <v>92.498</v>
+        <v>84.992</v>
       </c>
       <c r="F8">
-        <v>66.665</v>
+        <v>83.059</v>
       </c>
       <c r="G8">
-        <v>65.357</v>
+        <v>84.992</v>
       </c>
       <c r="H8">
-        <v>76.568</v>
+        <v>86.354</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="3"/>
-      <c r="B9" s="1">
+      <c r="A9" s="6"/>
+      <c r="B9" s="4">
         <v>4</v>
       </c>
       <c r="C9">
-        <v>99.8943150043488</v>
+        <v>99.125760276509</v>
       </c>
       <c r="D9">
-        <v>99.8338580131531</v>
+        <v>98.8067030777383</v>
       </c>
       <c r="E9">
-        <v>96.136</v>
+        <v>95.97</v>
       </c>
       <c r="F9">
-        <v>78.087</v>
+        <v>95.859</v>
       </c>
       <c r="G9">
-        <v>76.456</v>
+        <v>95.97</v>
       </c>
       <c r="H9">
-        <v>80.867</v>
+        <v>96.048</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="4">
         <v>1</v>
       </c>
       <c r="C10">
@@ -1339,21 +1342,21 @@
         <v>99.7906684875488</v>
       </c>
       <c r="E10">
-        <v>97.822</v>
+        <v>97.564</v>
       </c>
       <c r="F10">
-        <v>94.715</v>
+        <v>97.469</v>
       </c>
       <c r="G10">
-        <v>92.733</v>
+        <v>97.564</v>
       </c>
       <c r="H10">
-        <v>97.042</v>
+        <v>97.543</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="2"/>
-      <c r="B11" s="1">
+      <c r="A11" s="5"/>
+      <c r="B11" s="4">
         <v>2</v>
       </c>
       <c r="C11">
@@ -1363,21 +1366,21 @@
         <v>99.8314917087555</v>
       </c>
       <c r="E11">
-        <v>98.956</v>
+        <v>98.433</v>
       </c>
       <c r="F11">
-        <v>97.064</v>
+        <v>98.388</v>
       </c>
       <c r="G11">
-        <v>95.665</v>
+        <v>98.433</v>
       </c>
       <c r="H11">
-        <v>98.63</v>
+        <v>98.439</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="2"/>
-      <c r="B12" s="1">
+      <c r="A12" s="5"/>
+      <c r="B12" s="4">
         <v>3</v>
       </c>
       <c r="C12">
@@ -1387,21 +1390,21 @@
         <v>99.881899356842</v>
       </c>
       <c r="E12">
-        <v>98.969</v>
+        <v>98.547</v>
       </c>
       <c r="F12">
-        <v>97.088</v>
+        <v>98.508</v>
       </c>
       <c r="G12">
-        <v>95.695</v>
+        <v>98.547</v>
       </c>
       <c r="H12">
-        <v>98.649</v>
+        <v>98.554</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="3"/>
-      <c r="B13" s="1">
+      <c r="A13" s="6"/>
+      <c r="B13" s="4">
         <v>4</v>
       </c>
       <c r="C13">
@@ -1411,16 +1414,16 @@
         <v>99.8603463172913</v>
       </c>
       <c r="E13">
-        <v>99.923</v>
+        <v>99.931</v>
       </c>
       <c r="F13">
-        <v>99.262</v>
+        <v>99.931</v>
       </c>
       <c r="G13">
-        <v>99.176</v>
+        <v>99.931</v>
       </c>
       <c r="H13">
-        <v>99.35</v>
+        <v>99.931</v>
       </c>
     </row>
   </sheetData>
@@ -1441,36 +1444,36 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C2">
@@ -1480,21 +1483,21 @@
         <v>99.9864816665649</v>
       </c>
       <c r="E2">
-        <v>99.99</v>
+        <v>99.977</v>
       </c>
       <c r="F2">
-        <v>90.513</v>
+        <v>99.977</v>
       </c>
       <c r="G2">
-        <v>90.522</v>
+        <v>99.977</v>
       </c>
       <c r="H2">
-        <v>90.505</v>
+        <v>99.977</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="2"/>
-      <c r="B3" s="1" t="s">
+      <c r="A3" s="5"/>
+      <c r="B3" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C3">
@@ -1504,21 +1507,21 @@
         <v>99.9896049499512</v>
       </c>
       <c r="E3">
-        <v>99.99</v>
+        <v>99.989</v>
       </c>
       <c r="F3">
-        <v>90.511</v>
+        <v>99.989</v>
       </c>
       <c r="G3">
-        <v>90.552</v>
+        <v>99.989</v>
       </c>
       <c r="H3">
-        <v>90.471</v>
+        <v>99.989</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="2"/>
-      <c r="B4" s="1" t="s">
+      <c r="A4" s="5"/>
+      <c r="B4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C4">
@@ -1528,21 +1531,21 @@
         <v>99.9912738800049</v>
       </c>
       <c r="E4">
-        <v>99.852</v>
+        <v>99.886</v>
       </c>
       <c r="F4">
-        <v>89.976</v>
+        <v>99.886</v>
       </c>
       <c r="G4">
-        <v>90.486</v>
+        <v>99.886</v>
       </c>
       <c r="H4">
-        <v>89.507</v>
+        <v>99.886</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="2"/>
-      <c r="B5" s="1" t="s">
+      <c r="A5" s="5"/>
+      <c r="B5" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C5">
@@ -1552,21 +1555,21 @@
         <v>99.983161687851</v>
       </c>
       <c r="E5">
-        <v>99.169</v>
+        <v>99.077</v>
       </c>
       <c r="F5">
-        <v>87.849</v>
+        <v>99.075</v>
       </c>
       <c r="G5">
-        <v>88.959</v>
+        <v>99.077</v>
       </c>
       <c r="H5">
-        <v>87.278</v>
+        <v>99.079</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="3"/>
-      <c r="B6" s="1" t="s">
+      <c r="A6" s="6"/>
+      <c r="B6" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C6">
@@ -1576,145 +1579,145 @@
         <v>99.9867081642151</v>
       </c>
       <c r="E6">
-        <v>99.888</v>
+        <v>99.904</v>
       </c>
       <c r="F6">
-        <v>90.083</v>
+        <v>99.904</v>
       </c>
       <c r="G6">
-        <v>90.508</v>
+        <v>99.904</v>
       </c>
       <c r="H6">
-        <v>89.703</v>
+        <v>99.904</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C7">
-        <v>99.8926162719727</v>
+        <v>99.1016938345034</v>
       </c>
       <c r="D7">
-        <v>99.821412563324</v>
+        <v>98.7474039983508</v>
       </c>
       <c r="E7">
-        <v>91.713</v>
+        <v>94.35</v>
       </c>
       <c r="F7">
-        <v>74.636</v>
+        <v>94.265</v>
       </c>
       <c r="G7">
-        <v>73.612</v>
+        <v>94.35</v>
       </c>
       <c r="H7">
-        <v>77.649</v>
+        <v>94.697</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="2"/>
-      <c r="B8" s="1" t="s">
+      <c r="A8" s="5"/>
+      <c r="B8" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C8">
-        <v>99.8909175395966</v>
+        <v>98.9718300272224</v>
       </c>
       <c r="D8">
-        <v>99.7759938240051</v>
+        <v>98.5203977175924</v>
       </c>
       <c r="E8">
-        <v>98.124</v>
+        <v>97.671</v>
       </c>
       <c r="F8">
-        <v>80.325</v>
+        <v>97.612</v>
       </c>
       <c r="G8">
-        <v>79.146</v>
+        <v>97.671</v>
       </c>
       <c r="H8">
-        <v>82.177</v>
+        <v>97.725</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="2"/>
-      <c r="B9" s="1" t="s">
+      <c r="A9" s="5"/>
+      <c r="B9" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C9">
-        <v>99.912965297699</v>
+        <v>99.0644134888163</v>
       </c>
       <c r="D9">
-        <v>99.8649716377258</v>
+        <v>98.6800474355123</v>
       </c>
       <c r="E9">
-        <v>94.827</v>
+        <v>95.095</v>
       </c>
       <c r="F9">
-        <v>75.172</v>
+        <v>94.833</v>
       </c>
       <c r="G9">
-        <v>73.351</v>
+        <v>95.095</v>
       </c>
       <c r="H9">
-        <v>79.794</v>
+        <v>95.272</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="2"/>
-      <c r="B10" s="1" t="s">
+      <c r="A10" s="5"/>
+      <c r="B10" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C10">
-        <v>99.9186158180237</v>
+        <v>99.1609923299119</v>
       </c>
       <c r="D10">
-        <v>99.8486459255219</v>
+        <v>98.7620679089235</v>
       </c>
       <c r="E10">
-        <v>79.793</v>
+        <v>76.262</v>
       </c>
       <c r="F10">
-        <v>56.416</v>
+        <v>75.538</v>
       </c>
       <c r="G10">
-        <v>54.994</v>
+        <v>76.262</v>
       </c>
       <c r="H10">
-        <v>68.705</v>
+        <v>79.857</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="3"/>
-      <c r="B11" s="1" t="s">
+      <c r="A11" s="6"/>
+      <c r="B11" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C11">
-        <v>99.8943150043488</v>
+        <v>99.125760276509</v>
       </c>
       <c r="D11">
-        <v>99.8338580131531</v>
+        <v>98.8067030777383</v>
       </c>
       <c r="E11">
-        <v>96.136</v>
+        <v>95.97</v>
       </c>
       <c r="F11">
-        <v>78.087</v>
+        <v>95.859</v>
       </c>
       <c r="G11">
-        <v>76.456</v>
+        <v>95.97</v>
       </c>
       <c r="H11">
-        <v>80.867</v>
+        <v>96.048</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C12">
@@ -1724,21 +1727,21 @@
         <v>99.8866438865662</v>
       </c>
       <c r="E12">
-        <v>99.328</v>
+        <v>99.378</v>
       </c>
       <c r="F12">
-        <v>98.089</v>
+        <v>99.379</v>
       </c>
       <c r="G12">
-        <v>97.633</v>
+        <v>99.378</v>
       </c>
       <c r="H12">
-        <v>98.571</v>
+        <v>99.381</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="2"/>
-      <c r="B13" s="1" t="s">
+      <c r="A13" s="5"/>
+      <c r="B13" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C13">
@@ -1748,21 +1751,21 @@
         <v>99.7939705848694</v>
       </c>
       <c r="E13">
-        <v>99.903</v>
+        <v>99.832</v>
       </c>
       <c r="F13">
-        <v>99.214</v>
+        <v>99.833</v>
       </c>
       <c r="G13">
-        <v>99.3</v>
+        <v>99.832</v>
       </c>
       <c r="H13">
-        <v>99.129</v>
+        <v>99.834</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="2"/>
-      <c r="B14" s="1" t="s">
+      <c r="A14" s="5"/>
+      <c r="B14" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C14">
@@ -1772,21 +1775,21 @@
         <v>99.7699856758118</v>
       </c>
       <c r="E14">
-        <v>99.373</v>
+        <v>99.287</v>
       </c>
       <c r="F14">
-        <v>98.045</v>
+        <v>99.277</v>
       </c>
       <c r="G14">
-        <v>97.167</v>
+        <v>99.287</v>
       </c>
       <c r="H14">
-        <v>98.983</v>
+        <v>99.29</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="2"/>
-      <c r="B15" s="1" t="s">
+      <c r="A15" s="5"/>
+      <c r="B15" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C15">
@@ -1796,21 +1799,21 @@
         <v>99.7935831546783</v>
       </c>
       <c r="E15">
-        <v>94.731</v>
+        <v>93.002</v>
       </c>
       <c r="F15">
-        <v>89.735</v>
+        <v>93.584</v>
       </c>
       <c r="G15">
-        <v>93.512</v>
+        <v>93.002</v>
       </c>
       <c r="H15">
-        <v>87.086</v>
+        <v>95.014</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="3"/>
-      <c r="B16" s="1" t="s">
+      <c r="A16" s="6"/>
+      <c r="B16" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C16">
@@ -1820,16 +1823,16 @@
         <v>99.8603463172913</v>
       </c>
       <c r="E16">
-        <v>99.923</v>
+        <v>99.931</v>
       </c>
       <c r="F16">
-        <v>99.262</v>
+        <v>99.931</v>
       </c>
       <c r="G16">
-        <v>99.176</v>
+        <v>99.931</v>
       </c>
       <c r="H16">
-        <v>99.35</v>
+        <v>99.931</v>
       </c>
     </row>
   </sheetData>
@@ -1846,1532 +1849,40 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="7"/>
-  <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>99.9864399433136</v>
-      </c>
-      <c r="D2">
-        <v>99.9900281429291</v>
-      </c>
-      <c r="E2">
-        <v>95.941</v>
-      </c>
-      <c r="F2">
-        <v>82.74</v>
-      </c>
-      <c r="G2">
-        <v>88.523</v>
-      </c>
-      <c r="H2">
-        <v>80.298</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="2"/>
-      <c r="B3" s="1">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>99.9875664710999</v>
-      </c>
-      <c r="D3">
-        <v>99.9908626079559</v>
-      </c>
-      <c r="E3">
-        <v>99.337</v>
-      </c>
-      <c r="F3">
-        <v>89.477</v>
-      </c>
-      <c r="G3">
-        <v>89.898</v>
-      </c>
-      <c r="H3">
-        <v>89.109</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="2"/>
-      <c r="B4" s="1">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>99.9902039766312</v>
-      </c>
-      <c r="D4">
-        <v>99.9927997589111</v>
-      </c>
-      <c r="E4">
-        <v>99.354</v>
-      </c>
-      <c r="F4">
-        <v>89.333</v>
-      </c>
-      <c r="G4">
-        <v>89.914</v>
-      </c>
-      <c r="H4">
-        <v>88.828</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="3"/>
-      <c r="B5" s="1">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>99.9819159507751</v>
-      </c>
-      <c r="D5">
-        <v>99.9867081642151</v>
-      </c>
-      <c r="E5">
-        <v>99.888</v>
-      </c>
-      <c r="F5">
-        <v>90.083</v>
-      </c>
-      <c r="G5">
-        <v>90.508</v>
-      </c>
-      <c r="H5">
-        <v>89.703</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="1">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>99.905052781105</v>
-      </c>
-      <c r="D6">
-        <v>99.8232543468475</v>
-      </c>
-      <c r="E6">
-        <v>84.821</v>
-      </c>
-      <c r="F6">
-        <v>68.451</v>
-      </c>
-      <c r="G6">
-        <v>68.322</v>
-      </c>
-      <c r="H6">
-        <v>70.871</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="2"/>
-      <c r="B7" s="1">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>99.9299168586731</v>
-      </c>
-      <c r="D7">
-        <v>99.8602092266083</v>
-      </c>
-      <c r="E7">
-        <v>87.278</v>
-      </c>
-      <c r="F7">
-        <v>69.951</v>
-      </c>
-      <c r="G7">
-        <v>71.112</v>
-      </c>
-      <c r="H7">
-        <v>70.714</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="2"/>
-      <c r="B8" s="1">
-        <v>3</v>
-      </c>
-      <c r="C8">
-        <v>99.9253928661346</v>
-      </c>
-      <c r="D8">
-        <v>99.8613595962524</v>
-      </c>
-      <c r="E8">
-        <v>93.787</v>
-      </c>
-      <c r="F8">
-        <v>76.54</v>
-      </c>
-      <c r="G8">
-        <v>76.734</v>
-      </c>
-      <c r="H8">
-        <v>77.337</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="3"/>
-      <c r="B9" s="1">
-        <v>4</v>
-      </c>
-      <c r="C9">
-        <v>99.8943150043488</v>
-      </c>
-      <c r="D9">
-        <v>99.8338580131531</v>
-      </c>
-      <c r="E9">
-        <v>99.591</v>
-      </c>
-      <c r="F9">
-        <v>83.306</v>
-      </c>
-      <c r="G9">
-        <v>83.472</v>
-      </c>
-      <c r="H9">
-        <v>83.205</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="1">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>99.9186158180237</v>
-      </c>
-      <c r="D10">
-        <v>99.7906684875488</v>
-      </c>
-      <c r="E10">
-        <v>97.822</v>
-      </c>
-      <c r="F10">
-        <v>94.715</v>
-      </c>
-      <c r="G10">
-        <v>92.733</v>
-      </c>
-      <c r="H10">
-        <v>97.042</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="2"/>
-      <c r="B11" s="1">
-        <v>2</v>
-      </c>
-      <c r="C11">
-        <v>99.9344408512115</v>
-      </c>
-      <c r="D11">
-        <v>99.8314917087555</v>
-      </c>
-      <c r="E11">
-        <v>98.956</v>
-      </c>
-      <c r="F11">
-        <v>97.064</v>
-      </c>
-      <c r="G11">
-        <v>95.665</v>
-      </c>
-      <c r="H11">
-        <v>98.63</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="2"/>
-      <c r="B12" s="1">
-        <v>3</v>
-      </c>
-      <c r="C12">
-        <v>99.9540328979492</v>
-      </c>
-      <c r="D12">
-        <v>99.881899356842</v>
-      </c>
-      <c r="E12">
-        <v>98.969</v>
-      </c>
-      <c r="F12">
-        <v>97.088</v>
-      </c>
-      <c r="G12">
-        <v>95.695</v>
-      </c>
-      <c r="H12">
-        <v>98.649</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="3"/>
-      <c r="B13" s="1">
-        <v>4</v>
-      </c>
-      <c r="C13">
-        <v>99.945741891861</v>
-      </c>
-      <c r="D13">
-        <v>99.8603463172913</v>
-      </c>
-      <c r="E13">
-        <v>99.923</v>
-      </c>
-      <c r="F13">
-        <v>99.262</v>
-      </c>
-      <c r="G13">
-        <v>99.176</v>
-      </c>
-      <c r="H13">
-        <v>99.35</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="7"/>
-  <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2">
-        <v>99.9920904636383</v>
-      </c>
-      <c r="D2">
-        <v>99.9864816665649</v>
-      </c>
-      <c r="E2">
-        <v>99.99</v>
-      </c>
-      <c r="F2">
-        <v>90.513</v>
-      </c>
-      <c r="G2">
-        <v>90.522</v>
-      </c>
-      <c r="H2">
-        <v>90.505</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="2"/>
-      <c r="B3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3">
-        <v>99.9858677387238</v>
-      </c>
-      <c r="D3">
-        <v>99.9896049499512</v>
-      </c>
-      <c r="E3">
-        <v>99.99</v>
-      </c>
-      <c r="F3">
-        <v>90.511</v>
-      </c>
-      <c r="G3">
-        <v>90.552</v>
-      </c>
-      <c r="H3">
-        <v>90.471</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="2"/>
-      <c r="B4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4">
-        <v>99.988129734993</v>
-      </c>
-      <c r="D4">
-        <v>99.9912738800049</v>
-      </c>
-      <c r="E4">
-        <v>99.852</v>
-      </c>
-      <c r="F4">
-        <v>89.976</v>
-      </c>
-      <c r="G4">
-        <v>90.486</v>
-      </c>
-      <c r="H4">
-        <v>89.507</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="2"/>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5">
-        <v>99.9875664710999</v>
-      </c>
-      <c r="D5">
-        <v>99.983161687851</v>
-      </c>
-      <c r="E5">
-        <v>99.169</v>
-      </c>
-      <c r="F5">
-        <v>87.849</v>
-      </c>
-      <c r="G5">
-        <v>88.959</v>
-      </c>
-      <c r="H5">
-        <v>87.278</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="3"/>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6">
-        <v>99.9819159507751</v>
-      </c>
-      <c r="D6">
-        <v>99.9867081642151</v>
-      </c>
-      <c r="E6">
-        <v>99.888</v>
-      </c>
-      <c r="F6">
-        <v>90.083</v>
-      </c>
-      <c r="G6">
-        <v>90.508</v>
-      </c>
-      <c r="H6">
-        <v>89.703</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7">
-        <v>99.8926162719727</v>
-      </c>
-      <c r="D7">
-        <v>99.821412563324</v>
-      </c>
-      <c r="E7">
-        <v>94.655</v>
-      </c>
-      <c r="F7">
-        <v>79.488</v>
-      </c>
-      <c r="G7">
-        <v>80.731</v>
-      </c>
-      <c r="H7">
-        <v>79.248</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="2"/>
-      <c r="B8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8">
-        <v>99.8909175395966</v>
-      </c>
-      <c r="D8">
-        <v>99.7759938240051</v>
-      </c>
-      <c r="E8">
-        <v>98.591</v>
-      </c>
-      <c r="F8">
-        <v>82.476</v>
-      </c>
-      <c r="G8">
-        <v>83.079</v>
-      </c>
-      <c r="H8">
-        <v>81.99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="2"/>
-      <c r="B9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9">
-        <v>99.912965297699</v>
-      </c>
-      <c r="D9">
-        <v>99.8649716377258</v>
-      </c>
-      <c r="E9">
-        <v>97.355</v>
-      </c>
-      <c r="F9">
-        <v>81.918</v>
-      </c>
-      <c r="G9">
-        <v>81.493</v>
-      </c>
-      <c r="H9">
-        <v>82.509</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="2"/>
-      <c r="B10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10">
-        <v>99.9186158180237</v>
-      </c>
-      <c r="D10">
-        <v>99.8486459255219</v>
-      </c>
-      <c r="E10">
-        <v>90.012</v>
-      </c>
-      <c r="F10">
-        <v>74.024</v>
-      </c>
-      <c r="G10">
-        <v>74.025</v>
-      </c>
-      <c r="H10">
-        <v>75.167</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="3"/>
-      <c r="B11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11">
-        <v>99.8943150043488</v>
-      </c>
-      <c r="D11">
-        <v>99.8338580131531</v>
-      </c>
-      <c r="E11">
-        <v>99.591</v>
-      </c>
-      <c r="F11">
-        <v>83.306</v>
-      </c>
-      <c r="G11">
-        <v>83.472</v>
-      </c>
-      <c r="H11">
-        <v>83.205</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12">
-        <v>99.9559164047241</v>
-      </c>
-      <c r="D12">
-        <v>99.8866438865662</v>
-      </c>
-      <c r="E12">
-        <v>99.328</v>
-      </c>
-      <c r="F12">
-        <v>98.089</v>
-      </c>
-      <c r="G12">
-        <v>97.633</v>
-      </c>
-      <c r="H12">
-        <v>98.571</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="2"/>
-      <c r="B13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13">
-        <v>99.9197423458099</v>
-      </c>
-      <c r="D13">
-        <v>99.7939705848694</v>
-      </c>
-      <c r="E13">
-        <v>99.903</v>
-      </c>
-      <c r="F13">
-        <v>99.214</v>
-      </c>
-      <c r="G13">
-        <v>99.3</v>
-      </c>
-      <c r="H13">
-        <v>99.129</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="2"/>
-      <c r="B14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14">
-        <v>99.9107003211975</v>
-      </c>
-      <c r="D14">
-        <v>99.7699856758118</v>
-      </c>
-      <c r="E14">
-        <v>99.373</v>
-      </c>
-      <c r="F14">
-        <v>98.045</v>
-      </c>
-      <c r="G14">
-        <v>97.167</v>
-      </c>
-      <c r="H14">
-        <v>98.983</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="2"/>
-      <c r="B15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15">
-        <v>99.9197423458099</v>
-      </c>
-      <c r="D15">
-        <v>99.7935831546783</v>
-      </c>
-      <c r="E15">
-        <v>94.731</v>
-      </c>
-      <c r="F15">
-        <v>89.735</v>
-      </c>
-      <c r="G15">
-        <v>93.512</v>
-      </c>
-      <c r="H15">
-        <v>87.086</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="3"/>
-      <c r="B16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16">
-        <v>99.945741891861</v>
-      </c>
-      <c r="D16">
-        <v>99.8603463172913</v>
-      </c>
-      <c r="E16">
-        <v>99.923</v>
-      </c>
-      <c r="F16">
-        <v>99.262</v>
-      </c>
-      <c r="G16">
-        <v>99.176</v>
-      </c>
-      <c r="H16">
-        <v>99.35</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="A7:A11"/>
-    <mergeCell ref="A12:A16"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="7"/>
-  <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>99.9864399433136</v>
-      </c>
-      <c r="D2">
-        <v>99.9900281429291</v>
-      </c>
-      <c r="E2">
-        <v>95.181</v>
-      </c>
-      <c r="F2">
-        <v>95.212</v>
-      </c>
-      <c r="G2">
-        <v>95.181</v>
-      </c>
-      <c r="H2">
-        <v>95.355</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="2"/>
-      <c r="B3" s="1">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>99.9875664710999</v>
-      </c>
-      <c r="D3">
-        <v>99.9908626079559</v>
-      </c>
-      <c r="E3">
-        <v>98.503</v>
-      </c>
-      <c r="F3">
-        <v>98.498</v>
-      </c>
-      <c r="G3">
-        <v>98.503</v>
-      </c>
-      <c r="H3">
-        <v>98.518</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="2"/>
-      <c r="B4" s="1">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>99.9902039766312</v>
-      </c>
-      <c r="D4">
-        <v>99.9927997589111</v>
-      </c>
-      <c r="E4">
-        <v>98.631</v>
-      </c>
-      <c r="F4">
-        <v>98.627</v>
-      </c>
-      <c r="G4">
-        <v>98.631</v>
-      </c>
-      <c r="H4">
-        <v>98.643</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="3"/>
-      <c r="B5" s="1">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>99.9819159507751</v>
-      </c>
-      <c r="D5">
-        <v>99.9867081642151</v>
-      </c>
-      <c r="E5">
-        <v>99.904</v>
-      </c>
-      <c r="F5">
-        <v>99.904</v>
-      </c>
-      <c r="G5">
-        <v>99.904</v>
-      </c>
-      <c r="H5">
-        <v>99.904</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="1">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>98.8420270684827</v>
-      </c>
-      <c r="D6">
-        <v>98.2860435123388</v>
-      </c>
-      <c r="E6">
-        <v>79.427</v>
-      </c>
-      <c r="F6">
-        <v>75.417</v>
-      </c>
-      <c r="G6">
-        <v>79.427</v>
-      </c>
-      <c r="H6">
-        <v>76.396</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="2"/>
-      <c r="B7" s="1">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>99.0813490800086</v>
-      </c>
-      <c r="D7">
-        <v>98.6454575478686</v>
-      </c>
-      <c r="E7">
-        <v>81.733</v>
-      </c>
-      <c r="F7">
-        <v>77.542</v>
-      </c>
-      <c r="G7">
-        <v>81.733</v>
-      </c>
-      <c r="H7">
-        <v>77.425</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="2"/>
-      <c r="B8" s="1">
-        <v>3</v>
-      </c>
-      <c r="C8">
-        <v>98.9600542799831</v>
-      </c>
-      <c r="D8">
-        <v>98.5175557858459</v>
-      </c>
-      <c r="E8">
-        <v>84.992</v>
-      </c>
-      <c r="F8">
-        <v>83.059</v>
-      </c>
-      <c r="G8">
-        <v>84.992</v>
-      </c>
-      <c r="H8">
-        <v>86.354</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="3"/>
-      <c r="B9" s="1">
-        <v>4</v>
-      </c>
-      <c r="C9">
-        <v>99.125760276509</v>
-      </c>
-      <c r="D9">
-        <v>98.8067030777383</v>
-      </c>
-      <c r="E9">
-        <v>95.97</v>
-      </c>
-      <c r="F9">
-        <v>95.859</v>
-      </c>
-      <c r="G9">
-        <v>95.97</v>
-      </c>
-      <c r="H9">
-        <v>96.048</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="1">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>99.9186158180237</v>
-      </c>
-      <c r="D10">
-        <v>99.7906684875488</v>
-      </c>
-      <c r="E10">
-        <v>97.564</v>
-      </c>
-      <c r="F10">
-        <v>97.469</v>
-      </c>
-      <c r="G10">
-        <v>97.564</v>
-      </c>
-      <c r="H10">
-        <v>97.543</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="2"/>
-      <c r="B11" s="1">
-        <v>2</v>
-      </c>
-      <c r="C11">
-        <v>99.9344408512115</v>
-      </c>
-      <c r="D11">
-        <v>99.8314917087555</v>
-      </c>
-      <c r="E11">
-        <v>98.433</v>
-      </c>
-      <c r="F11">
-        <v>98.388</v>
-      </c>
-      <c r="G11">
-        <v>98.433</v>
-      </c>
-      <c r="H11">
-        <v>98.439</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="2"/>
-      <c r="B12" s="1">
-        <v>3</v>
-      </c>
-      <c r="C12">
-        <v>99.9540328979492</v>
-      </c>
-      <c r="D12">
-        <v>99.881899356842</v>
-      </c>
-      <c r="E12">
-        <v>98.547</v>
-      </c>
-      <c r="F12">
-        <v>98.508</v>
-      </c>
-      <c r="G12">
-        <v>98.547</v>
-      </c>
-      <c r="H12">
-        <v>98.554</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="3"/>
-      <c r="B13" s="1">
-        <v>4</v>
-      </c>
-      <c r="C13">
-        <v>99.945741891861</v>
-      </c>
-      <c r="D13">
-        <v>99.8603463172913</v>
-      </c>
-      <c r="E13">
-        <v>99.931</v>
-      </c>
-      <c r="F13">
-        <v>99.931</v>
-      </c>
-      <c r="G13">
-        <v>99.931</v>
-      </c>
-      <c r="H13">
-        <v>99.931</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="7"/>
-  <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2">
-        <v>99.9920904636383</v>
-      </c>
-      <c r="D2">
-        <v>99.9864816665649</v>
-      </c>
-      <c r="E2">
-        <v>99.977</v>
-      </c>
-      <c r="F2">
-        <v>99.977</v>
-      </c>
-      <c r="G2">
-        <v>99.977</v>
-      </c>
-      <c r="H2">
-        <v>99.977</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="2"/>
-      <c r="B3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3">
-        <v>99.9858677387238</v>
-      </c>
-      <c r="D3">
-        <v>99.9896049499512</v>
-      </c>
-      <c r="E3">
-        <v>99.989</v>
-      </c>
-      <c r="F3">
-        <v>99.989</v>
-      </c>
-      <c r="G3">
-        <v>99.989</v>
-      </c>
-      <c r="H3">
-        <v>99.989</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="2"/>
-      <c r="B4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4">
-        <v>99.988129734993</v>
-      </c>
-      <c r="D4">
-        <v>99.9912738800049</v>
-      </c>
-      <c r="E4">
-        <v>99.886</v>
-      </c>
-      <c r="F4">
-        <v>99.886</v>
-      </c>
-      <c r="G4">
-        <v>99.886</v>
-      </c>
-      <c r="H4">
-        <v>99.886</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="2"/>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5">
-        <v>99.9875664710999</v>
-      </c>
-      <c r="D5">
-        <v>99.983161687851</v>
-      </c>
-      <c r="E5">
-        <v>99.077</v>
-      </c>
-      <c r="F5">
-        <v>99.075</v>
-      </c>
-      <c r="G5">
-        <v>99.077</v>
-      </c>
-      <c r="H5">
-        <v>99.079</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="3"/>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6">
-        <v>99.9819159507751</v>
-      </c>
-      <c r="D6">
-        <v>99.9867081642151</v>
-      </c>
-      <c r="E6">
-        <v>99.904</v>
-      </c>
-      <c r="F6">
-        <v>99.904</v>
-      </c>
-      <c r="G6">
-        <v>99.904</v>
-      </c>
-      <c r="H6">
-        <v>99.904</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7">
-        <v>99.1016938345034</v>
-      </c>
-      <c r="D7">
-        <v>98.7474039983508</v>
-      </c>
-      <c r="E7">
-        <v>94.35</v>
-      </c>
-      <c r="F7">
-        <v>94.265</v>
-      </c>
-      <c r="G7">
-        <v>94.35</v>
-      </c>
-      <c r="H7">
-        <v>94.697</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="2"/>
-      <c r="B8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8">
-        <v>98.9718300272224</v>
-      </c>
-      <c r="D8">
-        <v>98.5203977175924</v>
-      </c>
-      <c r="E8">
-        <v>97.671</v>
-      </c>
-      <c r="F8">
-        <v>97.612</v>
-      </c>
-      <c r="G8">
-        <v>97.671</v>
-      </c>
-      <c r="H8">
-        <v>97.725</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="2"/>
-      <c r="B9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9">
-        <v>99.0644134888163</v>
-      </c>
-      <c r="D9">
-        <v>98.6800474355123</v>
-      </c>
-      <c r="E9">
-        <v>95.095</v>
-      </c>
-      <c r="F9">
-        <v>94.833</v>
-      </c>
-      <c r="G9">
-        <v>95.095</v>
-      </c>
-      <c r="H9">
-        <v>95.272</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="2"/>
-      <c r="B10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10">
-        <v>99.1609923299119</v>
-      </c>
-      <c r="D10">
-        <v>98.7620679089235</v>
-      </c>
-      <c r="E10">
-        <v>76.262</v>
-      </c>
-      <c r="F10">
-        <v>75.538</v>
-      </c>
-      <c r="G10">
-        <v>76.262</v>
-      </c>
-      <c r="H10">
-        <v>79.857</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="3"/>
-      <c r="B11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11">
-        <v>99.125760276509</v>
-      </c>
-      <c r="D11">
-        <v>98.8067030777383</v>
-      </c>
-      <c r="E11">
-        <v>95.97</v>
-      </c>
-      <c r="F11">
-        <v>95.859</v>
-      </c>
-      <c r="G11">
-        <v>95.97</v>
-      </c>
-      <c r="H11">
-        <v>96.048</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12">
-        <v>99.9559164047241</v>
-      </c>
-      <c r="D12">
-        <v>99.8866438865662</v>
-      </c>
-      <c r="E12">
-        <v>99.378</v>
-      </c>
-      <c r="F12">
-        <v>99.379</v>
-      </c>
-      <c r="G12">
-        <v>99.378</v>
-      </c>
-      <c r="H12">
-        <v>99.381</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="2"/>
-      <c r="B13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13">
-        <v>99.9197423458099</v>
-      </c>
-      <c r="D13">
-        <v>99.7939705848694</v>
-      </c>
-      <c r="E13">
-        <v>99.832</v>
-      </c>
-      <c r="F13">
-        <v>99.833</v>
-      </c>
-      <c r="G13">
-        <v>99.832</v>
-      </c>
-      <c r="H13">
-        <v>99.834</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="2"/>
-      <c r="B14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14">
-        <v>99.9107003211975</v>
-      </c>
-      <c r="D14">
-        <v>99.7699856758118</v>
-      </c>
-      <c r="E14">
-        <v>99.287</v>
-      </c>
-      <c r="F14">
-        <v>99.277</v>
-      </c>
-      <c r="G14">
-        <v>99.287</v>
-      </c>
-      <c r="H14">
-        <v>99.29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="2"/>
-      <c r="B15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15">
-        <v>99.9197423458099</v>
-      </c>
-      <c r="D15">
-        <v>99.7935831546783</v>
-      </c>
-      <c r="E15">
-        <v>93.002</v>
-      </c>
-      <c r="F15">
-        <v>93.584</v>
-      </c>
-      <c r="G15">
-        <v>93.002</v>
-      </c>
-      <c r="H15">
-        <v>95.014</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="3"/>
-      <c r="B16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16">
-        <v>99.945741891861</v>
-      </c>
-      <c r="D16">
-        <v>99.8603463172913</v>
-      </c>
-      <c r="E16">
-        <v>99.931</v>
-      </c>
-      <c r="F16">
-        <v>99.931</v>
-      </c>
-      <c r="G16">
-        <v>99.931</v>
-      </c>
-      <c r="H16">
-        <v>99.931</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="A7:A11"/>
-    <mergeCell ref="A12:A16"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C2">
@@ -3394,8 +1905,8 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="2"/>
-      <c r="B3" s="1" t="s">
+      <c r="A3" s="5"/>
+      <c r="B3" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C3">
@@ -3418,8 +1929,8 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="2"/>
-      <c r="B4" s="1" t="s">
+      <c r="A4" s="5"/>
+      <c r="B4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C4">
@@ -3442,8 +1953,8 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="2"/>
-      <c r="B5" s="1" t="s">
+      <c r="A5" s="5"/>
+      <c r="B5" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C5">
@@ -3466,8 +1977,8 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="3"/>
-      <c r="B6" s="1" t="s">
+      <c r="A6" s="6"/>
+      <c r="B6" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C6">
@@ -3490,10 +2001,10 @@
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C7">
@@ -3516,8 +2027,8 @@
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="2"/>
-      <c r="B8" s="1" t="s">
+      <c r="A8" s="5"/>
+      <c r="B8" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C8">
@@ -3540,8 +2051,8 @@
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="2"/>
-      <c r="B9" s="1" t="s">
+      <c r="A9" s="5"/>
+      <c r="B9" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C9">
@@ -3564,8 +2075,8 @@
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="2"/>
-      <c r="B10" s="1" t="s">
+      <c r="A10" s="5"/>
+      <c r="B10" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C10">
@@ -3588,8 +2099,8 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="3"/>
-      <c r="B11" s="1" t="s">
+      <c r="A11" s="6"/>
+      <c r="B11" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C11">
@@ -3621,43 +2132,43 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelRow="5" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C2">
@@ -3680,8 +2191,8 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1" t="s">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C3">
@@ -3704,8 +2215,8 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1" t="s">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C4">
@@ -3728,8 +2239,8 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1" t="s">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C5">
@@ -3752,8 +2263,8 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1" t="s">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C6">
@@ -3782,4 +2293,576 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6" outlineLevelCol="7"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2">
+        <v>99.9615669250488</v>
+      </c>
+      <c r="D2">
+        <v>99.9614536762238</v>
+      </c>
+      <c r="E2">
+        <v>99.929</v>
+      </c>
+      <c r="F2">
+        <v>99.929</v>
+      </c>
+      <c r="G2">
+        <v>99.929</v>
+      </c>
+      <c r="H2">
+        <v>99.929</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="2"/>
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3">
+        <v>99.9446153640747</v>
+      </c>
+      <c r="D3">
+        <v>99.9444544315338</v>
+      </c>
+      <c r="E3">
+        <v>99.96</v>
+      </c>
+      <c r="F3">
+        <v>99.96</v>
+      </c>
+      <c r="G3">
+        <v>99.96</v>
+      </c>
+      <c r="H3">
+        <v>99.96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="2"/>
+      <c r="B4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4">
+        <v>99.345526099205</v>
+      </c>
+      <c r="D4">
+        <v>99.3422150611877</v>
+      </c>
+      <c r="E4">
+        <v>99.589</v>
+      </c>
+      <c r="F4">
+        <v>99.589</v>
+      </c>
+      <c r="G4">
+        <v>99.589</v>
+      </c>
+      <c r="H4">
+        <v>99.591</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2"/>
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>99.9547898769379</v>
+      </c>
+      <c r="D5">
+        <v>99.9546527862549</v>
+      </c>
+      <c r="E5">
+        <v>99.551</v>
+      </c>
+      <c r="F5">
+        <v>99.551</v>
+      </c>
+      <c r="G5">
+        <v>99.551</v>
+      </c>
+      <c r="H5">
+        <v>99.552</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="3"/>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6">
+        <v>99.9706149101257</v>
+      </c>
+      <c r="D6">
+        <v>99.9705195426941</v>
+      </c>
+      <c r="E6">
+        <v>99.853</v>
+      </c>
+      <c r="F6">
+        <v>99.853</v>
+      </c>
+      <c r="G6">
+        <v>99.853</v>
+      </c>
+      <c r="H6">
+        <v>99.853</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>96.4461743831635</v>
+      </c>
+      <c r="D7">
+        <v>96.4397728443146</v>
+      </c>
+      <c r="E7">
+        <v>87.883</v>
+      </c>
+      <c r="F7">
+        <v>87.36</v>
+      </c>
+      <c r="G7">
+        <v>87.883</v>
+      </c>
+      <c r="H7">
+        <v>89.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="2"/>
+      <c r="B8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>95.5000698566437</v>
+      </c>
+      <c r="D8">
+        <v>95.4918324947357</v>
+      </c>
+      <c r="E8">
+        <v>92.294</v>
+      </c>
+      <c r="F8">
+        <v>91.827</v>
+      </c>
+      <c r="G8">
+        <v>92.294</v>
+      </c>
+      <c r="H8">
+        <v>92.968</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="2"/>
+      <c r="B9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>95.6673592329025</v>
+      </c>
+      <c r="D9">
+        <v>95.6646621227264</v>
+      </c>
+      <c r="E9">
+        <v>91.115</v>
+      </c>
+      <c r="F9">
+        <v>90.478</v>
+      </c>
+      <c r="G9">
+        <v>91.115</v>
+      </c>
+      <c r="H9">
+        <v>91.924</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="2"/>
+      <c r="B10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>97.0283031463623</v>
+      </c>
+      <c r="D10">
+        <v>97.037261724472</v>
+      </c>
+      <c r="E10">
+        <v>73.476</v>
+      </c>
+      <c r="F10">
+        <v>74.026</v>
+      </c>
+      <c r="G10">
+        <v>73.476</v>
+      </c>
+      <c r="H10">
+        <v>79.024</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="3"/>
+      <c r="B11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>89.6550178527832</v>
+      </c>
+      <c r="D11">
+        <v>89.8758232593536</v>
+      </c>
+      <c r="E11">
+        <v>86.773</v>
+      </c>
+      <c r="F11">
+        <v>85.769</v>
+      </c>
+      <c r="G11">
+        <v>86.773</v>
+      </c>
+      <c r="H11">
+        <v>87.658</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6" outlineLevelCol="7"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2">
+        <v>99.9276548624039</v>
+      </c>
+      <c r="D2">
+        <v>99.927294254303</v>
+      </c>
+      <c r="E2">
+        <v>99.864</v>
+      </c>
+      <c r="F2">
+        <v>99.864</v>
+      </c>
+      <c r="G2">
+        <v>99.864</v>
+      </c>
+      <c r="H2">
+        <v>99.864</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3">
+        <v>99.8394817113876</v>
+      </c>
+      <c r="D3">
+        <v>99.8387575149536</v>
+      </c>
+      <c r="E3">
+        <v>99.87</v>
+      </c>
+      <c r="F3">
+        <v>99.87</v>
+      </c>
+      <c r="G3">
+        <v>99.87</v>
+      </c>
+      <c r="H3">
+        <v>99.87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4">
+        <v>99.8914808034897</v>
+      </c>
+      <c r="D4">
+        <v>99.8909890651703</v>
+      </c>
+      <c r="E4">
+        <v>99.913</v>
+      </c>
+      <c r="F4">
+        <v>99.913</v>
+      </c>
+      <c r="G4">
+        <v>99.913</v>
+      </c>
+      <c r="H4">
+        <v>99.913</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>99.1137653589249</v>
+      </c>
+      <c r="D5">
+        <v>99.1086959838867</v>
+      </c>
+      <c r="E5">
+        <v>97.943</v>
+      </c>
+      <c r="F5">
+        <v>97.947</v>
+      </c>
+      <c r="G5">
+        <v>97.943</v>
+      </c>
+      <c r="H5">
+        <v>97.963</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6">
+        <v>99.8914808034897</v>
+      </c>
+      <c r="D6">
+        <v>99.8910009860992</v>
+      </c>
+      <c r="E6">
+        <v>99.722</v>
+      </c>
+      <c r="F6">
+        <v>99.722</v>
+      </c>
+      <c r="G6">
+        <v>99.722</v>
+      </c>
+      <c r="H6">
+        <v>99.722</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>93.2492315769196</v>
+      </c>
+      <c r="D7">
+        <v>93.1852996349335</v>
+      </c>
+      <c r="E7">
+        <v>83.237</v>
+      </c>
+      <c r="F7">
+        <v>82.209</v>
+      </c>
+      <c r="G7">
+        <v>83.237</v>
+      </c>
+      <c r="H7">
+        <v>85.137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>92.9078489542007</v>
+      </c>
+      <c r="D8">
+        <v>92.8485572338104</v>
+      </c>
+      <c r="E8">
+        <v>88.334</v>
+      </c>
+      <c r="F8">
+        <v>87.388</v>
+      </c>
+      <c r="G8">
+        <v>88.334</v>
+      </c>
+      <c r="H8">
+        <v>89.607</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>92.8739368915558</v>
+      </c>
+      <c r="D9">
+        <v>92.8263187408447</v>
+      </c>
+      <c r="E9">
+        <v>88.307</v>
+      </c>
+      <c r="F9">
+        <v>87.205</v>
+      </c>
+      <c r="G9">
+        <v>88.307</v>
+      </c>
+      <c r="H9">
+        <v>89.244</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>94.4384157657623</v>
+      </c>
+      <c r="D10">
+        <v>94.4093823432922</v>
+      </c>
+      <c r="E10">
+        <v>71.045</v>
+      </c>
+      <c r="F10">
+        <v>71.379</v>
+      </c>
+      <c r="G10">
+        <v>71.045</v>
+      </c>
+      <c r="H10">
+        <v>76.352</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>90.0321006774902</v>
+      </c>
+      <c r="D11">
+        <v>90.0094449520111</v>
+      </c>
+      <c r="E11">
+        <v>84.857</v>
+      </c>
+      <c r="F11">
+        <v>83.486</v>
+      </c>
+      <c r="G11">
+        <v>84.857</v>
+      </c>
+      <c r="H11">
+        <v>85.731</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/results/results.xlsx
+++ b/results/results.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -552,7 +552,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>kernel_size</t>
+          <t>out_channels</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
@@ -561,22 +561,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>99.51281547546387</v>
+        <v>96.00533545017242</v>
       </c>
       <c r="D2" t="n">
-        <v>99.5119571685791</v>
+        <v>96.02869749069214</v>
       </c>
       <c r="E2" t="n">
-        <v>99.361</v>
+        <v>83.321</v>
       </c>
       <c r="F2" t="n">
-        <v>99.361</v>
+        <v>82.636</v>
       </c>
       <c r="G2" t="n">
-        <v>99.361</v>
+        <v>83.321</v>
       </c>
       <c r="H2" t="n">
-        <v>99.36499999999999</v>
+        <v>84.681</v>
       </c>
     </row>
     <row r="3">
@@ -587,22 +587,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>98.94086122512817</v>
+        <v>95.73235809803009</v>
       </c>
       <c r="D3" t="n">
-        <v>98.99482727050781</v>
+        <v>95.74950337409973</v>
       </c>
       <c r="E3" t="n">
-        <v>99.286</v>
+        <v>88.58799999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>99.289</v>
+        <v>88.29300000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>99.286</v>
+        <v>88.58799999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>99.295</v>
+        <v>89.613</v>
       </c>
     </row>
     <row r="4">
@@ -613,22 +613,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>99.83949065208435</v>
+        <v>95.38929462432861</v>
       </c>
       <c r="D4" t="n">
-        <v>99.83908534049988</v>
+        <v>95.41730880737305</v>
       </c>
       <c r="E4" t="n">
-        <v>99.789</v>
+        <v>89.526</v>
       </c>
       <c r="F4" t="n">
-        <v>99.789</v>
+        <v>88.83799999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>99.789</v>
+        <v>89.526</v>
       </c>
       <c r="H4" t="n">
-        <v>99.789</v>
+        <v>90.42400000000001</v>
       </c>
     </row>
     <row r="5">
@@ -639,22 +639,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>99.79201555252075</v>
+        <v>96.5366005897522</v>
       </c>
       <c r="D5" t="n">
-        <v>99.79152679443359</v>
+        <v>96.56528830528259</v>
       </c>
       <c r="E5" t="n">
-        <v>99.015</v>
+        <v>66.04300000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>99.06999999999999</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>99.015</v>
+        <v>66.04300000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>99.205</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="6">
@@ -665,26 +665,161 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>71.26362025737762</v>
+      </c>
+      <c r="D6" t="n">
+        <v>73.08618426322937</v>
+      </c>
+      <c r="E6" t="n">
+        <v>84.786</v>
+      </c>
+      <c r="F6" t="n">
+        <v>84.203</v>
+      </c>
+      <c r="G6" t="n">
+        <v>84.786</v>
+      </c>
+      <c r="H6" t="n">
+        <v>86.236</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>kernel_size</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>99.51281547546387</v>
+      </c>
+      <c r="D7" t="n">
+        <v>99.5119571685791</v>
+      </c>
+      <c r="E7" t="n">
+        <v>99.361</v>
+      </c>
+      <c r="F7" t="n">
+        <v>99.361</v>
+      </c>
+      <c r="G7" t="n">
+        <v>99.361</v>
+      </c>
+      <c r="H7" t="n">
+        <v>99.36499999999999</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>98.94086122512817</v>
+      </c>
+      <c r="D8" t="n">
+        <v>98.99482727050781</v>
+      </c>
+      <c r="E8" t="n">
+        <v>99.286</v>
+      </c>
+      <c r="F8" t="n">
+        <v>99.289</v>
+      </c>
+      <c r="G8" t="n">
+        <v>99.286</v>
+      </c>
+      <c r="H8" t="n">
+        <v>99.295</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>99.83949065208435</v>
+      </c>
+      <c r="D9" t="n">
+        <v>99.83908534049988</v>
+      </c>
+      <c r="E9" t="n">
+        <v>99.789</v>
+      </c>
+      <c r="F9" t="n">
+        <v>99.789</v>
+      </c>
+      <c r="G9" t="n">
+        <v>99.789</v>
+      </c>
+      <c r="H9" t="n">
+        <v>99.789</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>99.79201555252075</v>
+      </c>
+      <c r="D10" t="n">
+        <v>99.79152679443359</v>
+      </c>
+      <c r="E10" t="n">
+        <v>99.015</v>
+      </c>
+      <c r="F10" t="n">
+        <v>99.06999999999999</v>
+      </c>
+      <c r="G10" t="n">
+        <v>99.015</v>
+      </c>
+      <c r="H10" t="n">
+        <v>99.205</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>99.85926747322083</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D11" t="n">
         <v>99.85884428024292</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E11" t="n">
         <v>99.562</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F11" t="n">
         <v>99.562</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G11" t="n">
         <v>99.562</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H11" t="n">
         <v>99.563</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A7:A11"/>
     <mergeCell ref="A2:A6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/results.xlsx
+++ b/results/results.xlsx
@@ -4,15 +4,19 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="15540" tabRatio="568" activeTab="5"/>
+    <workbookView windowWidth="30720" windowHeight="15540" tabRatio="860" activeTab="8"/>
   </bookViews>
   <sheets>
-    <sheet name="conv2d_O_regression" sheetId="5" r:id="rId1"/>
-    <sheet name="conv2d_T_regression" sheetId="6" r:id="rId2"/>
-    <sheet name="max_pool2d_T" sheetId="7" r:id="rId3"/>
-    <sheet name="linear_T_regression" sheetId="8" r:id="rId4"/>
-    <sheet name="conv2d_T_regression_half" sheetId="9" r:id="rId5"/>
-    <sheet name="conv2d_T_regression_quarter" sheetId="10" r:id="rId6"/>
+    <sheet name="conv2d" sheetId="6" r:id="rId1"/>
+    <sheet name="max_pool2d" sheetId="7" r:id="rId2"/>
+    <sheet name="linear" sheetId="8" r:id="rId3"/>
+    <sheet name="conv2d_O" sheetId="5" r:id="rId4"/>
+    <sheet name="conv2d_half" sheetId="9" r:id="rId5"/>
+    <sheet name="conv2d_quarter" sheetId="10" r:id="rId6"/>
+    <sheet name="conv2d_RAPL2" sheetId="11" r:id="rId7"/>
+    <sheet name="conv2d_RAPL1" sheetId="12" r:id="rId8"/>
+    <sheet name="abolation_demlp" sheetId="13" r:id="rId9"/>
+    <sheet name="abolation_deLvar" sheetId="14" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,12 +36,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="18">
   <si>
     <t>HyperParameters</t>
   </si>
   <si>
-    <t>Origin_domain_nums</t>
+    <t>test_domain</t>
   </si>
   <si>
     <t>VAL_ACC</t>
@@ -61,15 +65,6 @@
     <t>kernel_size</t>
   </si>
   <si>
-    <t>out_channels</t>
-  </si>
-  <si>
-    <t>stride</t>
-  </si>
-  <si>
-    <t>test_domain</t>
-  </si>
-  <si>
     <t>160</t>
   </si>
   <si>
@@ -85,7 +80,16 @@
     <t>331</t>
   </si>
   <si>
+    <t>out_channels</t>
+  </si>
+  <si>
+    <t>stride</t>
+  </si>
+  <si>
     <t>padding</t>
+  </si>
+  <si>
+    <t>Origin_domain_nums</t>
   </si>
 </sst>
 </file>
@@ -98,7 +102,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -109,6 +113,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -258,12 +269,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -615,55 +632,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
@@ -678,75 +692,84 @@
     <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -757,6 +780,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1103,378 +1127,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="7"/>
-  <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="4">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>99.9864399433136</v>
-      </c>
-      <c r="D2">
-        <v>99.9900281429291</v>
-      </c>
-      <c r="E2">
-        <v>95.181</v>
-      </c>
-      <c r="F2">
-        <v>95.212</v>
-      </c>
-      <c r="G2">
-        <v>95.181</v>
-      </c>
-      <c r="H2">
-        <v>95.355</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="5"/>
-      <c r="B3" s="4">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>99.9875664710999</v>
-      </c>
-      <c r="D3">
-        <v>99.9908626079559</v>
-      </c>
-      <c r="E3">
-        <v>98.503</v>
-      </c>
-      <c r="F3">
-        <v>98.498</v>
-      </c>
-      <c r="G3">
-        <v>98.503</v>
-      </c>
-      <c r="H3">
-        <v>98.518</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="5"/>
-      <c r="B4" s="4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>99.9902039766312</v>
-      </c>
-      <c r="D4">
-        <v>99.9927997589111</v>
-      </c>
-      <c r="E4">
-        <v>98.631</v>
-      </c>
-      <c r="F4">
-        <v>98.627</v>
-      </c>
-      <c r="G4">
-        <v>98.631</v>
-      </c>
-      <c r="H4">
-        <v>98.643</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="6"/>
-      <c r="B5" s="4">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>99.9819159507751</v>
-      </c>
-      <c r="D5">
-        <v>99.9867081642151</v>
-      </c>
-      <c r="E5">
-        <v>99.904</v>
-      </c>
-      <c r="F5">
-        <v>99.904</v>
-      </c>
-      <c r="G5">
-        <v>99.904</v>
-      </c>
-      <c r="H5">
-        <v>99.904</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="4">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>98.8420270684827</v>
-      </c>
-      <c r="D6">
-        <v>98.2860435123388</v>
-      </c>
-      <c r="E6">
-        <v>79.427</v>
-      </c>
-      <c r="F6">
-        <v>75.417</v>
-      </c>
-      <c r="G6">
-        <v>79.427</v>
-      </c>
-      <c r="H6">
-        <v>76.396</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="5"/>
-      <c r="B7" s="4">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>99.0813490800086</v>
-      </c>
-      <c r="D7">
-        <v>98.6454575478686</v>
-      </c>
-      <c r="E7">
-        <v>81.733</v>
-      </c>
-      <c r="F7">
-        <v>77.542</v>
-      </c>
-      <c r="G7">
-        <v>81.733</v>
-      </c>
-      <c r="H7">
-        <v>77.425</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="5"/>
-      <c r="B8" s="4">
-        <v>3</v>
-      </c>
-      <c r="C8">
-        <v>98.9600542799831</v>
-      </c>
-      <c r="D8">
-        <v>98.5175557858459</v>
-      </c>
-      <c r="E8">
-        <v>84.992</v>
-      </c>
-      <c r="F8">
-        <v>83.059</v>
-      </c>
-      <c r="G8">
-        <v>84.992</v>
-      </c>
-      <c r="H8">
-        <v>86.354</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="6"/>
-      <c r="B9" s="4">
-        <v>4</v>
-      </c>
-      <c r="C9">
-        <v>99.125760276509</v>
-      </c>
-      <c r="D9">
-        <v>98.8067030777383</v>
-      </c>
-      <c r="E9">
-        <v>95.97</v>
-      </c>
-      <c r="F9">
-        <v>95.859</v>
-      </c>
-      <c r="G9">
-        <v>95.97</v>
-      </c>
-      <c r="H9">
-        <v>96.048</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="4">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>99.9186158180237</v>
-      </c>
-      <c r="D10">
-        <v>99.7906684875488</v>
-      </c>
-      <c r="E10">
-        <v>97.564</v>
-      </c>
-      <c r="F10">
-        <v>97.469</v>
-      </c>
-      <c r="G10">
-        <v>97.564</v>
-      </c>
-      <c r="H10">
-        <v>97.543</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="5"/>
-      <c r="B11" s="4">
-        <v>2</v>
-      </c>
-      <c r="C11">
-        <v>99.9344408512115</v>
-      </c>
-      <c r="D11">
-        <v>99.8314917087555</v>
-      </c>
-      <c r="E11">
-        <v>98.433</v>
-      </c>
-      <c r="F11">
-        <v>98.388</v>
-      </c>
-      <c r="G11">
-        <v>98.433</v>
-      </c>
-      <c r="H11">
-        <v>98.439</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="5"/>
-      <c r="B12" s="4">
-        <v>3</v>
-      </c>
-      <c r="C12">
-        <v>99.9540328979492</v>
-      </c>
-      <c r="D12">
-        <v>99.881899356842</v>
-      </c>
-      <c r="E12">
-        <v>98.547</v>
-      </c>
-      <c r="F12">
-        <v>98.508</v>
-      </c>
-      <c r="G12">
-        <v>98.547</v>
-      </c>
-      <c r="H12">
-        <v>98.554</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="6"/>
-      <c r="B13" s="4">
-        <v>4</v>
-      </c>
-      <c r="C13">
-        <v>99.945741891861</v>
-      </c>
-      <c r="D13">
-        <v>99.8603463172913</v>
-      </c>
-      <c r="E13">
-        <v>99.931</v>
-      </c>
-      <c r="F13">
-        <v>99.931</v>
-      </c>
-      <c r="G13">
-        <v>99.931</v>
-      </c>
-      <c r="H13">
-        <v>99.931</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>12</v>
+      <c r="B2" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="C2">
         <v>99.9920904636383</v>
@@ -1496,9 +1183,9 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="5"/>
-      <c r="B3" s="4" t="s">
-        <v>13</v>
+      <c r="A3" s="7"/>
+      <c r="B3" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="C3">
         <v>99.9858677387238</v>
@@ -1520,9 +1207,9 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="5"/>
-      <c r="B4" s="4" t="s">
-        <v>14</v>
+      <c r="A4" s="7"/>
+      <c r="B4" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C4">
         <v>99.988129734993</v>
@@ -1544,9 +1231,9 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="5"/>
-      <c r="B5" s="4" t="s">
-        <v>15</v>
+      <c r="A5" s="7"/>
+      <c r="B5" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="C5">
         <v>99.9875664710999</v>
@@ -1568,9 +1255,9 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="6"/>
-      <c r="B6" s="4" t="s">
-        <v>16</v>
+      <c r="A6" s="8"/>
+      <c r="B6" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="C6">
         <v>99.9819159507751</v>
@@ -1592,11 +1279,11 @@
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>9</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>12</v>
       </c>
       <c r="C7">
         <v>99.1016938345034</v>
@@ -1618,9 +1305,9 @@
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="5"/>
-      <c r="B8" s="4" t="s">
-        <v>13</v>
+      <c r="A8" s="7"/>
+      <c r="B8" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="C8">
         <v>98.9718300272224</v>
@@ -1642,9 +1329,9 @@
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="5"/>
-      <c r="B9" s="4" t="s">
-        <v>14</v>
+      <c r="A9" s="7"/>
+      <c r="B9" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C9">
         <v>99.0644134888163</v>
@@ -1666,9 +1353,9 @@
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="5"/>
-      <c r="B10" s="4" t="s">
-        <v>15</v>
+      <c r="A10" s="7"/>
+      <c r="B10" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="C10">
         <v>99.1609923299119</v>
@@ -1690,9 +1377,9 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="6"/>
-      <c r="B11" s="4" t="s">
-        <v>16</v>
+      <c r="A11" s="8"/>
+      <c r="B11" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="C11">
         <v>99.125760276509</v>
@@ -1714,11 +1401,11 @@
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>12</v>
+      <c r="A12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="C12">
         <v>99.9559164047241</v>
@@ -1740,9 +1427,9 @@
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="5"/>
-      <c r="B13" s="4" t="s">
-        <v>13</v>
+      <c r="A13" s="7"/>
+      <c r="B13" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="C13">
         <v>99.9197423458099</v>
@@ -1764,9 +1451,9 @@
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="5"/>
-      <c r="B14" s="4" t="s">
-        <v>14</v>
+      <c r="A14" s="7"/>
+      <c r="B14" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C14">
         <v>99.9107003211975</v>
@@ -1788,9 +1475,9 @@
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="5"/>
-      <c r="B15" s="4" t="s">
-        <v>15</v>
+      <c r="A15" s="7"/>
+      <c r="B15" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="C15">
         <v>99.9197423458099</v>
@@ -1801,7 +1488,7 @@
       <c r="E15">
         <v>93.002</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="9">
         <v>93.584</v>
       </c>
       <c r="G15">
@@ -1812,9 +1499,9 @@
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="6"/>
-      <c r="B16" s="4" t="s">
-        <v>16</v>
+      <c r="A16" s="8"/>
+      <c r="B16" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="C16">
         <v>99.945741891861</v>
@@ -1846,44 +1533,207 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6" outlineLevelRow="5" outlineLevelCol="7"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2">
+        <v>98.2603847980499</v>
+      </c>
+      <c r="D2" s="2">
+        <v>97.7003276348114</v>
+      </c>
+      <c r="E2" s="2">
+        <v>98.512</v>
+      </c>
+      <c r="F2" s="2">
+        <v>97.934</v>
+      </c>
+      <c r="G2" s="2">
+        <v>98.512</v>
+      </c>
+      <c r="H2" s="2">
+        <v>97.372</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2">
+        <v>98.2507824897766</v>
+      </c>
+      <c r="D3" s="2">
+        <v>97.6907432079315</v>
+      </c>
+      <c r="E3" s="2">
+        <v>98.617</v>
+      </c>
+      <c r="F3" s="2">
+        <v>98.038</v>
+      </c>
+      <c r="G3" s="2">
+        <v>98.617</v>
+      </c>
+      <c r="H3" s="2">
+        <v>97.472</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2">
+        <v>98.2547342777252</v>
+      </c>
+      <c r="D4" s="2">
+        <v>97.6948022842407</v>
+      </c>
+      <c r="E4" s="2">
+        <v>98.436</v>
+      </c>
+      <c r="F4" s="2">
+        <v>97.857</v>
+      </c>
+      <c r="G4" s="2">
+        <v>98.436</v>
+      </c>
+      <c r="H4" s="2">
+        <v>97.29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2">
+        <v>98.3999848365784</v>
+      </c>
+      <c r="D5" s="2">
+        <v>97.8393852710724</v>
+      </c>
+      <c r="E5" s="2">
+        <v>97.033</v>
+      </c>
+      <c r="F5" s="2">
+        <v>96.461</v>
+      </c>
+      <c r="G5" s="2">
+        <v>97.033</v>
+      </c>
+      <c r="H5" s="2">
+        <v>95.899</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="2">
+        <v>98.4169453382492</v>
+      </c>
+      <c r="D6" s="2">
+        <v>97.8559136390686</v>
+      </c>
+      <c r="E6" s="2">
+        <v>97.752</v>
+      </c>
+      <c r="F6" s="2">
+        <v>97.177</v>
+      </c>
+      <c r="G6" s="2">
+        <v>97.752</v>
+      </c>
+      <c r="H6" s="2">
+        <v>96.622</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>12</v>
+      <c r="B2" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -1905,9 +1755,9 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="5"/>
-      <c r="B3" s="4" t="s">
-        <v>13</v>
+      <c r="A3" s="7"/>
+      <c r="B3" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="C3">
         <v>100</v>
@@ -1929,9 +1779,9 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="5"/>
-      <c r="B4" s="4" t="s">
-        <v>14</v>
+      <c r="A4" s="7"/>
+      <c r="B4" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -1953,9 +1803,9 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="5"/>
-      <c r="B5" s="4" t="s">
-        <v>15</v>
+      <c r="A5" s="7"/>
+      <c r="B5" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -1977,35 +1827,35 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="6"/>
-      <c r="B6" s="4" t="s">
+      <c r="A6" s="8"/>
+      <c r="B6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+      <c r="D6">
+        <v>100</v>
+      </c>
+      <c r="E6">
+        <v>100</v>
+      </c>
+      <c r="F6">
+        <v>100</v>
+      </c>
+      <c r="G6">
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C6">
-        <v>100</v>
-      </c>
-      <c r="D6">
-        <v>100</v>
-      </c>
-      <c r="E6">
-        <v>100</v>
-      </c>
-      <c r="F6">
-        <v>100</v>
-      </c>
-      <c r="G6">
-        <v>100</v>
-      </c>
-      <c r="H6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>12</v>
+      <c r="B7" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -2027,81 +1877,81 @@
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="5"/>
-      <c r="B8" s="4" t="s">
+      <c r="A8" s="7"/>
+      <c r="B8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>100</v>
+      </c>
+      <c r="D8">
+        <v>100</v>
+      </c>
+      <c r="E8">
+        <v>100</v>
+      </c>
+      <c r="F8">
+        <v>100</v>
+      </c>
+      <c r="G8">
+        <v>100</v>
+      </c>
+      <c r="H8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="7"/>
+      <c r="B9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>100</v>
+      </c>
+      <c r="D9">
+        <v>100</v>
+      </c>
+      <c r="E9">
+        <v>100</v>
+      </c>
+      <c r="F9">
+        <v>100</v>
+      </c>
+      <c r="G9">
+        <v>100</v>
+      </c>
+      <c r="H9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="7"/>
+      <c r="B10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>100</v>
+      </c>
+      <c r="D10">
+        <v>100</v>
+      </c>
+      <c r="E10">
+        <v>100</v>
+      </c>
+      <c r="F10">
+        <v>100</v>
+      </c>
+      <c r="G10">
+        <v>100</v>
+      </c>
+      <c r="H10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="8"/>
+      <c r="B11" s="6" t="s">
         <v>13</v>
-      </c>
-      <c r="C8">
-        <v>100</v>
-      </c>
-      <c r="D8">
-        <v>100</v>
-      </c>
-      <c r="E8">
-        <v>100</v>
-      </c>
-      <c r="F8">
-        <v>100</v>
-      </c>
-      <c r="G8">
-        <v>100</v>
-      </c>
-      <c r="H8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="5"/>
-      <c r="B9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9">
-        <v>100</v>
-      </c>
-      <c r="D9">
-        <v>100</v>
-      </c>
-      <c r="E9">
-        <v>100</v>
-      </c>
-      <c r="F9">
-        <v>100</v>
-      </c>
-      <c r="G9">
-        <v>100</v>
-      </c>
-      <c r="H9">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="5"/>
-      <c r="B10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10">
-        <v>100</v>
-      </c>
-      <c r="D10">
-        <v>100</v>
-      </c>
-      <c r="E10">
-        <v>100</v>
-      </c>
-      <c r="F10">
-        <v>100</v>
-      </c>
-      <c r="G10">
-        <v>100</v>
-      </c>
-      <c r="H10">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="6"/>
-      <c r="B11" s="4" t="s">
-        <v>16</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -2132,44 +1982,44 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelRow="5" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>9</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>12</v>
       </c>
       <c r="C2">
         <v>99.9794125556946</v>
@@ -2191,9 +2041,9 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4" t="s">
-        <v>13</v>
+      <c r="A3" s="6"/>
+      <c r="B3" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="C3">
         <v>100</v>
@@ -2215,9 +2065,9 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4" t="s">
-        <v>14</v>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C4">
         <v>99.9794006347656</v>
@@ -2239,9 +2089,9 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4" t="s">
-        <v>15</v>
+      <c r="A5" s="6"/>
+      <c r="B5" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -2263,9 +2113,9 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4" t="s">
-        <v>16</v>
+      <c r="A6" s="6"/>
+      <c r="B6" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -2289,6 +2139,343 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:A6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="7"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="6">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>99.9864399433136</v>
+      </c>
+      <c r="D2">
+        <v>99.9900281429291</v>
+      </c>
+      <c r="E2">
+        <v>95.181</v>
+      </c>
+      <c r="F2">
+        <v>95.212</v>
+      </c>
+      <c r="G2">
+        <v>95.181</v>
+      </c>
+      <c r="H2">
+        <v>95.355</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="7"/>
+      <c r="B3" s="6">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>99.9875664710999</v>
+      </c>
+      <c r="D3">
+        <v>99.9908626079559</v>
+      </c>
+      <c r="E3">
+        <v>98.503</v>
+      </c>
+      <c r="F3">
+        <v>98.498</v>
+      </c>
+      <c r="G3">
+        <v>98.503</v>
+      </c>
+      <c r="H3">
+        <v>98.518</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="7"/>
+      <c r="B4" s="6">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>99.9902039766312</v>
+      </c>
+      <c r="D4">
+        <v>99.9927997589111</v>
+      </c>
+      <c r="E4">
+        <v>98.631</v>
+      </c>
+      <c r="F4">
+        <v>98.627</v>
+      </c>
+      <c r="G4">
+        <v>98.631</v>
+      </c>
+      <c r="H4">
+        <v>98.643</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="8"/>
+      <c r="B5" s="6">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>99.9819159507751</v>
+      </c>
+      <c r="D5">
+        <v>99.9867081642151</v>
+      </c>
+      <c r="E5">
+        <v>99.904</v>
+      </c>
+      <c r="F5">
+        <v>99.904</v>
+      </c>
+      <c r="G5">
+        <v>99.904</v>
+      </c>
+      <c r="H5">
+        <v>99.904</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>98.8420270684827</v>
+      </c>
+      <c r="D6">
+        <v>98.2860435123388</v>
+      </c>
+      <c r="E6">
+        <v>79.427</v>
+      </c>
+      <c r="F6">
+        <v>75.417</v>
+      </c>
+      <c r="G6">
+        <v>79.427</v>
+      </c>
+      <c r="H6">
+        <v>76.396</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="7"/>
+      <c r="B7" s="6">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>99.0813490800086</v>
+      </c>
+      <c r="D7">
+        <v>98.6454575478686</v>
+      </c>
+      <c r="E7">
+        <v>81.733</v>
+      </c>
+      <c r="F7">
+        <v>77.542</v>
+      </c>
+      <c r="G7">
+        <v>81.733</v>
+      </c>
+      <c r="H7">
+        <v>77.425</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="7"/>
+      <c r="B8" s="6">
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <v>98.9600542799831</v>
+      </c>
+      <c r="D8">
+        <v>98.5175557858459</v>
+      </c>
+      <c r="E8">
+        <v>84.992</v>
+      </c>
+      <c r="F8">
+        <v>83.059</v>
+      </c>
+      <c r="G8">
+        <v>84.992</v>
+      </c>
+      <c r="H8">
+        <v>86.354</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="8"/>
+      <c r="B9" s="6">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>99.125760276509</v>
+      </c>
+      <c r="D9">
+        <v>98.8067030777383</v>
+      </c>
+      <c r="E9">
+        <v>95.97</v>
+      </c>
+      <c r="F9">
+        <v>95.859</v>
+      </c>
+      <c r="G9">
+        <v>95.97</v>
+      </c>
+      <c r="H9">
+        <v>96.048</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="6">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>99.9186158180237</v>
+      </c>
+      <c r="D10">
+        <v>99.7906684875488</v>
+      </c>
+      <c r="E10">
+        <v>97.564</v>
+      </c>
+      <c r="F10">
+        <v>97.469</v>
+      </c>
+      <c r="G10">
+        <v>97.564</v>
+      </c>
+      <c r="H10">
+        <v>97.543</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="7"/>
+      <c r="B11" s="6">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>99.9344408512115</v>
+      </c>
+      <c r="D11">
+        <v>99.8314917087555</v>
+      </c>
+      <c r="E11">
+        <v>98.433</v>
+      </c>
+      <c r="F11">
+        <v>98.388</v>
+      </c>
+      <c r="G11">
+        <v>98.433</v>
+      </c>
+      <c r="H11">
+        <v>98.439</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="7"/>
+      <c r="B12" s="6">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>99.9540328979492</v>
+      </c>
+      <c r="D12">
+        <v>99.881899356842</v>
+      </c>
+      <c r="E12">
+        <v>98.547</v>
+      </c>
+      <c r="F12">
+        <v>98.508</v>
+      </c>
+      <c r="G12">
+        <v>98.547</v>
+      </c>
+      <c r="H12">
+        <v>98.554</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="8"/>
+      <c r="B13" s="6">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>99.945741891861</v>
+      </c>
+      <c r="D13">
+        <v>99.8603463172913</v>
+      </c>
+      <c r="E13">
+        <v>99.931</v>
+      </c>
+      <c r="F13">
+        <v>99.931</v>
+      </c>
+      <c r="G13">
+        <v>99.931</v>
+      </c>
+      <c r="H13">
+        <v>99.931</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2302,37 +2489,37 @@
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
+      <c r="B2" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="C2">
         <v>99.9615669250488</v>
@@ -2354,9 +2541,9 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="2"/>
-      <c r="B3" s="1" t="s">
-        <v>13</v>
+      <c r="A3" s="7"/>
+      <c r="B3" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="C3">
         <v>99.9446153640747</v>
@@ -2378,9 +2565,9 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="2"/>
-      <c r="B4" s="1" t="s">
-        <v>14</v>
+      <c r="A4" s="7"/>
+      <c r="B4" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C4">
         <v>99.345526099205</v>
@@ -2402,9 +2589,9 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="2"/>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
+      <c r="A5" s="7"/>
+      <c r="B5" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="C5">
         <v>99.9547898769379</v>
@@ -2426,9 +2613,9 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="3"/>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
+      <c r="A6" s="8"/>
+      <c r="B6" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="C6">
         <v>99.9706149101257</v>
@@ -2450,11 +2637,11 @@
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>9</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C7">
         <v>96.4461743831635</v>
@@ -2476,9 +2663,9 @@
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="2"/>
-      <c r="B8" s="1" t="s">
-        <v>13</v>
+      <c r="A8" s="7"/>
+      <c r="B8" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="C8">
         <v>95.5000698566437</v>
@@ -2500,9 +2687,9 @@
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="2"/>
-      <c r="B9" s="1" t="s">
-        <v>14</v>
+      <c r="A9" s="7"/>
+      <c r="B9" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C9">
         <v>95.6673592329025</v>
@@ -2524,9 +2711,9 @@
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="2"/>
-      <c r="B10" s="1" t="s">
-        <v>15</v>
+      <c r="A10" s="7"/>
+      <c r="B10" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="C10">
         <v>97.0283031463623</v>
@@ -2548,9 +2735,9 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="3"/>
-      <c r="B11" s="1" t="s">
-        <v>16</v>
+      <c r="A11" s="8"/>
+      <c r="B11" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="C11">
         <v>89.6550178527832</v>
@@ -2588,11 +2775,869 @@
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2">
+        <v>99.9276548624039</v>
+      </c>
+      <c r="D2">
+        <v>99.927294254303</v>
+      </c>
+      <c r="E2">
+        <v>99.864</v>
+      </c>
+      <c r="F2">
+        <v>99.864</v>
+      </c>
+      <c r="G2">
+        <v>99.864</v>
+      </c>
+      <c r="H2">
+        <v>99.864</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>99.8394817113876</v>
+      </c>
+      <c r="D3">
+        <v>99.8387575149536</v>
+      </c>
+      <c r="E3">
+        <v>99.87</v>
+      </c>
+      <c r="F3">
+        <v>99.87</v>
+      </c>
+      <c r="G3">
+        <v>99.87</v>
+      </c>
+      <c r="H3">
+        <v>99.87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>99.8914808034897</v>
+      </c>
+      <c r="D4">
+        <v>99.8909890651703</v>
+      </c>
+      <c r="E4">
+        <v>99.913</v>
+      </c>
+      <c r="F4">
+        <v>99.913</v>
+      </c>
+      <c r="G4">
+        <v>99.913</v>
+      </c>
+      <c r="H4">
+        <v>99.913</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>99.1137653589249</v>
+      </c>
+      <c r="D5">
+        <v>99.1086959838867</v>
+      </c>
+      <c r="E5">
+        <v>97.943</v>
+      </c>
+      <c r="F5">
+        <v>97.947</v>
+      </c>
+      <c r="G5">
+        <v>97.943</v>
+      </c>
+      <c r="H5">
+        <v>97.963</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6">
+        <v>99.8914808034897</v>
+      </c>
+      <c r="D6">
+        <v>99.8910009860992</v>
+      </c>
+      <c r="E6">
+        <v>99.722</v>
+      </c>
+      <c r="F6">
+        <v>99.722</v>
+      </c>
+      <c r="G6">
+        <v>99.722</v>
+      </c>
+      <c r="H6">
+        <v>99.722</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>93.2492315769196</v>
+      </c>
+      <c r="D7">
+        <v>93.1852996349335</v>
+      </c>
+      <c r="E7">
+        <v>83.237</v>
+      </c>
+      <c r="F7">
+        <v>82.209</v>
+      </c>
+      <c r="G7">
+        <v>83.237</v>
+      </c>
+      <c r="H7">
+        <v>85.137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>92.9078489542007</v>
+      </c>
+      <c r="D8">
+        <v>92.8485572338104</v>
+      </c>
+      <c r="E8">
+        <v>88.334</v>
+      </c>
+      <c r="F8">
+        <v>87.388</v>
+      </c>
+      <c r="G8">
+        <v>88.334</v>
+      </c>
+      <c r="H8">
+        <v>89.607</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>92.8739368915558</v>
+      </c>
+      <c r="D9">
+        <v>92.8263187408447</v>
+      </c>
+      <c r="E9">
+        <v>88.307</v>
+      </c>
+      <c r="F9">
+        <v>87.205</v>
+      </c>
+      <c r="G9">
+        <v>88.307</v>
+      </c>
+      <c r="H9">
+        <v>89.244</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>94.4384157657623</v>
+      </c>
+      <c r="D10">
+        <v>94.4093823432922</v>
+      </c>
+      <c r="E10">
+        <v>71.045</v>
+      </c>
+      <c r="F10">
+        <v>71.379</v>
+      </c>
+      <c r="G10">
+        <v>71.045</v>
+      </c>
+      <c r="H10">
+        <v>76.352</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11">
+        <v>90.0321006774902</v>
+      </c>
+      <c r="D11">
+        <v>90.0094449520111</v>
+      </c>
+      <c r="E11">
+        <v>84.857</v>
+      </c>
+      <c r="F11">
+        <v>83.486</v>
+      </c>
+      <c r="G11">
+        <v>84.857</v>
+      </c>
+      <c r="H11">
+        <v>85.731</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6" outlineLevelCol="7"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2">
+        <v>99.9338775873184</v>
+      </c>
+      <c r="D2">
+        <v>99.933660030365</v>
+      </c>
+      <c r="E2">
+        <v>99.662</v>
+      </c>
+      <c r="F2">
+        <v>99.662</v>
+      </c>
+      <c r="G2">
+        <v>99.662</v>
+      </c>
+      <c r="H2">
+        <v>99.664</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="4"/>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>99.9451786279678</v>
+      </c>
+      <c r="D3">
+        <v>99.9450147151947</v>
+      </c>
+      <c r="E3">
+        <v>99.899</v>
+      </c>
+      <c r="F3">
+        <v>99.899</v>
+      </c>
+      <c r="G3">
+        <v>99.899</v>
+      </c>
+      <c r="H3">
+        <v>99.899</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="4"/>
+      <c r="B4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>99.9570429325104</v>
+      </c>
+      <c r="D4">
+        <v>99.9568998813629</v>
+      </c>
+      <c r="E4">
+        <v>99.815</v>
+      </c>
+      <c r="F4">
+        <v>99.815</v>
+      </c>
+      <c r="G4">
+        <v>99.815</v>
+      </c>
+      <c r="H4">
+        <v>99.815</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="4"/>
+      <c r="B5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>99.9632656574249</v>
+      </c>
+      <c r="D5">
+        <v>99.9631762504578</v>
+      </c>
+      <c r="E5">
+        <v>99.209</v>
+      </c>
+      <c r="F5">
+        <v>99.208</v>
+      </c>
+      <c r="G5">
+        <v>99.209</v>
+      </c>
+      <c r="H5">
+        <v>99.211</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="5"/>
+      <c r="B6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6">
+        <v>99.9576151371002</v>
+      </c>
+      <c r="D6">
+        <v>99.9574899673462</v>
+      </c>
+      <c r="E6">
+        <v>99.792</v>
+      </c>
+      <c r="F6">
+        <v>99.792</v>
+      </c>
+      <c r="G6">
+        <v>99.792</v>
+      </c>
+      <c r="H6">
+        <v>99.792</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>97.2656786441803</v>
+      </c>
+      <c r="D7">
+        <v>97.2638964653015</v>
+      </c>
+      <c r="E7">
+        <v>88.706</v>
+      </c>
+      <c r="F7">
+        <v>88.3</v>
+      </c>
+      <c r="G7">
+        <v>88.706</v>
+      </c>
+      <c r="H7">
+        <v>90.109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="4"/>
+      <c r="B8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>96.6971129179001</v>
+      </c>
+      <c r="D8">
+        <v>96.7011988162994</v>
+      </c>
+      <c r="E8">
+        <v>92.095</v>
+      </c>
+      <c r="F8">
+        <v>91.848</v>
+      </c>
+      <c r="G8">
+        <v>92.095</v>
+      </c>
+      <c r="H8">
+        <v>92.639</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="4"/>
+      <c r="B9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>96.3619619607925</v>
+      </c>
+      <c r="D9">
+        <v>96.3698387145996</v>
+      </c>
+      <c r="E9">
+        <v>91.269</v>
+      </c>
+      <c r="F9">
+        <v>90.604</v>
+      </c>
+      <c r="G9">
+        <v>91.269</v>
+      </c>
+      <c r="H9">
+        <v>92.09</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="4"/>
+      <c r="B10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>97.6087421178818</v>
+      </c>
+      <c r="D10">
+        <v>97.6225078105927</v>
+      </c>
+      <c r="E10">
+        <v>76.424</v>
+      </c>
+      <c r="F10">
+        <v>75.775</v>
+      </c>
+      <c r="G10">
+        <v>76.424</v>
+      </c>
+      <c r="H10">
+        <v>80.597</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="5"/>
+      <c r="B11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11">
+        <v>90.330970287323</v>
+      </c>
+      <c r="D11">
+        <v>90.5585944652557</v>
+      </c>
+      <c r="E11">
+        <v>90.105</v>
+      </c>
+      <c r="F11">
+        <v>89.66</v>
+      </c>
+      <c r="G11">
+        <v>90.105</v>
+      </c>
+      <c r="H11">
+        <v>90.509</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6" outlineLevelCol="7"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2">
+        <v>99.921441078186</v>
+      </c>
+      <c r="D2">
+        <v>99.9213099479675</v>
+      </c>
+      <c r="E2">
+        <v>99.7</v>
+      </c>
+      <c r="F2">
+        <v>99.699</v>
+      </c>
+      <c r="G2">
+        <v>99.7</v>
+      </c>
+      <c r="H2">
+        <v>99.701</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>99.8767912387848</v>
+      </c>
+      <c r="D3">
+        <v>99.876457452774</v>
+      </c>
+      <c r="E3">
+        <v>99.835</v>
+      </c>
+      <c r="F3">
+        <v>99.834</v>
+      </c>
+      <c r="G3">
+        <v>99.835</v>
+      </c>
+      <c r="H3">
+        <v>99.835</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>99.6026784181595</v>
+      </c>
+      <c r="D4">
+        <v>99.6010065078735</v>
+      </c>
+      <c r="E4">
+        <v>99.894</v>
+      </c>
+      <c r="F4">
+        <v>99.894</v>
+      </c>
+      <c r="G4">
+        <v>99.894</v>
+      </c>
+      <c r="H4">
+        <v>99.894</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>99.8914897441864</v>
+      </c>
+      <c r="D5">
+        <v>99.8912274837494</v>
+      </c>
+      <c r="E5">
+        <v>98.629</v>
+      </c>
+      <c r="F5">
+        <v>98.79</v>
+      </c>
+      <c r="G5">
+        <v>98.629</v>
+      </c>
+      <c r="H5">
+        <v>99.137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6">
+        <v>99.8553156852722</v>
+      </c>
+      <c r="D6">
+        <v>99.8549282550812</v>
+      </c>
+      <c r="E6">
+        <v>99.693</v>
+      </c>
+      <c r="F6">
+        <v>99.693</v>
+      </c>
+      <c r="G6">
+        <v>99.693</v>
+      </c>
+      <c r="H6">
+        <v>99.694</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7">
+        <v>96.0437715053558</v>
+      </c>
+      <c r="D7">
+        <v>96.0088789463043</v>
+      </c>
+      <c r="E7">
+        <v>93.141</v>
+      </c>
+      <c r="F7">
+        <v>92.929</v>
+      </c>
+      <c r="G7">
+        <v>93.141</v>
+      </c>
+      <c r="H7">
+        <v>93.356</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>96.2670117616653</v>
+      </c>
+      <c r="D8">
+        <v>96.2429821491241</v>
+      </c>
+      <c r="E8">
+        <v>95.31</v>
+      </c>
+      <c r="F8">
+        <v>95.076</v>
+      </c>
+      <c r="G8">
+        <v>95.31</v>
+      </c>
+      <c r="H8">
+        <v>95.436</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>95.7363098859787</v>
+      </c>
+      <c r="D9">
+        <v>95.7019865512848</v>
+      </c>
+      <c r="E9">
+        <v>92.242</v>
+      </c>
+      <c r="F9">
+        <v>91.951</v>
+      </c>
+      <c r="G9">
+        <v>92.242</v>
+      </c>
+      <c r="H9">
+        <v>92.58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>97.3821043968201</v>
+      </c>
+      <c r="D10">
+        <v>97.3456621170044</v>
+      </c>
+      <c r="E10">
+        <v>77.885</v>
+      </c>
+      <c r="F10">
+        <v>77.689</v>
+      </c>
+      <c r="G10">
+        <v>77.885</v>
+      </c>
+      <c r="H10">
+        <v>80.87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11">
+        <v>77.0775854587555</v>
+      </c>
+      <c r="D11">
+        <v>78.0784487724304</v>
+      </c>
+      <c r="E11">
+        <v>76.464</v>
+      </c>
+      <c r="F11">
+        <v>75.923</v>
+      </c>
+      <c r="G11">
+        <v>76.464</v>
+      </c>
+      <c r="H11">
+        <v>78.279</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6" outlineLevelCol="7"/>
+  <sheetData>
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -2615,246 +3660,246 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2">
-        <v>99.9276548624039</v>
-      </c>
-      <c r="D2">
-        <v>99.927294254303</v>
-      </c>
-      <c r="E2">
-        <v>99.864</v>
-      </c>
-      <c r="F2">
-        <v>99.864</v>
-      </c>
-      <c r="G2">
-        <v>99.864</v>
-      </c>
-      <c r="H2">
-        <v>99.864</v>
+        <v>9</v>
+      </c>
+      <c r="C2" s="2">
+        <v>96.0053354501724</v>
+      </c>
+      <c r="D2" s="2">
+        <v>96.0286974906921</v>
+      </c>
+      <c r="E2" s="2">
+        <v>83.321</v>
+      </c>
+      <c r="F2" s="2">
+        <v>82.636</v>
+      </c>
+      <c r="G2" s="2">
+        <v>83.321</v>
+      </c>
+      <c r="H2" s="2">
+        <v>84.681</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3">
-        <v>99.8394817113876</v>
-      </c>
-      <c r="D3">
-        <v>99.8387575149536</v>
-      </c>
-      <c r="E3">
-        <v>99.87</v>
-      </c>
-      <c r="F3">
-        <v>99.87</v>
-      </c>
-      <c r="G3">
-        <v>99.87</v>
-      </c>
-      <c r="H3">
-        <v>99.87</v>
+        <v>10</v>
+      </c>
+      <c r="C3" s="2">
+        <v>95.7323580980301</v>
+      </c>
+      <c r="D3" s="2">
+        <v>95.7495033740997</v>
+      </c>
+      <c r="E3" s="2">
+        <v>88.588</v>
+      </c>
+      <c r="F3" s="2">
+        <v>88.293</v>
+      </c>
+      <c r="G3" s="2">
+        <v>88.588</v>
+      </c>
+      <c r="H3" s="2">
+        <v>89.613</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4">
-        <v>99.8914808034897</v>
-      </c>
-      <c r="D4">
-        <v>99.8909890651703</v>
-      </c>
-      <c r="E4">
-        <v>99.913</v>
-      </c>
-      <c r="F4">
-        <v>99.913</v>
-      </c>
-      <c r="G4">
-        <v>99.913</v>
-      </c>
-      <c r="H4">
-        <v>99.913</v>
+        <v>11</v>
+      </c>
+      <c r="C4" s="2">
+        <v>95.3892946243286</v>
+      </c>
+      <c r="D4" s="2">
+        <v>95.417308807373</v>
+      </c>
+      <c r="E4" s="2">
+        <v>89.526</v>
+      </c>
+      <c r="F4" s="2">
+        <v>88.838</v>
+      </c>
+      <c r="G4" s="2">
+        <v>89.526</v>
+      </c>
+      <c r="H4" s="2">
+        <v>90.424</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5">
-        <v>99.1137653589249</v>
-      </c>
-      <c r="D5">
-        <v>99.1086959838867</v>
-      </c>
-      <c r="E5">
-        <v>97.943</v>
-      </c>
-      <c r="F5">
-        <v>97.947</v>
-      </c>
-      <c r="G5">
-        <v>97.943</v>
-      </c>
-      <c r="H5">
-        <v>97.963</v>
+        <v>12</v>
+      </c>
+      <c r="C5" s="2">
+        <v>96.5366005897522</v>
+      </c>
+      <c r="D5" s="2">
+        <v>96.5652883052826</v>
+      </c>
+      <c r="E5" s="2">
+        <v>66.043</v>
+      </c>
+      <c r="F5" s="2">
+        <v>67.93</v>
+      </c>
+      <c r="G5" s="2">
+        <v>66.043</v>
+      </c>
+      <c r="H5" s="2">
+        <v>75.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6">
-        <v>99.8914808034897</v>
-      </c>
-      <c r="D6">
-        <v>99.8910009860992</v>
-      </c>
-      <c r="E6">
-        <v>99.722</v>
-      </c>
-      <c r="F6">
-        <v>99.722</v>
-      </c>
-      <c r="G6">
-        <v>99.722</v>
-      </c>
-      <c r="H6">
-        <v>99.722</v>
+        <v>13</v>
+      </c>
+      <c r="C6" s="2">
+        <v>71.2636202573776</v>
+      </c>
+      <c r="D6" s="2">
+        <v>73.0861842632294</v>
+      </c>
+      <c r="E6" s="2">
+        <v>84.786</v>
+      </c>
+      <c r="F6" s="2">
+        <v>84.203</v>
+      </c>
+      <c r="G6" s="2">
+        <v>84.786</v>
+      </c>
+      <c r="H6" s="2">
+        <v>86.236</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7">
-        <v>93.2492315769196</v>
-      </c>
-      <c r="D7">
-        <v>93.1852996349335</v>
-      </c>
-      <c r="E7">
-        <v>83.237</v>
-      </c>
-      <c r="F7">
-        <v>82.209</v>
-      </c>
-      <c r="G7">
-        <v>83.237</v>
-      </c>
-      <c r="H7">
-        <v>85.137</v>
+      <c r="C7" s="2">
+        <v>99.5128154754639</v>
+      </c>
+      <c r="D7" s="2">
+        <v>99.5119571685791</v>
+      </c>
+      <c r="E7" s="2">
+        <v>99.361</v>
+      </c>
+      <c r="F7" s="2">
+        <v>99.361</v>
+      </c>
+      <c r="G7" s="2">
+        <v>99.361</v>
+      </c>
+      <c r="H7" s="2">
+        <v>99.365</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8">
-        <v>92.9078489542007</v>
-      </c>
-      <c r="D8">
-        <v>92.8485572338104</v>
-      </c>
-      <c r="E8">
-        <v>88.334</v>
-      </c>
-      <c r="F8">
-        <v>87.388</v>
-      </c>
-      <c r="G8">
-        <v>88.334</v>
-      </c>
-      <c r="H8">
-        <v>89.607</v>
+        <v>10</v>
+      </c>
+      <c r="C8" s="2">
+        <v>98.9408612251282</v>
+      </c>
+      <c r="D8" s="2">
+        <v>98.9948272705078</v>
+      </c>
+      <c r="E8" s="2">
+        <v>99.286</v>
+      </c>
+      <c r="F8" s="2">
+        <v>99.289</v>
+      </c>
+      <c r="G8" s="2">
+        <v>99.286</v>
+      </c>
+      <c r="H8" s="2">
+        <v>99.295</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9">
-        <v>92.8739368915558</v>
-      </c>
-      <c r="D9">
-        <v>92.8263187408447</v>
-      </c>
-      <c r="E9">
-        <v>88.307</v>
-      </c>
-      <c r="F9">
-        <v>87.205</v>
-      </c>
-      <c r="G9">
-        <v>88.307</v>
-      </c>
-      <c r="H9">
-        <v>89.244</v>
+        <v>11</v>
+      </c>
+      <c r="C9" s="2">
+        <v>99.8394906520844</v>
+      </c>
+      <c r="D9" s="2">
+        <v>99.8390853404999</v>
+      </c>
+      <c r="E9" s="2">
+        <v>99.789</v>
+      </c>
+      <c r="F9" s="2">
+        <v>99.789</v>
+      </c>
+      <c r="G9" s="2">
+        <v>99.789</v>
+      </c>
+      <c r="H9" s="2">
+        <v>99.789</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10">
-        <v>94.4384157657623</v>
-      </c>
-      <c r="D10">
-        <v>94.4093823432922</v>
-      </c>
-      <c r="E10">
-        <v>71.045</v>
-      </c>
-      <c r="F10">
-        <v>71.379</v>
-      </c>
-      <c r="G10">
-        <v>71.045</v>
-      </c>
-      <c r="H10">
-        <v>76.352</v>
+        <v>12</v>
+      </c>
+      <c r="C10" s="2">
+        <v>99.7920155525208</v>
+      </c>
+      <c r="D10" s="2">
+        <v>99.7915267944336</v>
+      </c>
+      <c r="E10" s="2">
+        <v>99.015</v>
+      </c>
+      <c r="F10" s="2">
+        <v>99.07</v>
+      </c>
+      <c r="G10" s="2">
+        <v>99.015</v>
+      </c>
+      <c r="H10" s="2">
+        <v>99.205</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1"/>
       <c r="B11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11">
-        <v>90.0321006774902</v>
-      </c>
-      <c r="D11">
-        <v>90.0094449520111</v>
-      </c>
-      <c r="E11">
-        <v>84.857</v>
-      </c>
-      <c r="F11">
-        <v>83.486</v>
-      </c>
-      <c r="G11">
-        <v>84.857</v>
-      </c>
-      <c r="H11">
-        <v>85.731</v>
+        <v>13</v>
+      </c>
+      <c r="C11" s="2">
+        <v>99.8592674732208</v>
+      </c>
+      <c r="D11" s="2">
+        <v>99.8588442802429</v>
+      </c>
+      <c r="E11" s="2">
+        <v>99.562</v>
+      </c>
+      <c r="F11" s="2">
+        <v>99.562</v>
+      </c>
+      <c r="G11" s="2">
+        <v>99.562</v>
+      </c>
+      <c r="H11" s="2">
+        <v>99.563</v>
       </c>
     </row>
   </sheetData>

--- a/results/results.xlsx
+++ b/results/results.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="conv2d_T_regression_demlp" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="conv2d_T_regression_demlp_S" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="145621" fullCalcOnLoad="1"/>
@@ -88,13 +89,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -560,126 +563,126 @@
           <t>160</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="0" t="n">
         <v>96.00533545017242</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="0" t="n">
         <v>96.02869749069214</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="0" t="n">
         <v>83.321</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="0" t="n">
         <v>82.636</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="0" t="n">
         <v>83.321</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="0" t="n">
         <v>84.681</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n"/>
+      <c r="A3" s="2" t="n"/>
       <c r="B3" s="1" t="inlineStr">
         <is>
           <t>192</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="0" t="n">
         <v>95.73235809803009</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="0" t="n">
         <v>95.74950337409973</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="0" t="n">
         <v>88.58799999999999</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="0" t="n">
         <v>88.29300000000001</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="0" t="n">
         <v>88.58799999999999</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="0" t="n">
         <v>89.613</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n"/>
+      <c r="A4" s="2" t="n"/>
       <c r="B4" s="1" t="inlineStr">
         <is>
           <t>224</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="0" t="n">
         <v>95.38929462432861</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="0" t="n">
         <v>95.41730880737305</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="0" t="n">
         <v>89.526</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="0" t="n">
         <v>88.83799999999999</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="0" t="n">
         <v>89.526</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="0" t="n">
         <v>90.42400000000001</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n"/>
+      <c r="A5" s="2" t="n"/>
       <c r="B5" s="1" t="inlineStr">
         <is>
           <t>299</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="0" t="n">
         <v>96.5366005897522</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="0" t="n">
         <v>96.56528830528259</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="0" t="n">
         <v>66.04300000000001</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="0" t="n">
         <v>67.93000000000001</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="0" t="n">
         <v>66.04300000000001</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="0" t="n">
         <v>75.2</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n"/>
+      <c r="A6" s="3" t="n"/>
       <c r="B6" s="1" t="inlineStr">
         <is>
           <t>331</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="0" t="n">
         <v>71.26362025737762</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="0" t="n">
         <v>73.08618426322937</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="0" t="n">
         <v>84.786</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="0" t="n">
         <v>84.203</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="0" t="n">
         <v>84.786</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="0" t="n">
         <v>86.236</v>
       </c>
     </row>
@@ -694,126 +697,126 @@
           <t>160</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="0" t="n">
         <v>99.51281547546387</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="0" t="n">
         <v>99.5119571685791</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="0" t="n">
         <v>99.361</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="0" t="n">
         <v>99.361</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="0" t="n">
         <v>99.361</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="0" t="n">
         <v>99.36499999999999</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n"/>
+      <c r="A8" s="2" t="n"/>
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>192</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="0" t="n">
         <v>98.94086122512817</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="0" t="n">
         <v>98.99482727050781</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="0" t="n">
         <v>99.286</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="0" t="n">
         <v>99.289</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="0" t="n">
         <v>99.286</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="0" t="n">
         <v>99.295</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n"/>
+      <c r="A9" s="2" t="n"/>
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>224</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="0" t="n">
         <v>99.83949065208435</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="0" t="n">
         <v>99.83908534049988</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="0" t="n">
         <v>99.789</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="0" t="n">
         <v>99.789</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="0" t="n">
         <v>99.789</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="0" t="n">
         <v>99.789</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="2" t="n"/>
       <c r="B10" s="1" t="inlineStr">
         <is>
           <t>299</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="0" t="n">
         <v>99.79201555252075</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="0" t="n">
         <v>99.79152679443359</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="0" t="n">
         <v>99.015</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="0" t="n">
         <v>99.06999999999999</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="0" t="n">
         <v>99.015</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="0" t="n">
         <v>99.205</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n"/>
+      <c r="A11" s="3" t="n"/>
       <c r="B11" s="1" t="inlineStr">
         <is>
           <t>331</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="0" t="n">
         <v>99.85926747322083</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="0" t="n">
         <v>99.85884428024292</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="0" t="n">
         <v>99.562</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="0" t="n">
         <v>99.562</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="0" t="n">
         <v>99.562</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="0" t="n">
         <v>99.563</v>
       </c>
     </row>
@@ -824,4 +827,197 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>HyperParameters</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>test_domain</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>VAL_ACC</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>VAL_F1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TEST_ACC</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>TEST_F1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>TEST_R</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>TEST_P</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>stride</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>99.18840527534485</v>
+      </c>
+      <c r="D2" t="n">
+        <v>99.17608499526978</v>
+      </c>
+      <c r="E2" t="n">
+        <v>97.806</v>
+      </c>
+      <c r="F2" t="n">
+        <v>97.751</v>
+      </c>
+      <c r="G2" t="n">
+        <v>97.806</v>
+      </c>
+      <c r="H2" t="n">
+        <v>97.768</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>99.17710423469543</v>
+      </c>
+      <c r="D3" t="n">
+        <v>99.16119575500488</v>
+      </c>
+      <c r="E3" t="n">
+        <v>98.613</v>
+      </c>
+      <c r="F3" t="n">
+        <v>98.584</v>
+      </c>
+      <c r="G3" t="n">
+        <v>98.613</v>
+      </c>
+      <c r="H3" t="n">
+        <v>98.60599999999999</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n"/>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>99.13245439529419</v>
+      </c>
+      <c r="D4" t="n">
+        <v>99.11394119262695</v>
+      </c>
+      <c r="E4" t="n">
+        <v>98.42100000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>98.377</v>
+      </c>
+      <c r="G4" t="n">
+        <v>98.42100000000001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>98.425</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>99.78805780410767</v>
+      </c>
+      <c r="D5" t="n">
+        <v>99.78627562522888</v>
+      </c>
+      <c r="E5" t="n">
+        <v>96.959</v>
+      </c>
+      <c r="F5" t="n">
+        <v>97.045</v>
+      </c>
+      <c r="G5" t="n">
+        <v>96.959</v>
+      </c>
+      <c r="H5" t="n">
+        <v>97.22799999999999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>97.26681113243103</v>
+      </c>
+      <c r="D6" t="n">
+        <v>97.31044769287109</v>
+      </c>
+      <c r="E6" t="n">
+        <v>98.199</v>
+      </c>
+      <c r="F6" t="n">
+        <v>98.247</v>
+      </c>
+      <c r="G6" t="n">
+        <v>98.199</v>
+      </c>
+      <c r="H6" t="n">
+        <v>98.386</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/results/results.xlsx
+++ b/results/results.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="15540" tabRatio="860" activeTab="8"/>
+    <workbookView windowWidth="30720" windowHeight="15540" tabRatio="860"/>
   </bookViews>
   <sheets>
     <sheet name="conv2d" sheetId="6" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="18">
   <si>
     <t>HyperParameters</t>
   </si>
@@ -102,7 +102,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -113,13 +113,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -632,149 +625,146 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1127,40 +1117,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C2">
@@ -1183,8 +1173,8 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="7"/>
-      <c r="B3" s="6" t="s">
+      <c r="A3" s="6"/>
+      <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C3">
@@ -1207,8 +1197,8 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="7"/>
-      <c r="B4" s="6" t="s">
+      <c r="A4" s="6"/>
+      <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C4">
@@ -1231,8 +1221,8 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="7"/>
-      <c r="B5" s="6" t="s">
+      <c r="A5" s="6"/>
+      <c r="B5" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C5">
@@ -1255,8 +1245,8 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="8"/>
-      <c r="B6" s="6" t="s">
+      <c r="A6" s="7"/>
+      <c r="B6" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C6">
@@ -1279,10 +1269,10 @@
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C7">
@@ -1305,8 +1295,8 @@
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="7"/>
-      <c r="B8" s="6" t="s">
+      <c r="A8" s="6"/>
+      <c r="B8" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C8">
@@ -1329,8 +1319,8 @@
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="7"/>
-      <c r="B9" s="6" t="s">
+      <c r="A9" s="6"/>
+      <c r="B9" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C9">
@@ -1353,8 +1343,8 @@
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="7"/>
-      <c r="B10" s="6" t="s">
+      <c r="A10" s="6"/>
+      <c r="B10" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C10">
@@ -1377,8 +1367,8 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="8"/>
-      <c r="B11" s="6" t="s">
+      <c r="A11" s="7"/>
+      <c r="B11" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C11">
@@ -1401,10 +1391,10 @@
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12">
@@ -1427,8 +1417,8 @@
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="7"/>
-      <c r="B13" s="6" t="s">
+      <c r="A13" s="6"/>
+      <c r="B13" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C13">
@@ -1451,8 +1441,8 @@
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="7"/>
-      <c r="B14" s="6" t="s">
+      <c r="A14" s="6"/>
+      <c r="B14" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C14">
@@ -1475,8 +1465,8 @@
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="7"/>
-      <c r="B15" s="6" t="s">
+      <c r="A15" s="6"/>
+      <c r="B15" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C15">
@@ -1488,7 +1478,7 @@
       <c r="E15">
         <v>93.002</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="8">
         <v>93.584</v>
       </c>
       <c r="G15">
@@ -1499,8 +1489,8 @@
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="8"/>
-      <c r="B16" s="6" t="s">
+      <c r="A16" s="7"/>
+      <c r="B16" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C16">
@@ -1521,6 +1511,9 @@
       <c r="H16">
         <v>99.931</v>
       </c>
+    </row>
+    <row r="27" spans="6:6">
+      <c r="F27" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1536,8 +1529,8 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6" outlineLevelRow="5" outlineLevelCol="7"/>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
@@ -1592,7 +1585,7 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="1"/>
+      <c r="A3" s="3"/>
       <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1616,7 +1609,7 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="1"/>
+      <c r="A4" s="3"/>
       <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
@@ -1640,7 +1633,7 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="1"/>
+      <c r="A5" s="3"/>
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
@@ -1664,7 +1657,7 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="1"/>
+      <c r="A6" s="4"/>
       <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
@@ -1687,9 +1680,132 @@
         <v>96.622</v>
       </c>
     </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2">
+        <v>89.2350912094116</v>
+      </c>
+      <c r="D7" s="2">
+        <v>84.1536819934845</v>
+      </c>
+      <c r="E7" s="2">
+        <v>89.227</v>
+      </c>
+      <c r="F7" s="2">
+        <v>84.443</v>
+      </c>
+      <c r="G7" s="2">
+        <v>89.227</v>
+      </c>
+      <c r="H7" s="2">
+        <v>90.391</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2">
+        <v>89.2215251922607</v>
+      </c>
+      <c r="D8" s="2">
+        <v>84.1208398342133</v>
+      </c>
+      <c r="E8" s="2">
+        <v>89.202</v>
+      </c>
+      <c r="F8" s="2">
+        <v>84.385</v>
+      </c>
+      <c r="G8" s="2">
+        <v>89.202</v>
+      </c>
+      <c r="H8" s="2">
+        <v>90.372</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="2">
+        <v>89.2333924770355</v>
+      </c>
+      <c r="D9" s="2">
+        <v>84.149581193924</v>
+      </c>
+      <c r="E9" s="2">
+        <v>89.236</v>
+      </c>
+      <c r="F9" s="2">
+        <v>84.463</v>
+      </c>
+      <c r="G9" s="2">
+        <v>89.236</v>
+      </c>
+      <c r="H9" s="2">
+        <v>90.398</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="2">
+        <v>89.342474937439</v>
+      </c>
+      <c r="D10" s="2">
+        <v>84.4114482402802</v>
+      </c>
+      <c r="E10" s="2">
+        <v>88.916</v>
+      </c>
+      <c r="F10" s="2">
+        <v>83.699</v>
+      </c>
+      <c r="G10" s="2">
+        <v>88.916</v>
+      </c>
+      <c r="H10" s="2">
+        <v>90.144</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="2">
+        <v>89.4854664802551</v>
+      </c>
+      <c r="D11" s="2">
+        <v>84.7485661506653</v>
+      </c>
+      <c r="E11" s="2">
+        <v>88.924</v>
+      </c>
+      <c r="F11" s="2">
+        <v>83.718</v>
+      </c>
+      <c r="G11" s="2">
+        <v>88.924</v>
+      </c>
+      <c r="H11" s="2">
+        <v>90.151</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1703,36 +1819,36 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C2">
@@ -1755,8 +1871,8 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="7"/>
-      <c r="B3" s="6" t="s">
+      <c r="A3" s="6"/>
+      <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C3">
@@ -1779,8 +1895,8 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="7"/>
-      <c r="B4" s="6" t="s">
+      <c r="A4" s="6"/>
+      <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C4">
@@ -1803,8 +1919,8 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="7"/>
-      <c r="B5" s="6" t="s">
+      <c r="A5" s="6"/>
+      <c r="B5" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C5">
@@ -1827,8 +1943,8 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="8"/>
-      <c r="B6" s="6" t="s">
+      <c r="A6" s="7"/>
+      <c r="B6" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C6">
@@ -1851,10 +1967,10 @@
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C7">
@@ -1877,8 +1993,8 @@
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="7"/>
-      <c r="B8" s="6" t="s">
+      <c r="A8" s="6"/>
+      <c r="B8" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C8">
@@ -1901,8 +2017,8 @@
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="7"/>
-      <c r="B9" s="6" t="s">
+      <c r="A9" s="6"/>
+      <c r="B9" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C9">
@@ -1925,8 +2041,8 @@
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="7"/>
-      <c r="B10" s="6" t="s">
+      <c r="A10" s="6"/>
+      <c r="B10" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C10">
@@ -1949,8 +2065,8 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="8"/>
-      <c r="B11" s="6" t="s">
+      <c r="A11" s="7"/>
+      <c r="B11" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C11">
@@ -1989,36 +2105,36 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelRow="5" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C2">
@@ -2041,8 +2157,8 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6" t="s">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C3">
@@ -2065,8 +2181,8 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6" t="s">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C4">
@@ -2089,8 +2205,8 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6" t="s">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C5">
@@ -2113,8 +2229,8 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6" t="s">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C6">
@@ -2152,36 +2268,36 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="5">
         <v>1</v>
       </c>
       <c r="C2">
@@ -2204,8 +2320,8 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="7"/>
-      <c r="B3" s="6">
+      <c r="A3" s="6"/>
+      <c r="B3" s="5">
         <v>2</v>
       </c>
       <c r="C3">
@@ -2228,8 +2344,8 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="7"/>
-      <c r="B4" s="6">
+      <c r="A4" s="6"/>
+      <c r="B4" s="5">
         <v>3</v>
       </c>
       <c r="C4">
@@ -2252,8 +2368,8 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="8"/>
-      <c r="B5" s="6">
+      <c r="A5" s="7"/>
+      <c r="B5" s="5">
         <v>4</v>
       </c>
       <c r="C5">
@@ -2276,10 +2392,10 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>1</v>
       </c>
       <c r="C6">
@@ -2302,8 +2418,8 @@
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="7"/>
-      <c r="B7" s="6">
+      <c r="A7" s="6"/>
+      <c r="B7" s="5">
         <v>2</v>
       </c>
       <c r="C7">
@@ -2326,8 +2442,8 @@
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="7"/>
-      <c r="B8" s="6">
+      <c r="A8" s="6"/>
+      <c r="B8" s="5">
         <v>3</v>
       </c>
       <c r="C8">
@@ -2350,8 +2466,8 @@
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="8"/>
-      <c r="B9" s="6">
+      <c r="A9" s="7"/>
+      <c r="B9" s="5">
         <v>4</v>
       </c>
       <c r="C9">
@@ -2374,10 +2490,10 @@
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="5">
         <v>1</v>
       </c>
       <c r="C10">
@@ -2400,8 +2516,8 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="7"/>
-      <c r="B11" s="6">
+      <c r="A11" s="6"/>
+      <c r="B11" s="5">
         <v>2</v>
       </c>
       <c r="C11">
@@ -2424,8 +2540,8 @@
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="7"/>
-      <c r="B12" s="6">
+      <c r="A12" s="6"/>
+      <c r="B12" s="5">
         <v>3</v>
       </c>
       <c r="C12">
@@ -2448,8 +2564,8 @@
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="8"/>
-      <c r="B13" s="6">
+      <c r="A13" s="7"/>
+      <c r="B13" s="5">
         <v>4</v>
       </c>
       <c r="C13">
@@ -2485,40 +2601,40 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C2">
@@ -2541,8 +2657,8 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="7"/>
-      <c r="B3" s="6" t="s">
+      <c r="A3" s="6"/>
+      <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C3">
@@ -2565,8 +2681,8 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="7"/>
-      <c r="B4" s="6" t="s">
+      <c r="A4" s="6"/>
+      <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C4">
@@ -2589,8 +2705,8 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="7"/>
-      <c r="B5" s="6" t="s">
+      <c r="A5" s="6"/>
+      <c r="B5" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C5">
@@ -2613,8 +2729,8 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="8"/>
-      <c r="B6" s="6" t="s">
+      <c r="A6" s="7"/>
+      <c r="B6" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C6">
@@ -2637,10 +2753,10 @@
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C7">
@@ -2663,8 +2779,8 @@
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="7"/>
-      <c r="B8" s="6" t="s">
+      <c r="A8" s="6"/>
+      <c r="B8" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C8">
@@ -2687,8 +2803,8 @@
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="7"/>
-      <c r="B9" s="6" t="s">
+      <c r="A9" s="6"/>
+      <c r="B9" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C9">
@@ -2711,8 +2827,8 @@
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="7"/>
-      <c r="B10" s="6" t="s">
+      <c r="A10" s="6"/>
+      <c r="B10" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C10">
@@ -2735,8 +2851,8 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="8"/>
-      <c r="B11" s="6" t="s">
+      <c r="A11" s="7"/>
+      <c r="B11" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C11">
@@ -2758,10 +2874,133 @@
         <v>87.658</v>
       </c>
     </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12">
+        <v>99.714020888909</v>
+      </c>
+      <c r="D12">
+        <v>99.7135281562805</v>
+      </c>
+      <c r="E12">
+        <v>98.838</v>
+      </c>
+      <c r="F12">
+        <v>98.812</v>
+      </c>
+      <c r="G12">
+        <v>98.838</v>
+      </c>
+      <c r="H12">
+        <v>98.845</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="6"/>
+      <c r="B13" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>99.5557715784238</v>
+      </c>
+      <c r="D13">
+        <v>99.5525240898132</v>
+      </c>
+      <c r="E13">
+        <v>99.374</v>
+      </c>
+      <c r="F13">
+        <v>99.368</v>
+      </c>
+      <c r="G13">
+        <v>99.374</v>
+      </c>
+      <c r="H13">
+        <v>99.375</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="6"/>
+      <c r="B14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14">
+        <v>99.3387439526156</v>
+      </c>
+      <c r="D14">
+        <v>99.3314683437347</v>
+      </c>
+      <c r="E14">
+        <v>98.518</v>
+      </c>
+      <c r="F14">
+        <v>98.476</v>
+      </c>
+      <c r="G14">
+        <v>98.518</v>
+      </c>
+      <c r="H14">
+        <v>98.528</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="6"/>
+      <c r="B15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15">
+        <v>99.1793642899127</v>
+      </c>
+      <c r="D15">
+        <v>99.1672277450562</v>
+      </c>
+      <c r="E15">
+        <v>96.386</v>
+      </c>
+      <c r="F15">
+        <v>96.477</v>
+      </c>
+      <c r="G15">
+        <v>96.386</v>
+      </c>
+      <c r="H15">
+        <v>96.643</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="7"/>
+      <c r="B16" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16">
+        <v>97.1458606501786</v>
+      </c>
+      <c r="D16">
+        <v>97.1981585025787</v>
+      </c>
+      <c r="E16">
+        <v>98.158</v>
+      </c>
+      <c r="F16">
+        <v>98.203</v>
+      </c>
+      <c r="G16">
+        <v>98.158</v>
+      </c>
+      <c r="H16">
+        <v>98.321</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A2:A6"/>
     <mergeCell ref="A7:A11"/>
+    <mergeCell ref="A12:A16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2771,40 +3010,40 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C2">
@@ -2828,7 +3067,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="6"/>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C3">
@@ -2852,7 +3091,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="6"/>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C4">
@@ -2876,7 +3115,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="6"/>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C5">
@@ -2899,8 +3138,8 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6" t="s">
+      <c r="A6" s="7"/>
+      <c r="B6" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C6">
@@ -2923,10 +3162,10 @@
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C7">
@@ -2950,7 +3189,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="6"/>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C8">
@@ -2974,7 +3213,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="6"/>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C9">
@@ -2998,7 +3237,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="6"/>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C10">
@@ -3021,8 +3260,8 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6" t="s">
+      <c r="A11" s="7"/>
+      <c r="B11" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C11">
@@ -3044,10 +3283,133 @@
         <v>85.731</v>
       </c>
     </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12">
+        <v>99.597576415265</v>
+      </c>
+      <c r="D12">
+        <v>99.5963871479034</v>
+      </c>
+      <c r="E12">
+        <v>98.646</v>
+      </c>
+      <c r="F12">
+        <v>98.621</v>
+      </c>
+      <c r="G12">
+        <v>98.646</v>
+      </c>
+      <c r="H12">
+        <v>98.637</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>99.4890576957859</v>
+      </c>
+      <c r="D13">
+        <v>99.48650598526</v>
+      </c>
+      <c r="E13">
+        <v>99.244</v>
+      </c>
+      <c r="F13">
+        <v>99.238</v>
+      </c>
+      <c r="G13">
+        <v>99.244</v>
+      </c>
+      <c r="H13">
+        <v>99.241</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14">
+        <v>99.2968891300416</v>
+      </c>
+      <c r="D14">
+        <v>99.2904841899872</v>
+      </c>
+      <c r="E14">
+        <v>98.322</v>
+      </c>
+      <c r="F14">
+        <v>98.288</v>
+      </c>
+      <c r="G14">
+        <v>98.322</v>
+      </c>
+      <c r="H14">
+        <v>98.303</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15">
+        <v>98.8424669922228</v>
+      </c>
+      <c r="D15">
+        <v>98.8263070583344</v>
+      </c>
+      <c r="E15">
+        <v>94.243</v>
+      </c>
+      <c r="F15">
+        <v>94.579</v>
+      </c>
+      <c r="G15">
+        <v>94.243</v>
+      </c>
+      <c r="H15">
+        <v>95.312</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16">
+        <v>96.8167842286128</v>
+      </c>
+      <c r="D16">
+        <v>96.9077110290527</v>
+      </c>
+      <c r="E16">
+        <v>96.939</v>
+      </c>
+      <c r="F16">
+        <v>97.535</v>
+      </c>
+      <c r="G16">
+        <v>96.939</v>
+      </c>
+      <c r="H16">
+        <v>97.087</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A2:A6"/>
     <mergeCell ref="A7:A11"/>
+    <mergeCell ref="A12:A16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -3057,40 +3419,40 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C2">
@@ -3113,8 +3475,8 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="4"/>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="6"/>
+      <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C3">
@@ -3137,8 +3499,8 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="4"/>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="6"/>
+      <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C4">
@@ -3161,8 +3523,8 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="4"/>
-      <c r="B5" s="3" t="s">
+      <c r="A5" s="6"/>
+      <c r="B5" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C5">
@@ -3185,8 +3547,8 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="5"/>
-      <c r="B6" s="3" t="s">
+      <c r="A6" s="7"/>
+      <c r="B6" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C6">
@@ -3209,10 +3571,10 @@
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C7">
@@ -3235,8 +3597,8 @@
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="4"/>
-      <c r="B8" s="3" t="s">
+      <c r="A8" s="6"/>
+      <c r="B8" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C8">
@@ -3259,8 +3621,8 @@
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="4"/>
-      <c r="B9" s="3" t="s">
+      <c r="A9" s="6"/>
+      <c r="B9" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C9">
@@ -3283,8 +3645,8 @@
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="4"/>
-      <c r="B10" s="3" t="s">
+      <c r="A10" s="6"/>
+      <c r="B10" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C10">
@@ -3307,8 +3669,8 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="5"/>
-      <c r="B11" s="3" t="s">
+      <c r="A11" s="7"/>
+      <c r="B11" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C11">
@@ -3330,10 +3692,133 @@
         <v>90.509</v>
       </c>
     </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12">
+        <v>99.2556631565094</v>
+      </c>
+      <c r="D12">
+        <v>99.2433309555054</v>
+      </c>
+      <c r="E12">
+        <v>97.386</v>
+      </c>
+      <c r="F12">
+        <v>97.307</v>
+      </c>
+      <c r="G12">
+        <v>97.386</v>
+      </c>
+      <c r="H12">
+        <v>97.331</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>98.9685535430908</v>
+      </c>
+      <c r="D13">
+        <v>98.9541530609131</v>
+      </c>
+      <c r="E13">
+        <v>98.746</v>
+      </c>
+      <c r="F13">
+        <v>98.725</v>
+      </c>
+      <c r="G13">
+        <v>98.746</v>
+      </c>
+      <c r="H13">
+        <v>98.738</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14">
+        <v>99.0861117839813</v>
+      </c>
+      <c r="D14">
+        <v>99.0696787834167</v>
+      </c>
+      <c r="E14">
+        <v>97.834</v>
+      </c>
+      <c r="F14">
+        <v>97.77</v>
+      </c>
+      <c r="G14">
+        <v>97.834</v>
+      </c>
+      <c r="H14">
+        <v>97.805</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15">
+        <v>99.2404043674469</v>
+      </c>
+      <c r="D15">
+        <v>99.2291152477264</v>
+      </c>
+      <c r="E15">
+        <v>96.331</v>
+      </c>
+      <c r="F15">
+        <v>96.438</v>
+      </c>
+      <c r="G15">
+        <v>96.331</v>
+      </c>
+      <c r="H15">
+        <v>96.645</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16">
+        <v>94.3465411663055</v>
+      </c>
+      <c r="D16">
+        <v>94.5609211921692</v>
+      </c>
+      <c r="E16">
+        <v>96.742</v>
+      </c>
+      <c r="F16">
+        <v>96.892</v>
+      </c>
+      <c r="G16">
+        <v>96.742</v>
+      </c>
+      <c r="H16">
+        <v>97.307</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A2:A6"/>
     <mergeCell ref="A7:A11"/>
+    <mergeCell ref="A12:A16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -3343,40 +3828,40 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C2">
@@ -3399,8 +3884,8 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="6"/>
+      <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C3">
@@ -3423,8 +3908,8 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="6"/>
+      <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C4">
@@ -3447,8 +3932,8 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3" t="s">
+      <c r="A5" s="6"/>
+      <c r="B5" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C5">
@@ -3471,8 +3956,8 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3" t="s">
+      <c r="A6" s="7"/>
+      <c r="B6" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C6">
@@ -3495,10 +3980,10 @@
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C7">
@@ -3521,8 +4006,8 @@
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3" t="s">
+      <c r="A8" s="6"/>
+      <c r="B8" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C8">
@@ -3545,8 +4030,8 @@
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3" t="s">
+      <c r="A9" s="6"/>
+      <c r="B9" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C9">
@@ -3569,8 +4054,8 @@
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3" t="s">
+      <c r="A10" s="6"/>
+      <c r="B10" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C10">
@@ -3593,8 +4078,8 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3" t="s">
+      <c r="A11" s="7"/>
+      <c r="B11" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C11">
@@ -3616,10 +4101,133 @@
         <v>78.279</v>
       </c>
     </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12">
+        <v>99.3568301200867</v>
+      </c>
+      <c r="D12">
+        <v>99.3468165397644</v>
+      </c>
+      <c r="E12">
+        <v>99.053</v>
+      </c>
+      <c r="F12">
+        <v>99.037</v>
+      </c>
+      <c r="G12">
+        <v>99.053</v>
+      </c>
+      <c r="H12">
+        <v>99.054</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="6"/>
+      <c r="B13" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>99.1946220397949</v>
+      </c>
+      <c r="D13">
+        <v>99.1811215877533</v>
+      </c>
+      <c r="E13">
+        <v>98.827</v>
+      </c>
+      <c r="F13">
+        <v>98.801</v>
+      </c>
+      <c r="G13">
+        <v>98.827</v>
+      </c>
+      <c r="H13">
+        <v>98.836</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="6"/>
+      <c r="B14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14">
+        <v>99.3523061275482</v>
+      </c>
+      <c r="D14">
+        <v>99.3448793888092</v>
+      </c>
+      <c r="E14">
+        <v>98.857</v>
+      </c>
+      <c r="F14">
+        <v>98.837</v>
+      </c>
+      <c r="G14">
+        <v>98.857</v>
+      </c>
+      <c r="H14">
+        <v>98.853</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="6"/>
+      <c r="B15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15">
+        <v>99.4263470172882</v>
+      </c>
+      <c r="D15">
+        <v>99.417632818222</v>
+      </c>
+      <c r="E15">
+        <v>96.897</v>
+      </c>
+      <c r="F15">
+        <v>96.982</v>
+      </c>
+      <c r="G15">
+        <v>96.897</v>
+      </c>
+      <c r="H15">
+        <v>97.157</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="7"/>
+      <c r="B16" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16">
+        <v>96.3190078735352</v>
+      </c>
+      <c r="D16">
+        <v>96.330726146698</v>
+      </c>
+      <c r="E16">
+        <v>96.629</v>
+      </c>
+      <c r="F16">
+        <v>96.715</v>
+      </c>
+      <c r="G16">
+        <v>96.629</v>
+      </c>
+      <c r="H16">
+        <v>96.878</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A2:A6"/>
     <mergeCell ref="A7:A11"/>
+    <mergeCell ref="A12:A16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -3629,7 +4237,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="15.6" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -3685,7 +4293,7 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="1"/>
+      <c r="A3" s="3"/>
       <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
@@ -3709,7 +4317,7 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="1"/>
+      <c r="A4" s="3"/>
       <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
@@ -3733,7 +4341,7 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="1"/>
+      <c r="A5" s="3"/>
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
@@ -3757,7 +4365,7 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="1"/>
+      <c r="A6" s="4"/>
       <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
@@ -3807,7 +4415,7 @@
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="1"/>
+      <c r="A8" s="3"/>
       <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
@@ -3831,7 +4439,7 @@
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="1"/>
+      <c r="A9" s="3"/>
       <c r="B9" s="1" t="s">
         <v>11</v>
       </c>
@@ -3855,7 +4463,7 @@
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="1"/>
+      <c r="A10" s="3"/>
       <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
@@ -3879,7 +4487,7 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="1"/>
+      <c r="A11" s="4"/>
       <c r="B11" s="1" t="s">
         <v>13</v>
       </c>
@@ -3902,10 +4510,133 @@
         <v>99.563</v>
       </c>
     </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="2">
+        <v>99.1884052753448</v>
+      </c>
+      <c r="D12" s="2">
+        <v>99.1760849952698</v>
+      </c>
+      <c r="E12" s="2">
+        <v>97.806</v>
+      </c>
+      <c r="F12" s="2">
+        <v>97.751</v>
+      </c>
+      <c r="G12" s="2">
+        <v>97.806</v>
+      </c>
+      <c r="H12" s="2">
+        <v>97.768</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="2">
+        <v>99.1771042346954</v>
+      </c>
+      <c r="D13" s="2">
+        <v>99.1611957550049</v>
+      </c>
+      <c r="E13" s="2">
+        <v>98.613</v>
+      </c>
+      <c r="F13" s="2">
+        <v>98.584</v>
+      </c>
+      <c r="G13" s="2">
+        <v>98.613</v>
+      </c>
+      <c r="H13" s="2">
+        <v>98.606</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="2">
+        <v>99.1324543952942</v>
+      </c>
+      <c r="D14" s="2">
+        <v>99.113941192627</v>
+      </c>
+      <c r="E14" s="2">
+        <v>98.421</v>
+      </c>
+      <c r="F14" s="2">
+        <v>98.377</v>
+      </c>
+      <c r="G14" s="2">
+        <v>98.421</v>
+      </c>
+      <c r="H14" s="2">
+        <v>98.425</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="2">
+        <v>99.7880578041077</v>
+      </c>
+      <c r="D15" s="2">
+        <v>99.7862756252289</v>
+      </c>
+      <c r="E15" s="2">
+        <v>96.959</v>
+      </c>
+      <c r="F15" s="2">
+        <v>97.045</v>
+      </c>
+      <c r="G15" s="2">
+        <v>96.959</v>
+      </c>
+      <c r="H15" s="2">
+        <v>97.228</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="2">
+        <v>97.266811132431</v>
+      </c>
+      <c r="D16" s="2">
+        <v>97.3104476928711</v>
+      </c>
+      <c r="E16" s="2">
+        <v>98.199</v>
+      </c>
+      <c r="F16" s="2">
+        <v>98.247</v>
+      </c>
+      <c r="G16" s="2">
+        <v>98.199</v>
+      </c>
+      <c r="H16" s="2">
+        <v>98.386</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A2:A6"/>
     <mergeCell ref="A7:A11"/>
+    <mergeCell ref="A12:A16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/results/results.xlsx
+++ b/results/results.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="conv2d_T_regression_deLvar" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="conv2d_T_regression_deLvar_S" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="145621" fullCalcOnLoad="1"/>
@@ -88,13 +89,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -560,23 +563,216 @@
           <t>160</t>
         </is>
       </c>
+      <c r="C2" s="0" t="n">
+        <v>98.26038479804993</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>97.7003276348114</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>98.512</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>97.934</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>98.512</v>
+      </c>
+      <c r="H2" s="0" t="n">
+        <v>97.372</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>98.25078248977661</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>97.69074320793152</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>98.617</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>98.038</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>98.617</v>
+      </c>
+      <c r="H3" s="0" t="n">
+        <v>97.47199999999999</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>98.25473427772522</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>97.69480228424072</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>98.43600000000001</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>97.857</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>98.43600000000001</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>97.29000000000001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>98.39998483657837</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>97.83938527107239</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>97.033</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>96.461</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>97.033</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>95.899</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n"/>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>98.41694533824921</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>97.8559136390686</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>97.752</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>97.17700000000001</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>97.752</v>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>96.622</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>HyperParameters</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>test_domain</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>VAL_ACC</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>VAL_F1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TEST_ACC</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>TEST_F1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>TEST_R</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>TEST_P</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>stride</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
       <c r="C2" t="n">
-        <v>98.26038479804993</v>
+        <v>89.23509120941162</v>
       </c>
       <c r="D2" t="n">
-        <v>97.7003276348114</v>
+        <v>84.1536819934845</v>
       </c>
       <c r="E2" t="n">
-        <v>98.512</v>
+        <v>89.227</v>
       </c>
       <c r="F2" t="n">
-        <v>97.934</v>
+        <v>84.443</v>
       </c>
       <c r="G2" t="n">
-        <v>98.512</v>
+        <v>89.227</v>
       </c>
       <c r="H2" t="n">
-        <v>97.372</v>
+        <v>90.39100000000001</v>
       </c>
     </row>
     <row r="3">
@@ -587,22 +783,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>98.25078248977661</v>
+        <v>89.22152519226074</v>
       </c>
       <c r="D3" t="n">
-        <v>97.69074320793152</v>
+        <v>84.12083983421326</v>
       </c>
       <c r="E3" t="n">
-        <v>98.617</v>
+        <v>89.202</v>
       </c>
       <c r="F3" t="n">
-        <v>98.038</v>
+        <v>84.38500000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>98.617</v>
+        <v>89.202</v>
       </c>
       <c r="H3" t="n">
-        <v>97.47199999999999</v>
+        <v>90.372</v>
       </c>
     </row>
     <row r="4">
@@ -613,22 +809,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>98.25473427772522</v>
+        <v>89.23339247703552</v>
       </c>
       <c r="D4" t="n">
-        <v>97.69480228424072</v>
+        <v>84.14958119392395</v>
       </c>
       <c r="E4" t="n">
-        <v>98.43600000000001</v>
+        <v>89.236</v>
       </c>
       <c r="F4" t="n">
-        <v>97.857</v>
+        <v>84.46299999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>98.43600000000001</v>
+        <v>89.236</v>
       </c>
       <c r="H4" t="n">
-        <v>97.29000000000001</v>
+        <v>90.398</v>
       </c>
     </row>
     <row r="5">
@@ -639,22 +835,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>98.39998483657837</v>
+        <v>89.34247493743896</v>
       </c>
       <c r="D5" t="n">
-        <v>97.83938527107239</v>
+        <v>84.41144824028015</v>
       </c>
       <c r="E5" t="n">
-        <v>97.033</v>
+        <v>88.916</v>
       </c>
       <c r="F5" t="n">
-        <v>96.461</v>
+        <v>83.699</v>
       </c>
       <c r="G5" t="n">
-        <v>97.033</v>
+        <v>88.916</v>
       </c>
       <c r="H5" t="n">
-        <v>95.899</v>
+        <v>90.14400000000001</v>
       </c>
     </row>
     <row r="6">
@@ -665,22 +861,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>98.41694533824921</v>
+        <v>89.48546648025513</v>
       </c>
       <c r="D6" t="n">
-        <v>97.8559136390686</v>
+        <v>84.74856615066528</v>
       </c>
       <c r="E6" t="n">
-        <v>97.752</v>
+        <v>88.92400000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>97.17700000000001</v>
+        <v>83.718</v>
       </c>
       <c r="G6" t="n">
-        <v>97.752</v>
+        <v>88.92400000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>96.622</v>
+        <v>90.151</v>
       </c>
     </row>
   </sheetData>
